--- a/Symbols_UpdateReferenceID.xlsx
+++ b/Symbols_UpdateReferenceID.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95973E97-E846-41DB-A841-A51127223D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F6D20E-0B6B-4F49-8DF4-A9A8D066F132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3930" yWindow="1155" windowWidth="22215" windowHeight="15480" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Symbols" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <author>tc={FBC2CACE-2F03-4DAC-8894-89865648F172}</author>
   </authors>
   <commentList>
-    <comment ref="C24" authorId="0" shapeId="0" xr:uid="{A32D579A-03F5-456F-BA00-67936BD401D0}">
+    <comment ref="C30" authorId="0" shapeId="0" xr:uid="{A32D579A-03F5-456F-BA00-67936BD401D0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -63,7 +63,7 @@
     Must support signal connection</t>
       </text>
     </comment>
-    <comment ref="C159" authorId="1" shapeId="0" xr:uid="{36C2758C-D037-4478-BDED-0DD258CAD031}">
+    <comment ref="C140" authorId="1" shapeId="0" xr:uid="{36C2758C-D037-4478-BDED-0DD258CAD031}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -71,7 +71,7 @@
     No signal</t>
       </text>
     </comment>
-    <comment ref="C160" authorId="2" shapeId="0" xr:uid="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
+    <comment ref="C141" authorId="2" shapeId="0" xr:uid="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -2164,27 +2164,9 @@
     <t>Wiremesh Demister</t>
   </si>
   <si>
-    <t>ND0043A</t>
-  </si>
-  <si>
-    <t>ND0043B</t>
-  </si>
-  <si>
-    <t>ND0045A</t>
-  </si>
-  <si>
-    <t>ND0045B</t>
-  </si>
-  <si>
-    <t>ND0045C</t>
-  </si>
-  <si>
     <t>ND0082A</t>
   </si>
   <si>
-    <t>ND0083B</t>
-  </si>
-  <si>
     <t>ND0206A</t>
   </si>
   <si>
@@ -2198,6 +2180,24 @@
   </si>
   <si>
     <t>New symbol</t>
+  </si>
+  <si>
+    <t>ND0248A</t>
+  </si>
+  <si>
+    <t>ND0248B</t>
+  </si>
+  <si>
+    <t>ND0249A</t>
+  </si>
+  <si>
+    <t>ND0249B</t>
+  </si>
+  <si>
+    <t>ND0249C</t>
+  </si>
+  <si>
+    <t>ND0082B</t>
   </si>
 </sst>
 </file>
@@ -2264,7 +2264,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2280,6 +2280,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2312,7 +2318,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2335,12 +2341,45 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2356,78 +2395,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2752,16 +2719,16 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C24" dT="2022-01-14T15:23:40.44" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{A32D579A-03F5-456F-BA00-67936BD401D0}">
+  <threadedComment ref="C30" dT="2022-01-14T15:23:40.44" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{A32D579A-03F5-456F-BA00-67936BD401D0}">
     <text>MCC/VSD/THY/MCS</text>
   </threadedComment>
-  <threadedComment ref="C24" dT="2022-01-14T15:24:43.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{67FB19B8-29DB-4553-BC61-721610DBDAD2}" parentId="{A32D579A-03F5-456F-BA00-67936BD401D0}">
+  <threadedComment ref="C30" dT="2022-01-14T15:24:43.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{67FB19B8-29DB-4553-BC61-721610DBDAD2}" parentId="{A32D579A-03F5-456F-BA00-67936BD401D0}">
     <text>Must support signal connection</text>
   </threadedComment>
-  <threadedComment ref="C159" dT="2022-01-14T13:33:08.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{36C2758C-D037-4478-BDED-0DD258CAD031}">
+  <threadedComment ref="C140" dT="2022-01-14T13:33:08.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{36C2758C-D037-4478-BDED-0DD258CAD031}">
     <text>No signal</text>
   </threadedComment>
-  <threadedComment ref="C160" dT="2022-01-14T13:33:16.93" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
+  <threadedComment ref="C141" dT="2022-01-14T13:33:16.93" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
     <text>No Signal - in-line</text>
   </threadedComment>
 </ThreadedComments>
@@ -2769,7 +2736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1" filterMode="1"/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C265"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2784,3163 +2751,3160 @@
     </row>
     <row r="2" spans="1:3" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>702</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>697</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>698</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>700</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
         <v>391</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B9" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="47.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+    <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B10" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B11" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="47.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="12" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B12" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+    <row r="13" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
         <v>349</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B13" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+    <row r="14" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B14" s="13" t="s">
         <v>351</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+    <row r="15" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B15" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+    <row r="16" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B16" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+    <row r="17" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
         <v>634</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B17" s="13" t="s">
         <v>634</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+    <row r="18" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15" t="s">
         <v>635</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B18" s="13" t="s">
         <v>635</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+    <row r="19" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>636</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B19" s="13" t="s">
         <v>636</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+    <row r="20" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="15" t="s">
         <v>637</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B20" s="13" t="s">
         <v>637</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+    <row r="21" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B21" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+    <row r="22" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B22" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+    <row r="23" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
         <v>399</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B23" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+    <row r="24" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B24" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+    <row r="25" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B25" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+    <row r="26" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B26" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="48.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+    <row r="27" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B27" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+    <row r="28" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
         <v>364</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B28" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+    <row r="29" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
         <v>365</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B29" s="13" t="s">
         <v>365</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+    <row r="30" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B30" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+    <row r="31" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B31" s="13" t="s">
         <v>367</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+    <row r="32" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
         <v>369</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B32" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+    <row r="33" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B33" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="60" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+    <row r="34" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
         <v>377</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B34" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+    <row r="35" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
         <v>380</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B35" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+    <row r="36" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
         <v>381</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B36" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+    <row r="37" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B37" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+    <row r="38" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
         <v>384</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B38" s="13" t="s">
         <v>384</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
-        <v>387</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="63" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="63" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>389</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="63" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
         <v>394</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B45" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="63" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
+    <row r="46" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
         <v>395</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B46" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="63" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+    <row r="47" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
         <v>638</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B47" s="13" t="s">
         <v>638</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="63" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+    <row r="48" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="15" t="s">
         <v>639</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B48" s="13" t="s">
         <v>639</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="63" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+    <row r="49" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="15" t="s">
         <v>640</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B49" s="13" t="s">
         <v>640</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+    <row r="50" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="15" t="s">
         <v>641</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B50" s="13" t="s">
         <v>641</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="63" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+    <row r="51" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B51" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
+    <row r="52" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="15" t="s">
         <v>444</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B52" s="14" t="s">
         <v>444</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
+    <row r="53" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B53" s="14" t="s">
         <v>445</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="15" t="s">
+    <row r="54" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="15" t="s">
         <v>447</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B54" s="14" t="s">
         <v>447</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="15" t="s">
+    <row r="55" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B55" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="15" t="s">
+    <row r="56" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
         <v>453</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B56" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="71.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="15" t="s">
+    <row r="57" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B57" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="71.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="15" t="s">
+    <row r="58" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B58" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>458</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="71.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="15" t="s">
+    <row r="59" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B59" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>691</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>692</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>693</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>694</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>695</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+    <row r="60" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>461</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B60" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="s">
-        <v>680</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>702</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="15" t="s">
-        <v>681</v>
-      </c>
-      <c r="B61" s="15" t="s">
-        <v>702</v>
+    <row r="61" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>462</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>3</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="15" t="s">
-        <v>623</v>
-      </c>
-      <c r="B62" s="15" t="s">
-        <v>702</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>463</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>47</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="15" t="s">
-        <v>624</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>702</v>
+        <v>89</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>464</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>91</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="15" t="s">
-        <v>625</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>702</v>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>465</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>147</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="15" t="s">
-        <v>626</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>702</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>466</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>146</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="15" t="s">
-        <v>627</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>702</v>
+        <v>145</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>467</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="15" t="s">
-        <v>628</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>702</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>468</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>242</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="15" t="s">
-        <v>629</v>
-      </c>
-      <c r="B68" s="15" t="s">
-        <v>702</v>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>469</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="15" t="s">
-        <v>630</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>702</v>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>470</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="15" t="s">
-        <v>631</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>702</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>471</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="15" t="s">
-        <v>632</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>702</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>472</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="15" t="s">
-        <v>633</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>702</v>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>473</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>151</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="15" t="s">
-        <v>652</v>
-      </c>
-      <c r="B73" s="15" t="s">
-        <v>702</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>474</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>153</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="15" t="s">
-        <v>653</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>702</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>475</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="15" t="s">
-        <v>654</v>
-      </c>
-      <c r="B75" s="15" t="s">
-        <v>702</v>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>476</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="15" t="s">
-        <v>655</v>
-      </c>
-      <c r="B76" s="15" t="s">
-        <v>702</v>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>477</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="B77" s="15" t="s">
-        <v>702</v>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>478</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="15" t="s">
-        <v>651</v>
-      </c>
-      <c r="B78" s="15" t="s">
-        <v>702</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>479</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>163</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>657</v>
+        <v>162</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>462</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>3</v>
+        <v>480</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>165</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>4</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>463</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>47</v>
+        <v>481</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>464</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>91</v>
+        <v>482</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>90</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>465</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>147</v>
+        <v>483</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>5</v>
+        <v>169</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>466</v>
-      </c>
-      <c r="B83" s="10" t="s">
-        <v>146</v>
+        <v>484</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>170</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>467</v>
-      </c>
-      <c r="B84" s="10" t="s">
-        <v>44</v>
+        <v>485</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>45</v>
+        <v>173</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>468</v>
-      </c>
-      <c r="B85" s="10" t="s">
-        <v>242</v>
+        <v>486</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>343</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>469</v>
-      </c>
-      <c r="B86" s="10" t="s">
-        <v>6</v>
+        <v>487</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>93</v>
+        <v>243</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>95</v>
+        <v>246</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>472</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>149</v>
+        <v>490</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>473</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>151</v>
+        <v>491</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>474</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>153</v>
+        <v>492</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>475</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>155</v>
+        <v>493</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>245</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>476</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>157</v>
+        <v>494</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>244</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>477</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>159</v>
+        <v>691</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>60</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="43.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>163</v>
+        <v>50</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>480</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>165</v>
+        <v>497</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>481</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>70</v>
+        <v>498</v>
+      </c>
+      <c r="B98" s="10" t="s">
+        <v>21</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>482</v>
-      </c>
-      <c r="B99" s="7" t="s">
-        <v>166</v>
+        <v>499</v>
+      </c>
+      <c r="B99" s="10" t="s">
+        <v>54</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>483</v>
-      </c>
-      <c r="B100" s="7" t="s">
-        <v>168</v>
+        <v>500</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>62</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>484</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>170</v>
+        <v>501</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>63</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>485</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>172</v>
+        <v>502</v>
+      </c>
+      <c r="B102" s="10" t="s">
+        <v>252</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>486</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>174</v>
+        <v>503</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>487</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>56</v>
+        <v>504</v>
+      </c>
+      <c r="B104" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="61.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>488</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>243</v>
+        <v>505</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>65</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="62.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>489</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>246</v>
+        <v>506</v>
+      </c>
+      <c r="B106" s="10" t="s">
+        <v>68</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>313</v>
+        <v>67</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>490</v>
-      </c>
-      <c r="B107" s="10" t="s">
-        <v>19</v>
+        <v>507</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>253</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>20</v>
+        <v>319</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>491</v>
-      </c>
-      <c r="B108" s="10" t="s">
-        <v>59</v>
+        <v>508</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>57</v>
+        <v>177</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>492</v>
-      </c>
-      <c r="B109" s="10" t="s">
-        <v>49</v>
+        <v>509</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>179</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>48</v>
+        <v>178</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>493</v>
-      </c>
-      <c r="B110" s="10" t="s">
-        <v>245</v>
+        <v>510</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>314</v>
+        <v>180</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>494</v>
-      </c>
-      <c r="B111" s="10" t="s">
-        <v>244</v>
+        <v>511</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>183</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>315</v>
+        <v>182</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>696</v>
-      </c>
-      <c r="B112" s="10" t="s">
-        <v>60</v>
+        <v>512</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>697</v>
-      </c>
-      <c r="B113" s="10" t="s">
-        <v>374</v>
+        <v>513</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>254</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>61</v>
+        <v>185</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>368</v>
+        <v>187</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>497</v>
-      </c>
-      <c r="B116" s="10" t="s">
-        <v>51</v>
+        <v>516</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>191</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>52</v>
+        <v>189</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>498</v>
-      </c>
-      <c r="B117" s="10" t="s">
-        <v>21</v>
+        <v>517</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>22</v>
+        <v>190</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>499</v>
-      </c>
-      <c r="B118" s="10" t="s">
-        <v>54</v>
+        <v>518</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>55</v>
+        <v>193</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>500</v>
-      </c>
-      <c r="B119" s="10" t="s">
-        <v>62</v>
+        <v>519</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>255</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>241</v>
+        <v>320</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>501</v>
-      </c>
-      <c r="B120" s="10" t="s">
-        <v>63</v>
+        <v>520</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>64</v>
+        <v>195</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>502</v>
-      </c>
-      <c r="B121" s="10" t="s">
-        <v>252</v>
+        <v>521</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>198</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>316</v>
+        <v>196</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>503</v>
-      </c>
-      <c r="B122" s="10" t="s">
-        <v>250</v>
+        <v>522</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>199</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>317</v>
+        <v>368</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>504</v>
-      </c>
-      <c r="B123" s="10" t="s">
-        <v>251</v>
+        <v>523</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>318</v>
+        <v>368</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>505</v>
-      </c>
-      <c r="B124" s="10" t="s">
-        <v>65</v>
+        <v>524</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>66</v>
+        <v>201</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="B125" s="10" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>253</v>
+        <v>203</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>508</v>
-      </c>
-      <c r="B127" s="8" t="s">
-        <v>176</v>
+        <v>527</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>509</v>
-      </c>
-      <c r="B128" s="8" t="s">
-        <v>179</v>
+        <v>528</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>207</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>181</v>
+        <v>256</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>511</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>183</v>
+        <v>530</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>513</v>
-      </c>
-      <c r="B132" s="7" t="s">
-        <v>254</v>
+        <v>532</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>213</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="54" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>514</v>
-      </c>
-      <c r="B133" s="7" t="s">
-        <v>185</v>
+        <v>533</v>
+      </c>
+      <c r="B133" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>515</v>
-      </c>
-      <c r="B134" s="7" t="s">
-        <v>188</v>
+        <v>534</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>217</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>516</v>
-      </c>
-      <c r="B135" s="7" t="s">
-        <v>191</v>
+        <v>535</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>220</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>517</v>
-      </c>
-      <c r="B136" s="8" t="s">
-        <v>192</v>
+        <v>536</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>247</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>518</v>
-      </c>
-      <c r="B137" s="7" t="s">
-        <v>194</v>
+        <v>537</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>222</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>519</v>
-      </c>
-      <c r="B138" s="7" t="s">
-        <v>255</v>
+        <v>538</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>223</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>520</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>197</v>
+        <v>539</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>521</v>
-      </c>
-      <c r="B140" s="8" t="s">
-        <v>198</v>
+        <v>540</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>225</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>522</v>
-      </c>
-      <c r="B141" s="7" t="s">
-        <v>199</v>
+        <v>541</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>227</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>523</v>
+        <v>542</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>200</v>
+        <v>229</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>202</v>
+        <v>249</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>201</v>
+        <v>338</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>525</v>
-      </c>
-      <c r="B144" s="10" t="s">
-        <v>23</v>
+        <v>544</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>233</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>203</v>
+        <v>234</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>527</v>
-      </c>
-      <c r="B146" s="7" t="s">
-        <v>205</v>
+        <v>546</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>235</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>528</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>207</v>
+        <v>547</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>7</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>529</v>
+        <v>548</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>256</v>
+        <v>97</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>451</v>
+        <v>96</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="B149" s="10" t="s">
-        <v>209</v>
+        <v>9</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>211</v>
+        <v>99</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>212</v>
+        <v>98</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>532</v>
-      </c>
-      <c r="B151" s="10" t="s">
-        <v>213</v>
+        <v>551</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>214</v>
+        <v>100</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>533</v>
-      </c>
-      <c r="B152" s="10" t="s">
-        <v>215</v>
+        <v>552</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>216</v>
+        <v>102</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>534</v>
-      </c>
-      <c r="B153" s="10" t="s">
-        <v>217</v>
+        <v>553</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>218</v>
+        <v>104</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>535</v>
-      </c>
-      <c r="B154" s="10" t="s">
-        <v>220</v>
+        <v>554</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>107</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>219</v>
+        <v>106</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>536</v>
-      </c>
-      <c r="B155" s="10" t="s">
-        <v>247</v>
+        <v>555</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>258</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>537</v>
-      </c>
-      <c r="B156" s="10" t="s">
-        <v>222</v>
+        <v>556</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>221</v>
+        <v>108</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>538</v>
-      </c>
-      <c r="B157" s="10" t="s">
-        <v>223</v>
+        <v>557</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>224</v>
+        <v>110</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>539</v>
-      </c>
-      <c r="B158" s="10" t="s">
-        <v>248</v>
+        <v>558</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>337</v>
+        <v>112</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>540</v>
-      </c>
-      <c r="B159" s="10" t="s">
-        <v>225</v>
+        <v>559</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>257</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="B160" s="10" t="s">
-        <v>227</v>
+        <v>115</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>229</v>
+        <v>117</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>249</v>
+        <v>119</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>233</v>
+        <v>121</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>545</v>
-      </c>
-      <c r="B164" s="7" t="s">
-        <v>234</v>
+        <v>564</v>
+      </c>
+      <c r="B164" s="10" t="s">
+        <v>123</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>231</v>
+        <v>122</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>235</v>
+        <v>125</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>232</v>
+        <v>124</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="B166" s="10" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>97</v>
+        <v>264</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>96</v>
+        <v>322</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>549</v>
-      </c>
-      <c r="B168" s="10" t="s">
-        <v>9</v>
+        <v>568</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>262</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>550</v>
+        <v>569</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>99</v>
+        <v>263</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>101</v>
+        <v>259</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="171" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>103</v>
+        <v>266</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>105</v>
+        <v>261</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>554</v>
-      </c>
-      <c r="B173" s="8" t="s">
-        <v>107</v>
+        <v>573</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>260</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="174" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="175" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>109</v>
+        <v>267</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>111</v>
+        <v>268</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>113</v>
+        <v>270</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
       <c r="B179" s="10" t="s">
-        <v>115</v>
+        <v>11</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>117</v>
+        <v>271</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>119</v>
+        <v>272</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>564</v>
-      </c>
-      <c r="B183" s="10" t="s">
-        <v>123</v>
+        <v>583</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>133</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>565</v>
-      </c>
-      <c r="B184" s="10" t="s">
-        <v>125</v>
+        <v>584</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>566</v>
-      </c>
-      <c r="B185" s="10" t="s">
-        <v>127</v>
+        <v>585</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>273</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>264</v>
+        <v>135</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>259</v>
+        <v>25</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>571</v>
-      </c>
-      <c r="B190" s="7" t="s">
-        <v>266</v>
+        <v>590</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>572</v>
-      </c>
-      <c r="B191" s="7" t="s">
-        <v>261</v>
+        <v>658</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>71</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>573</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>260</v>
+        <v>659</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>408</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>574</v>
+        <v>660</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>265</v>
+        <v>72</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>575</v>
+        <v>661</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>267</v>
+        <v>411</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="195" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>576</v>
-      </c>
-      <c r="B195" s="7" t="s">
-        <v>268</v>
+        <v>662</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>577</v>
-      </c>
-      <c r="B196" s="7" t="s">
-        <v>270</v>
+        <v>663</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>414</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>578</v>
+        <v>664</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>269</v>
+        <v>73</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>333</v>
+        <v>418</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>579</v>
-      </c>
-      <c r="B198" s="10" t="s">
-        <v>11</v>
+        <v>665</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>417</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>580</v>
+        <v>666</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>271</v>
+        <v>74</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>581</v>
+        <v>668</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>272</v>
+        <v>420</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>131</v>
+        <v>275</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>583</v>
-      </c>
-      <c r="B202" s="7" t="s">
-        <v>133</v>
+        <v>592</v>
+      </c>
+      <c r="B202" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>584</v>
-      </c>
-      <c r="B203" s="7" t="s">
-        <v>129</v>
+        <v>593</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>585</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>273</v>
+        <v>594</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>586</v>
+        <v>667</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>587</v>
+        <v>669</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>137</v>
+        <v>423</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>588</v>
+        <v>670</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>589</v>
+        <v>671</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>25</v>
+        <v>426</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>26</v>
+        <v>428</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>590</v>
-      </c>
-      <c r="B209" s="10" t="s">
-        <v>27</v>
+        <v>672</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>28</v>
+        <v>430</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>658</v>
-      </c>
-      <c r="B210" s="10" t="s">
-        <v>71</v>
+        <v>673</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>429</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>659</v>
+        <v>674</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>408</v>
+        <v>33</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>660</v>
-      </c>
-      <c r="B212" s="7" t="s">
-        <v>72</v>
+        <v>675</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>432</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>661</v>
-      </c>
-      <c r="B213" s="7" t="s">
-        <v>411</v>
+        <v>676</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>662</v>
+        <v>677</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>12</v>
+        <v>435</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>663</v>
-      </c>
-      <c r="B215" s="10" t="s">
-        <v>414</v>
+        <v>595</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>664</v>
+        <v>596</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>73</v>
+        <v>276</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>417</v>
+        <v>83</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>74</v>
+        <v>438</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>668</v>
-      </c>
-      <c r="B219" s="7" t="s">
-        <v>420</v>
+        <v>597</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>591</v>
-      </c>
-      <c r="B220" s="7" t="s">
-        <v>275</v>
+        <v>598</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>40</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>592</v>
-      </c>
-      <c r="B221" s="8" t="s">
-        <v>76</v>
+        <v>599</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>593</v>
-      </c>
-      <c r="B222" s="8" t="s">
-        <v>78</v>
+        <v>600</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>277</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>77</v>
+        <v>368</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>594</v>
-      </c>
-      <c r="B223" s="10" t="s">
-        <v>31</v>
+        <v>601</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>139</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>667</v>
+        <v>602</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>79</v>
+        <v>279</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>669</v>
+        <v>603</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>423</v>
+        <v>278</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>670</v>
+        <v>604</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>671</v>
+        <v>605</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>426</v>
+        <v>280</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>81</v>
+        <v>143</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>429</v>
+        <v>373</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>431</v>
+        <v>141</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>674</v>
-      </c>
-      <c r="B230" s="10" t="s">
-        <v>33</v>
+        <v>606</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>433</v>
+        <v>142</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>675</v>
+        <v>607</v>
       </c>
       <c r="B231" s="10" t="s">
-        <v>432</v>
+        <v>35</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>434</v>
+        <v>36</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>676</v>
-      </c>
-      <c r="B232" s="10" t="s">
-        <v>34</v>
+        <v>608</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>436</v>
+        <v>310</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>677</v>
-      </c>
-      <c r="B233" s="10" t="s">
-        <v>435</v>
+        <v>609</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>291</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>595</v>
+        <v>610</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>86</v>
+        <v>284</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>596</v>
+        <v>611</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>678</v>
+        <v>612</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>83</v>
+        <v>290</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>679</v>
+        <v>613</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>438</v>
+        <v>294</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>440</v>
+        <v>303</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="B238" s="10" t="s">
-        <v>88</v>
+        <v>288</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>87</v>
+        <v>304</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>598</v>
-      </c>
-      <c r="B239" s="10" t="s">
-        <v>40</v>
+        <v>615</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>599</v>
+        <v>616</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>138</v>
+        <v>283</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" ht="54" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>601</v>
+        <v>618</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>139</v>
+        <v>292</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" ht="48.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>602</v>
+        <v>619</v>
       </c>
       <c r="B243" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" ht="45.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>603</v>
+        <v>620</v>
       </c>
       <c r="B244" s="7" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" ht="45.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>604</v>
-      </c>
-      <c r="B245" s="7" t="s">
-        <v>140</v>
+        <v>621</v>
+      </c>
+      <c r="B245" s="10" t="s">
+        <v>289</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" ht="36" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>605</v>
-      </c>
-      <c r="B246" s="7" t="s">
-        <v>280</v>
+        <v>622</v>
+      </c>
+      <c r="B246" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" ht="42.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>698</v>
-      </c>
-      <c r="B247" s="7" t="s">
-        <v>143</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A247" s="15" t="s">
+        <v>680</v>
+      </c>
+      <c r="B247" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" ht="45.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>699</v>
-      </c>
-      <c r="B248" s="7" t="s">
-        <v>373</v>
+        <v>682</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="B248" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>606</v>
-      </c>
-      <c r="B249" s="7" t="s">
-        <v>144</v>
+        <v>683</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="15" t="s">
+        <v>623</v>
+      </c>
+      <c r="B249" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>142</v>
+        <v>688</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>607</v>
-      </c>
-      <c r="B250" s="10" t="s">
-        <v>35</v>
+      <c r="A250" s="15" t="s">
+        <v>624</v>
+      </c>
+      <c r="B250" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>608</v>
-      </c>
-      <c r="B251" s="7" t="s">
-        <v>293</v>
+        <v>689</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A251" s="15" t="s">
+        <v>625</v>
+      </c>
+      <c r="B251" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>609</v>
-      </c>
-      <c r="B252" s="7" t="s">
-        <v>291</v>
+        <v>690</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="15" t="s">
+        <v>626</v>
+      </c>
+      <c r="B252" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" ht="42" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>610</v>
-      </c>
-      <c r="B253" s="7" t="s">
-        <v>284</v>
+        <v>642</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="B253" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>611</v>
-      </c>
-      <c r="B254" s="7" t="s">
-        <v>285</v>
+        <v>644</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A254" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="B254" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>612</v>
-      </c>
-      <c r="B255" s="7" t="s">
-        <v>290</v>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A255" s="15" t="s">
+        <v>629</v>
+      </c>
+      <c r="B255" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>613</v>
-      </c>
-      <c r="B256" s="7" t="s">
-        <v>294</v>
+        <v>646</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A256" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="B256" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>303</v>
+        <v>647</v>
       </c>
     </row>
     <row r="257" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>614</v>
-      </c>
-      <c r="B257" s="10" t="s">
-        <v>288</v>
+      <c r="A257" s="15" t="s">
+        <v>631</v>
+      </c>
+      <c r="B257" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A258" t="s">
-        <v>615</v>
-      </c>
-      <c r="B258" s="7" t="s">
-        <v>287</v>
+        <v>648</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="15" t="s">
+        <v>632</v>
+      </c>
+      <c r="B258" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A259" t="s">
-        <v>616</v>
-      </c>
-      <c r="B259" s="7" t="s">
-        <v>283</v>
+        <v>649</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="B259" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
-        <v>617</v>
-      </c>
-      <c r="B260" s="7" t="s">
-        <v>282</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="B260" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A261" t="s">
-        <v>618</v>
-      </c>
-      <c r="B261" s="7" t="s">
-        <v>292</v>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="B261" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A262" t="s">
-        <v>619</v>
-      </c>
-      <c r="B262" s="7" t="s">
-        <v>281</v>
+        <v>685</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="B262" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" ht="35.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A263" t="s">
-        <v>620</v>
-      </c>
-      <c r="B263" s="7" t="s">
-        <v>286</v>
+        <v>686</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="15" t="s">
+        <v>655</v>
+      </c>
+      <c r="B263" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>308</v>
+        <v>687</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" t="s">
-        <v>621</v>
-      </c>
-      <c r="B264" s="10" t="s">
-        <v>289</v>
+      <c r="A264" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="B264" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>309</v>
+        <v>656</v>
       </c>
     </row>
     <row r="265" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A265" t="s">
-        <v>622</v>
-      </c>
-      <c r="B265" s="11" t="s">
-        <v>41</v>
+      <c r="A265" s="15" t="s">
+        <v>651</v>
+      </c>
+      <c r="B265" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>42</v>
+        <v>657</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:C265" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <colorFilter dxfId="3"/>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C78">
-      <sortCondition sortBy="cellColor" ref="B2:B265" dxfId="5"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C265">
+      <sortCondition sortBy="cellColor" ref="A2:A265" dxfId="1"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B79" r:id="rId1" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA001A_Detail.svg" xr:uid="{17ADBAC8-7138-41E8-BDFB-2ED015B2E3B6}"/>
-    <hyperlink ref="B86" r:id="rId2" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA008A_Detail.svg" xr:uid="{3A518947-B6F8-4C42-81D7-7894D9144A33}"/>
-    <hyperlink ref="B166" r:id="rId3" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP001A_Detail.svg" xr:uid="{761B47C6-804C-4528-8497-BBE932BB2C49}"/>
-    <hyperlink ref="B168" r:id="rId4" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP003A_Detail.svg" xr:uid="{EC8BC23F-0549-4B47-A475-38BE73BE9CEE}"/>
-    <hyperlink ref="B222" r:id="rId5" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV012A_Detail.svg" xr:uid="{5A391EDE-1D55-4CFD-9901-A29E0591193B}"/>
-    <hyperlink ref="B9" r:id="rId6" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0006_Detail.svg" xr:uid="{975176F7-F497-4824-8376-23C959379C06}"/>
-    <hyperlink ref="B10" r:id="rId7" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0007_Detail.svg" xr:uid="{5FA11009-5EE8-4528-A809-14E1B1FB1C10}"/>
-    <hyperlink ref="B11" r:id="rId8" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0008_Detail.svg" xr:uid="{7720A7D8-16EA-4565-A935-C37587E784A7}"/>
-    <hyperlink ref="B15" r:id="rId9" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0010_Detail.svg" xr:uid="{8BCC9369-A109-4DC7-B34A-9DE621C69D33}"/>
-    <hyperlink ref="B108" r:id="rId10" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE002A_Detail.svg" xr:uid="{BD7A7DCC-BFC7-48AF-B865-B8368E55F2E6}"/>
-    <hyperlink ref="B134" r:id="rId11" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE027A_Detail.svg" xr:uid="{4ECEB4FA-D039-495A-8F42-FFC9B443FDC3}"/>
-    <hyperlink ref="B159" r:id="rId12" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF009A_Detail.svg" xr:uid="{907022FE-3A1A-45BE-8FF2-AC230B1DD29B}"/>
-    <hyperlink ref="B208" r:id="rId13" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV001A_Detail.svg" xr:uid="{A8069CA7-B440-43C6-B571-35216079CADD}"/>
-    <hyperlink ref="B213" r:id="rId14" xr:uid="{7398F614-893C-4326-BA65-62E7CEF8B17B}"/>
-    <hyperlink ref="B227" r:id="rId15" xr:uid="{86D99A6B-DD65-4D76-9524-599D4EAB2E02}"/>
-    <hyperlink ref="B230" r:id="rId16" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV018A_Detail.svg" xr:uid="{3E8578A0-8239-405C-B417-86D7CEF2DB87}"/>
-    <hyperlink ref="B234" r:id="rId17" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV021A_Detail.svg" xr:uid="{27E00768-DA9C-4DAF-98AA-2381306E4A13}"/>
-    <hyperlink ref="B250" r:id="rId18" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ013A_Detail.svg" xr:uid="{9F7EE259-EBE5-4578-86F7-E5EF694FDA65}"/>
-    <hyperlink ref="B245" r:id="rId19" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ009A_Detail.svg" xr:uid="{30065FD0-FD2C-4BF8-A534-106ECA4A05E6}"/>
-    <hyperlink ref="B265" r:id="rId20" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/STPL008_Detail.svg" xr:uid="{F132DB26-A2BF-4161-B712-08766D64B599}"/>
-    <hyperlink ref="B56" r:id="rId21" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{21C87E9B-CBD0-4B81-A925-45F9B4FD8864}"/>
-    <hyperlink ref="B84" r:id="rId22" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA006A_Detail.svg" xr:uid="{C46298F6-C022-42A8-88EB-27031801D32E}"/>
-    <hyperlink ref="B17" r:id="rId23" xr:uid="{045D2E44-4A59-4C52-AA81-3156413AFAFC}"/>
-    <hyperlink ref="B81" r:id="rId24" display="PA002A" xr:uid="{6BAE8F82-BC2B-4427-9773-0A3AE429BDE1}"/>
-    <hyperlink ref="B109" r:id="rId25" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE003A_Detail.svg" xr:uid="{4004AC67-08BF-4573-A91C-196B852BE782}"/>
-    <hyperlink ref="B115" r:id="rId26" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE008A_Detail.svg" xr:uid="{907142FB-A61F-493E-ADCC-40C2E404D844}"/>
-    <hyperlink ref="B116" r:id="rId27" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE009A_Detail.svg" xr:uid="{42D7E312-902B-45B8-B2E6-478D821615A1}"/>
-    <hyperlink ref="B117" r:id="rId28" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE010A_Detail.svg" xr:uid="{12CE6EBF-4CA8-44DF-B6FC-040DFB92731D}"/>
-    <hyperlink ref="B104" r:id="rId29" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD018A_Detail.svg" xr:uid="{D9AD65D0-256C-4FDA-AB63-641CAEF296B8}"/>
-    <hyperlink ref="B107" r:id="rId30" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE001A_Detail.svg" xr:uid="{B5B862E7-DBAB-44C9-B7B4-21949ADAF9C9}"/>
-    <hyperlink ref="B112" r:id="rId31" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE006A_Detail.svg" xr:uid="{AA6401E6-CD51-4574-ABA6-C7BB3663F989}"/>
-    <hyperlink ref="B114" r:id="rId32" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE007A_Detail.svg" xr:uid="{B35184E7-56AF-48CA-8CC6-9A61FB055044}"/>
-    <hyperlink ref="B118" r:id="rId33" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE011A_Detail.svg" xr:uid="{52A5B7C0-AD9C-472F-899E-86CD63EFB3AA}"/>
-    <hyperlink ref="B119" r:id="rId34" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE012A_Detail.svg" xr:uid="{C3016BE0-26B5-41E3-A7DB-D7C53F62C108}"/>
-    <hyperlink ref="B120" r:id="rId35" display="PE012A" xr:uid="{FFB4E872-E736-41AC-8F80-41BB1E8C57A6}"/>
-    <hyperlink ref="B124" r:id="rId36" display="PE013A" xr:uid="{69F4C8E5-12AD-463A-8F4A-4719422312A8}"/>
-    <hyperlink ref="B98" r:id="rId37" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD012A_Detail.svg" xr:uid="{F25BE2C8-8813-4940-8329-63BBA6D15B89}"/>
-    <hyperlink ref="B209" r:id="rId38" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV002A_Detail.svg" xr:uid="{EB3DD888-4A6F-42F8-AD39-FAC973963B51}"/>
-    <hyperlink ref="B211" r:id="rId39" xr:uid="{C8A2ABD8-A0CE-4FB6-BD75-7694D40F91BE}"/>
-    <hyperlink ref="B215" r:id="rId40" xr:uid="{10BB9991-94D9-43E5-9038-0AD1029C8456}"/>
-    <hyperlink ref="B217" r:id="rId41" xr:uid="{E92459C1-EFAE-4D41-A9A2-B6CBF8031302}"/>
-    <hyperlink ref="B219" r:id="rId42" xr:uid="{FB94CBE5-59E0-4451-A8F5-AF4BCA7E6242}"/>
-    <hyperlink ref="B221" r:id="rId43" display="PV008A" xr:uid="{7C2F94E7-1DC8-40D5-9F4C-AA07CD1D7F60}"/>
-    <hyperlink ref="B223" r:id="rId44" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV013A_Detail.svg" xr:uid="{D981260A-8BAC-4F90-8B22-F4387848B90B}"/>
-    <hyperlink ref="B225" r:id="rId45" xr:uid="{7AB8E356-44B8-49E6-B29B-395AA92E87A4}"/>
-    <hyperlink ref="B229" r:id="rId46" xr:uid="{27C7E718-E4EC-4B45-A105-4219CB86145A}"/>
-    <hyperlink ref="B237" r:id="rId47" xr:uid="{22BEA91F-E09D-41B1-979E-65B6D728D85F}"/>
-    <hyperlink ref="B233" r:id="rId48" xr:uid="{64580D0C-1766-4DB3-AF77-41B1C3F4FBCB}"/>
-    <hyperlink ref="B238" r:id="rId49" display="PZ001A" xr:uid="{6198CEDF-7056-49B0-8C8C-0CE4F43ED518}"/>
-    <hyperlink ref="B80" r:id="rId50" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA002A_Detail.svg" xr:uid="{0302EB7E-2FF3-47CA-B5A8-8E3511F52559}"/>
-    <hyperlink ref="B93" r:id="rId51" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD007A_Detail.svg" xr:uid="{55939466-04EF-445D-B8C5-29A1F47BFBEC}"/>
-    <hyperlink ref="B87" r:id="rId52" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD001A_Detail.svg" xr:uid="{3C931296-EFA6-4A17-ABBE-BA3CEEBAE7CD}"/>
-    <hyperlink ref="B167" r:id="rId53" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP002A_Detail.svg" xr:uid="{7B04BB8C-B4F8-4443-9951-FF9779382F5E}"/>
-    <hyperlink ref="B173" r:id="rId54" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP008A_Detail.svg" xr:uid="{B8AA4B11-0A29-4052-8E9D-3BF8D275C0C3}"/>
-    <hyperlink ref="B169" r:id="rId55" display="PP003A" xr:uid="{A0025AF4-1428-4206-B942-D976CF2EABF6}"/>
-    <hyperlink ref="B170" r:id="rId56" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP005A_Detail.svg" xr:uid="{A6177C8F-61D8-4517-924D-AC098541874E}"/>
-    <hyperlink ref="B171" r:id="rId57" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP006A_Detail.svg" xr:uid="{CCC65F5C-1709-40F0-BC1E-5E22B9EE2E8B}"/>
-    <hyperlink ref="B172" r:id="rId58" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP007A_Detail.svg" xr:uid="{CF9DC830-F3E2-46F7-BB6E-F40EE3588C98}"/>
-    <hyperlink ref="B185" r:id="rId59" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS004A_Detail.svg" xr:uid="{9053D430-E6CE-479A-9C3A-E85BE51DDA2D}"/>
-    <hyperlink ref="B175" r:id="rId60" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP010A_Detail.svg" xr:uid="{0970F33B-0575-4123-83FA-27B45C94A4A2}"/>
-    <hyperlink ref="B176" r:id="rId61" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP011A_Detail.svg" xr:uid="{0EA32245-04D0-41E6-991A-61C23D6D04D5}"/>
-    <hyperlink ref="B177" r:id="rId62" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP012A_Detail.svg" xr:uid="{FBE8CA96-6772-460A-8C03-4C086593A5CE}"/>
-    <hyperlink ref="B179" r:id="rId63" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP014A_Detail.svg" xr:uid="{9377286C-CA88-49CA-8DB6-8B4673069711}"/>
-    <hyperlink ref="B180" r:id="rId64" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP015A_Detail.svg" xr:uid="{4CF07C91-9442-4F6E-8428-DC8B0ABD88EC}"/>
-    <hyperlink ref="B181" r:id="rId65" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP016A_Detail.svg" xr:uid="{95445AC5-539C-433D-929D-1B79509AB314}"/>
-    <hyperlink ref="B182" r:id="rId66" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP017A_Detail.svg" xr:uid="{F1EAA06B-6B10-469E-BFA8-DBE8DA0E67EC}"/>
-    <hyperlink ref="B183" r:id="rId67" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS001A_Detail.svg" xr:uid="{53C8229D-2E3F-405D-A9C8-3F6FE5E0EFCC}"/>
-    <hyperlink ref="B198" r:id="rId68" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT002A_Detail.svg" xr:uid="{8ED0FE06-63C6-4619-8AFA-C21DEA756B38}"/>
-    <hyperlink ref="B202" r:id="rId69" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT006A_Detail.svg" xr:uid="{DE7E75F2-6055-421D-A22C-888A6804396D}"/>
-    <hyperlink ref="B201" r:id="rId70" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT005A_Detail.svg" xr:uid="{95A726E8-8601-4CDB-BBED-77B49873F4C0}"/>
-    <hyperlink ref="B203" r:id="rId71" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT007A_Detail.svg" xr:uid="{B6131D2E-4752-4739-997C-D3CBF679F940}"/>
-    <hyperlink ref="B205" r:id="rId72" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT009A_Detail.svg" xr:uid="{D06AD6E5-7BA2-492F-8D44-8B09ADBF6122}"/>
-    <hyperlink ref="B206" r:id="rId73" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT010A_Detail.svg" xr:uid="{52343A83-46C2-4D49-BFE5-DA8717644CD2}"/>
-    <hyperlink ref="B239" r:id="rId74" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ003A_Detail.svg" xr:uid="{335D3D40-BE42-44FE-929A-0F3D3F26D262}"/>
-    <hyperlink ref="B240" r:id="rId75" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ004A_Detail.svg" xr:uid="{45517A4C-49CF-4A14-BE92-F3323139DBA8}"/>
-    <hyperlink ref="B242" r:id="rId76" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ006A_Detail.svg" xr:uid="{92F8D01F-B6E2-40C7-970D-7EAFB7872F29}"/>
-    <hyperlink ref="B249" r:id="rId77" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ012A_Detail.svg" xr:uid="{F5F1079A-1346-46A4-BF70-9025442AFB80}"/>
-    <hyperlink ref="B247" r:id="rId78" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ011A_Detail.svg" xr:uid="{BDA2ADBE-AC37-448F-9C41-243FB16B0996}"/>
-    <hyperlink ref="B83" r:id="rId79" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA005A_Detail.svg" xr:uid="{BA3A7E34-7D5B-4A78-BB78-1727C668EB8F}"/>
-    <hyperlink ref="B82" r:id="rId80" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA004A_Detail.svg" xr:uid="{39481051-1B60-44BF-8211-0D5C1980FD4B}"/>
-    <hyperlink ref="B88" r:id="rId81" display="PD001A" xr:uid="{3969656E-C88B-42A9-9C3B-B8275B159B5B}"/>
-    <hyperlink ref="B89" r:id="rId82" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD003A_Detail.svg" xr:uid="{86AB2467-10FE-4C5F-883D-EDA03495CD55}"/>
-    <hyperlink ref="B90" r:id="rId83" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD004A_Detail.svg" xr:uid="{A3F7C2AC-969E-4A1D-87C5-6BFE5671E4DC}"/>
-    <hyperlink ref="B91" r:id="rId84" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD005A_Detail.svg" xr:uid="{6DFFDA9D-5A28-4CC7-8DE9-876E2360BFEE}"/>
-    <hyperlink ref="B92" r:id="rId85" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD006A_Detail.svg" xr:uid="{3BB6ACEF-9AAF-4C4D-9A87-FCF6EA0F91BD}"/>
-    <hyperlink ref="B103" r:id="rId86" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD017A_Detail.svg" xr:uid="{28D1C6B0-DDE6-442D-9F10-91D27566478A}"/>
-    <hyperlink ref="B94" r:id="rId87" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD008A_Detail.svg" xr:uid="{AB7B0FCA-5804-4486-8380-FBA9F83DEE66}"/>
-    <hyperlink ref="B95" r:id="rId88" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD009A_Detail.svg" xr:uid="{9D870461-08B6-4714-8A00-09714564A8DF}"/>
-    <hyperlink ref="B96" r:id="rId89" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD010A_Detail.svg" xr:uid="{BB4A6A70-CBD2-4C62-B476-1DB99A7B8C9C}"/>
-    <hyperlink ref="B97" r:id="rId90" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD011A_Detail.svg" xr:uid="{5A9D789E-5B6D-46CC-883A-8FE28112F14B}"/>
-    <hyperlink ref="B99" r:id="rId91" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD013A_Detail.svg" xr:uid="{6394051E-0C5B-4871-B946-B73195930CB1}"/>
-    <hyperlink ref="B100" r:id="rId92" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD014A_Detail.svg" xr:uid="{89E87861-2175-4BEE-A5F9-33D47934E630}"/>
-    <hyperlink ref="B101" r:id="rId93" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD015A_Detail.svg" xr:uid="{C0901CAD-B396-4045-9DFB-94C087A6E9C7}"/>
-    <hyperlink ref="B102" r:id="rId94" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD016A_Detail.svg" xr:uid="{FE18571B-26F6-45A2-AE52-5E17B76EC7F3}"/>
-    <hyperlink ref="B125" r:id="rId95" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE018A_Detail.svg" xr:uid="{6D3B7973-3EAF-4809-A3A6-949465067CBC}"/>
-    <hyperlink ref="B127" r:id="rId96" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE020A_Detail.svg" xr:uid="{39CB98B6-29C9-4B55-BB4D-C050812B9145}"/>
-    <hyperlink ref="B128" r:id="rId97" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE021A_Detail.svg" xr:uid="{50AE8AE5-DEF4-4FC6-8682-258DF3904CD7}"/>
-    <hyperlink ref="B129" r:id="rId98" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE022A_Detail.svg" xr:uid="{93F60579-BA2A-4EDC-B883-017EBA23D13F}"/>
-    <hyperlink ref="B130" r:id="rId99" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE023A_Detail.svg" xr:uid="{2F7FC80D-3FA4-4BE4-A403-E017F265775F}"/>
-    <hyperlink ref="B131" r:id="rId100" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE024A_Detail.svg" xr:uid="{212E32CA-E31F-4B52-AC82-844C20339614}"/>
-    <hyperlink ref="B133" r:id="rId101" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE026A_Detail.svg" xr:uid="{9078864B-22E7-4236-BA73-76CA46B86A31}"/>
-    <hyperlink ref="B135" r:id="rId102" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE028A_Detail.svg" xr:uid="{F436B4D7-3AA5-4126-BBD2-BACE69A4A4E0}"/>
-    <hyperlink ref="B136" r:id="rId103" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE029A_Detail.svg" xr:uid="{C7A515AB-6C11-4EA4-85E4-5091485DAA17}"/>
-    <hyperlink ref="B140" r:id="rId104" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE033A_Detail.svg" xr:uid="{34E7B3BE-E531-4018-BB45-6CCB618C0FBB}"/>
-    <hyperlink ref="B137" r:id="rId105" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE030A_Detail.svg" xr:uid="{1F74D129-65A3-4B07-BF1F-5193476A8A04}"/>
-    <hyperlink ref="B139" r:id="rId106" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE032A_Detail.svg" xr:uid="{8A8FA28E-6634-4E0D-A29F-388C878E8DB9}"/>
-    <hyperlink ref="B141" r:id="rId107" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE034A_Detail.svg" xr:uid="{6C65D9E8-788A-4EFB-B896-E4E82EAA3CB0}"/>
-    <hyperlink ref="B143" r:id="rId108" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE036A_Detail.svg" xr:uid="{6A654C5A-571F-47D9-9387-6F62409DC1B7}"/>
-    <hyperlink ref="B142" r:id="rId109" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE035A_Detail.svg" xr:uid="{8BF957E4-037D-4E36-9BCA-83538FEE7EAF}"/>
-    <hyperlink ref="B144" r:id="rId110" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE037A_Detail.svg" xr:uid="{7931F92F-DB33-458A-84AB-EEE6E7217AAA}"/>
-    <hyperlink ref="B145" r:id="rId111" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE038A_Detail.svg" xr:uid="{F73D9E2D-2341-4000-BD06-BEF7EA513332}"/>
-    <hyperlink ref="B146" r:id="rId112" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE039A_Detail.svg" xr:uid="{FB0AAC16-DEA9-41D3-8765-ACE272916988}"/>
-    <hyperlink ref="B147" r:id="rId113" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE040A_Detail.svg" xr:uid="{9D15EFC4-F96D-4011-83A8-7E4FB0A02FD4}"/>
-    <hyperlink ref="B149" r:id="rId114" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE042A_Detail.svg" xr:uid="{4DC635F0-1E08-4047-98E2-D16EA3B8D3B6}"/>
-    <hyperlink ref="B150" r:id="rId115" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE043A_Detail.svg" xr:uid="{7A91C884-B181-4AC9-8872-A5B4FEC2FA44}"/>
-    <hyperlink ref="B151" r:id="rId116" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF001A_Detail.svg" xr:uid="{226AE98E-A3DA-4D82-91A1-7CFDF93A8DE9}"/>
-    <hyperlink ref="B152" r:id="rId117" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF002A_Detail.svg" xr:uid="{467E946A-F396-4E22-A95C-421F6CE0BC8B}"/>
-    <hyperlink ref="B153" r:id="rId118" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF003A_Detail.svg" xr:uid="{55C30B46-FD0C-4081-A7D2-D7A7DFE70B52}"/>
-    <hyperlink ref="B154" r:id="rId119" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF004A_Detail.svg" xr:uid="{1127E743-3E80-461C-9E2E-11276A527952}"/>
-    <hyperlink ref="B156" r:id="rId120" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF006A_Detail.svg" xr:uid="{C896FA40-2C0C-4F45-ABB7-4A0598EF464F}"/>
-    <hyperlink ref="B157" r:id="rId121" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF007A_Detail.svg" xr:uid="{B63E94F9-6FBE-473E-BB35-4B04D8BA205A}"/>
-    <hyperlink ref="B165" r:id="rId122" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF015A_Detail.svg" xr:uid="{D0C9703A-C515-442F-88BF-811B68EF3142}"/>
-    <hyperlink ref="B160" r:id="rId123" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF010A_Detail.svg" xr:uid="{8776960A-3D62-49BB-964C-0A029249E4ED}"/>
-    <hyperlink ref="B161" r:id="rId124" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF011A_Detail.svg" xr:uid="{52198015-5884-4164-AE13-C31DC940BF9F}"/>
-    <hyperlink ref="B163" r:id="rId125" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF013A_Detail.svg" xr:uid="{1676627D-C9A1-412D-A74B-FEC1DD6ADAFC}"/>
-    <hyperlink ref="B164" r:id="rId126" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF014A_Detail.svg" xr:uid="{0AE6782A-A294-4988-A1A8-09100E831215}"/>
-    <hyperlink ref="B19" r:id="rId127" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0014_Detail.svg" xr:uid="{1F3765D3-EFE7-463A-B085-1DE36D0AE049}"/>
-    <hyperlink ref="B59" r:id="rId128" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/LZ009A_Detail.svg" xr:uid="{964B3FA4-6BEE-49FA-A53D-C16D25DADF11}"/>
-    <hyperlink ref="B18" r:id="rId129" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0013_Detail.svg" xr:uid="{5203DA34-E147-4733-BD2B-596D44AF2F0D}"/>
-    <hyperlink ref="B184" r:id="rId130" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS003A_Detail.svg" xr:uid="{D3E46F2B-78B9-41FF-AD13-E05C1AAC94AA}"/>
-    <hyperlink ref="B204" r:id="rId131" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT008A_Detail.svg" xr:uid="{A09F2ECE-A3F2-485F-89B3-392B6CCF3E0F}"/>
-    <hyperlink ref="B21" r:id="rId132" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0016_Detail.svg" xr:uid="{D78471C4-ED27-412C-838A-FDFC562E1EC3}"/>
-    <hyperlink ref="B235" r:id="rId133" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV022A_Detail.svg" xr:uid="{7F2ADD73-6C39-4114-8228-83338A629639}"/>
-    <hyperlink ref="B261" r:id="rId134" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ024A_Detail.svg" xr:uid="{D7DC9173-D444-4E60-B47B-45295B162EA3}"/>
-    <hyperlink ref="B14" r:id="rId135" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0009_Detail.svg" xr:uid="{CF5F7511-92B4-421B-B7C3-594BAC34117C}"/>
-    <hyperlink ref="B253" r:id="rId136" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ016A_Detail.svg" xr:uid="{223CCECC-C661-4D77-99FB-373C2C3EB9FD}"/>
-    <hyperlink ref="B259" r:id="rId137" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ022A_Detail.svg" xr:uid="{4E646DA6-844E-461F-A30F-E45D4A6BAEE0}"/>
-    <hyperlink ref="B254" r:id="rId138" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ017A_Detail.svg" xr:uid="{4AF15DA4-056F-4E39-B57F-D527D7C96314}"/>
-    <hyperlink ref="B255" r:id="rId139" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ018A_Detail.svg" xr:uid="{6A08BE2B-2F4A-40D0-87F1-2BF30F7E5204}"/>
-    <hyperlink ref="B256" r:id="rId140" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ019A_Detail.svg" xr:uid="{6C2DB1B2-D14C-41F7-85E9-0AD5CD60A40D}"/>
-    <hyperlink ref="B257" r:id="rId141" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ020A_Detail.svg" xr:uid="{3E5BB973-5805-404F-A772-22A577F5EA77}"/>
-    <hyperlink ref="B258" r:id="rId142" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ021A_Detail.svg" xr:uid="{96375F5D-1843-4B64-9FEB-59352041AF1C}"/>
-    <hyperlink ref="B260" r:id="rId143" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ023A_Detail.svg" xr:uid="{D811FB39-FE0C-4790-A865-54A17F50CA6D}"/>
-    <hyperlink ref="B262" r:id="rId144" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ025A_Detail.svg" xr:uid="{60163B1A-1792-49FF-9790-F2BF94ABFA4A}"/>
-    <hyperlink ref="B263" r:id="rId145" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ026A_Detail.svg" xr:uid="{0AAE0EB6-ECBB-4198-AA26-C684A0AECB97}"/>
-    <hyperlink ref="B264" r:id="rId146" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ027A_Detail.svg" xr:uid="{824407FA-7B30-4D5E-93CE-ED8122F65FFE}"/>
-    <hyperlink ref="B251" r:id="rId147" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ014A_Detail.svg" xr:uid="{F99B97AB-F1A6-4427-ABEB-25E3CC85B5DC}"/>
-    <hyperlink ref="B252" r:id="rId148" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ015A_Detail.svg" xr:uid="{12DA03AC-3D4B-49FC-B523-CC4091EF5CF4}"/>
-    <hyperlink ref="B105" r:id="rId149" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD019A_Detail.svg" xr:uid="{1FEADDE7-E396-46B6-9322-03EDCA28A99A}"/>
-    <hyperlink ref="B106" r:id="rId150" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD020A_Detail.svg" xr:uid="{1987EC41-B7CC-4E23-B295-01B52113BE11}"/>
-    <hyperlink ref="B110" r:id="rId151" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE004A_Detail.svg" xr:uid="{22A02656-E11C-40BA-93D1-A3BA2FBE802C}"/>
-    <hyperlink ref="B111" r:id="rId152" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE005A_Detail.svg" xr:uid="{D679D4B8-1D0A-498C-B0C6-64751CDFD8A9}"/>
-    <hyperlink ref="B85" r:id="rId153" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA007A_Detail.svg" xr:uid="{30DD321A-DB3E-4139-B7C6-5B72D5F41E50}"/>
-    <hyperlink ref="B121" r:id="rId154" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE014A_Detail.svg" xr:uid="{2B620BE4-F09B-478A-BDA6-76461B53049C}"/>
-    <hyperlink ref="B122" r:id="rId155" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE015A_Detail.svg" xr:uid="{57F06AB3-A2D4-42BD-8A97-785E7A9DEED3}"/>
-    <hyperlink ref="B123" r:id="rId156" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE016A_Detail.svg" xr:uid="{7714B096-A821-46A9-B38E-478AC0F60DFA}"/>
-    <hyperlink ref="B126" r:id="rId157" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE019A_Detail.svg" xr:uid="{77B288AB-A3B1-4E08-ABAC-36CEFD1274DD}"/>
-    <hyperlink ref="B138" r:id="rId158" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE031A_Detail.svg" xr:uid="{BD8A7598-0DFE-4ACB-ABFF-A23EE4147A0C}"/>
-    <hyperlink ref="B132" r:id="rId159" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE025A_Detail.svg" xr:uid="{111CB70F-38F3-4FA2-9171-155C1FE97029}"/>
-    <hyperlink ref="B186" r:id="rId160" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS005A_Detail.svg" xr:uid="{8BD8F9B2-845D-4212-B985-91349C8461AA}"/>
-    <hyperlink ref="B187" r:id="rId161" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS006A_Detail.svg" xr:uid="{616ABAAF-2406-46A1-9490-096325FB538C}"/>
-    <hyperlink ref="B188" r:id="rId162" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS007A_Detail.svg" xr:uid="{C158EBE4-9C88-4608-8165-95D1C5969FE5}"/>
-    <hyperlink ref="B189" r:id="rId163" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS008A_Detail.svg" xr:uid="{8B850863-4DBF-4261-A871-9900D82512A0}"/>
-    <hyperlink ref="B190" r:id="rId164" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS009A_Detail.svg" xr:uid="{EAA92938-1022-4B27-8A45-FC38DB3D12AB}"/>
-    <hyperlink ref="B191" r:id="rId165" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS010A_Detail.svg" xr:uid="{DE97D73F-147C-4EDC-A7D8-86145F37E03C}"/>
-    <hyperlink ref="B192" r:id="rId166" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS011A_Detail.svg" xr:uid="{006F66EF-728F-49E8-A5FE-751016748DAC}"/>
-    <hyperlink ref="B193" r:id="rId167" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS012A_Detail.svg" xr:uid="{8F448560-0B77-4837-B70F-0B9A88CD3C63}"/>
-    <hyperlink ref="B194" r:id="rId168" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS013A_Detail.svg" xr:uid="{0221699E-5F49-4DF1-B0AB-C4E5888F2A80}"/>
-    <hyperlink ref="B195" r:id="rId169" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS014A_Detail.svg" xr:uid="{C05394F3-DC5D-41A9-A414-4B0B18AAED5C}"/>
-    <hyperlink ref="B196" r:id="rId170" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS015A_Detail.svg" xr:uid="{C2CC68D8-9E61-4D94-BCC1-7A22522BAC81}"/>
-    <hyperlink ref="B197" r:id="rId171" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS016A_Detail.svg" xr:uid="{47A88BDB-E04A-43F6-992D-C76510B510EF}"/>
-    <hyperlink ref="B199" r:id="rId172" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT003A_Detail.svg" xr:uid="{7CF97CF8-3E1A-4A9E-ABE2-3A579CF8676B}"/>
-    <hyperlink ref="B200" r:id="rId173" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT004A_Detail.svg" xr:uid="{75DC4A11-DAE8-4DC6-A6D0-7E3E61B719CC}"/>
-    <hyperlink ref="B148" r:id="rId174" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE041A_Detail.svg" xr:uid="{EF9B4A93-EF2D-4E76-A4CC-16163CED7262}"/>
-    <hyperlink ref="B155" r:id="rId175" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF005A_Detail.svg" xr:uid="{3383514A-9E6D-45A7-AD65-0B18E1BAAD22}"/>
-    <hyperlink ref="B158" r:id="rId176" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF008A_Detail.svg" xr:uid="{73E8300F-62F2-4049-934B-015EDBEED287}"/>
-    <hyperlink ref="B162" r:id="rId177" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF012A_Detail.svg" xr:uid="{E9B3CC0D-A34B-4C8A-B89B-B330DAD71021}"/>
-    <hyperlink ref="B174" r:id="rId178" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP009A_Detail.svg" xr:uid="{0A13328E-0285-44BD-B9CF-A05D28AD6EAD}"/>
-    <hyperlink ref="B207" r:id="rId179" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT011A_Detail.svg" xr:uid="{E88B48B0-2B27-4600-8526-87B72CED5EC1}"/>
-    <hyperlink ref="B220" r:id="rId180" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV009A_Detail.svg" xr:uid="{25FF9022-3620-4A11-BF03-2A03200DD6CC}"/>
-    <hyperlink ref="B241" r:id="rId181" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ005A_Detail.svg" xr:uid="{92F69C2E-BC95-4B0C-9D0B-5D880C9FFE1C}"/>
-    <hyperlink ref="B243" r:id="rId182" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ007A_Detail.svg" xr:uid="{D96D22DE-45BD-4E25-A768-C8AAD05A8872}"/>
-    <hyperlink ref="B244" r:id="rId183" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ008A_Detail.svg" xr:uid="{14ADB638-7CCB-453F-BBA2-E88CDF197096}"/>
-    <hyperlink ref="B246" r:id="rId184" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ010A_Detail.svg" xr:uid="{7FE7B2D2-712E-48EB-BF5E-8AF8801ACB71}"/>
-    <hyperlink ref="B178" r:id="rId185" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP013A_Detail.svg" xr:uid="{81BF01ED-214F-4F7B-B7B6-1F88A3E341A7}"/>
-    <hyperlink ref="B55" r:id="rId186" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM005B_Detail.svg" xr:uid="{C4A57621-4274-4BF3-A654-A53519FAE7AF}"/>
-    <hyperlink ref="B57" r:id="rId187" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017B_Detail.svg" xr:uid="{8BEF6540-739A-43C4-8507-74B88B0E3308}"/>
-    <hyperlink ref="B6" r:id="rId188" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0003_Detail.svg" xr:uid="{5B095D40-6B08-42E7-9F0C-145F4A159D92}"/>
-    <hyperlink ref="B7" r:id="rId189" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0004_Detail.svg" xr:uid="{BA90B708-8CAD-4F91-A3A6-34C70C7242F4}"/>
-    <hyperlink ref="B8" r:id="rId190" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0005_Detail.svg" xr:uid="{A1CF53AA-4E63-4100-8F21-E83AA35C1604}"/>
-    <hyperlink ref="B5" r:id="rId191" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0002_Detail.svg" xr:uid="{A26CE6C0-2BFB-47C3-94E0-6267BE1C6C94}"/>
-    <hyperlink ref="B4" r:id="rId192" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0001_Detail.svg" xr:uid="{E14A7086-B4C6-4FDB-B7D4-7C18C702630A}"/>
-    <hyperlink ref="B20" r:id="rId193" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0015_Detail.svg" xr:uid="{AE8EBDA0-0651-4848-9397-12A25DA64674}"/>
-    <hyperlink ref="B22" r:id="rId194" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0017_Detail.svg" xr:uid="{0FDA170A-0CC3-4C20-BE1F-657A2C1B4131}"/>
-    <hyperlink ref="B23" r:id="rId195" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0018_Detail.svg" xr:uid="{258E20C7-8611-4032-9805-B672D23F3D38}"/>
-    <hyperlink ref="B24" r:id="rId196" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0019_Detail.svg" xr:uid="{16F5DBC3-6C32-416B-BD7D-406F3FF5549E}"/>
-    <hyperlink ref="B25" r:id="rId197" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0020_Detail.svg" xr:uid="{48785553-D98B-4E34-ABA8-058CAA66099A}"/>
-    <hyperlink ref="B26" r:id="rId198" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0021_Detail.svg" xr:uid="{139BFB00-00F8-4867-8E15-C1F2154F05F9}"/>
-    <hyperlink ref="B27" r:id="rId199" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0022_Detail.svg" xr:uid="{5494B9F9-EB11-44D9-9244-7B9E92E147F5}"/>
-    <hyperlink ref="B248" r:id="rId200" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PZ011B_Detail.svg" xr:uid="{0DC3D1D5-A861-49FB-8B82-28A6BF8D90FC}"/>
-    <hyperlink ref="B113" r:id="rId201" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PE006B_Detail.svg" xr:uid="{0C45D283-A845-475E-BF69-81FD14E9C822}"/>
-    <hyperlink ref="B28" r:id="rId202" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0023_Detail.svg" xr:uid="{4C39EC85-7752-4400-9B2C-6C4A7CF9129D}"/>
-    <hyperlink ref="B29" r:id="rId203" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0024_Detail.svg" xr:uid="{F3E501F0-9A11-487D-B608-F9A46D11F5A1}"/>
-    <hyperlink ref="B30" r:id="rId204" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0025_Detail.svg" xr:uid="{83989651-E3F6-4AA7-96A2-FD7640656CAE}"/>
-    <hyperlink ref="B31" r:id="rId205" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0026_Detail.svg" xr:uid="{8691DDEC-7612-406D-B419-95FB08A40E04}"/>
-    <hyperlink ref="B32" r:id="rId206" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0027_Detail.svg" xr:uid="{E1D1D665-0762-4836-9D4E-CFC33239EFAB}"/>
-    <hyperlink ref="B33" r:id="rId207" xr:uid="{288414F9-9549-44EE-B603-BFEE8D6BFFCA}"/>
-    <hyperlink ref="B35" r:id="rId208" xr:uid="{126A3199-30C9-44DA-A9EF-F40296E4A52B}"/>
-    <hyperlink ref="B37" r:id="rId209" xr:uid="{FEADDADD-5407-491E-99C2-A1941A1DD8B1}"/>
-    <hyperlink ref="B38" r:id="rId210" xr:uid="{B79E6062-5651-4B01-BEC5-7AE62BF9E579}"/>
-    <hyperlink ref="B54" r:id="rId211" xr:uid="{D8769202-39EC-477B-918F-91334ACD1BAB}"/>
-    <hyperlink ref="B39" r:id="rId212" xr:uid="{DA884DEF-0521-4137-A538-91F1C7FA4324}"/>
-    <hyperlink ref="B40" r:id="rId213" xr:uid="{E1ACDD90-AB13-4518-A219-F9098936AE31}"/>
-    <hyperlink ref="B58" r:id="rId214" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{7F83B0A5-0EE0-43AE-AE92-E2BAA0FD9574}"/>
-    <hyperlink ref="B16" r:id="rId215" xr:uid="{77F0653D-0E68-4330-940A-9F070D3ED346}"/>
-    <hyperlink ref="B34" r:id="rId216" xr:uid="{9365B1F6-4046-4D2E-9EF9-1AB982DE479E}"/>
-    <hyperlink ref="B36" r:id="rId217" xr:uid="{B6BE678E-A7C5-4B5B-BB06-091807E2A914}"/>
-    <hyperlink ref="B210" r:id="rId218" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV003A_Detail.svg" xr:uid="{0C8B99AD-4AA9-417E-B1B0-268F75966BCC}"/>
-    <hyperlink ref="B212" r:id="rId219" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV004A_Detail.svg" xr:uid="{BDAFB8FD-95C0-434B-AE16-15137BA37528}"/>
-    <hyperlink ref="B214" r:id="rId220" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV005A_Detail.svg" xr:uid="{0038139D-21F7-423E-87D5-9C5E62376BA1}"/>
-    <hyperlink ref="B216" r:id="rId221" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV007A_Detail.svg" xr:uid="{5EC742DE-13C4-4141-8F82-5BD0F4B990E0}"/>
-    <hyperlink ref="B218" r:id="rId222" display="PV007A" xr:uid="{830B1051-3967-43FC-B80A-74AF1570BEB9}"/>
-    <hyperlink ref="B224" r:id="rId223" display="PV013A" xr:uid="{30F95586-AB92-4653-B23F-7D3D3A962855}"/>
-    <hyperlink ref="B226" r:id="rId224" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV015A_Detail.svg" xr:uid="{F26CE65B-B76B-4D88-BDC6-01693C600359}"/>
-    <hyperlink ref="B228" r:id="rId225" display="PV007A" xr:uid="{02722343-94B7-48EC-B39E-9165025BCC28}"/>
-    <hyperlink ref="B231" r:id="rId226" xr:uid="{58E62EE8-432E-4351-BC8D-0F8B4B9357B7}"/>
-    <hyperlink ref="B232" r:id="rId227" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV019A_Detail.svg" xr:uid="{78DCB1A4-463F-4102-997B-4F6DE28990A5}"/>
-    <hyperlink ref="B236" r:id="rId228" display="PV008A" xr:uid="{6917B420-C7C7-497A-A516-FF58A19815DA}"/>
-    <hyperlink ref="B44" r:id="rId229" display="ND0034" xr:uid="{856BC43A-036F-4783-BEFB-EFFAD7B38C2F}"/>
-    <hyperlink ref="B45" r:id="rId230" xr:uid="{818DB528-76D8-4FC4-8EC1-42D46B78152C}"/>
-    <hyperlink ref="B46" r:id="rId231" xr:uid="{F49E31A7-2551-4B04-BAED-A755D94DE548}"/>
-    <hyperlink ref="B47" r:id="rId232" xr:uid="{89382148-ED37-496D-BF2A-B7BD4982B43D}"/>
-    <hyperlink ref="B48" r:id="rId233" xr:uid="{FCC63734-2BEB-4CAA-ACB1-D5C765DB6D72}"/>
-    <hyperlink ref="B49" r:id="rId234" xr:uid="{B6C12D2A-856C-4100-A4FF-9108F71FAB3F}"/>
-    <hyperlink ref="B50" r:id="rId235" xr:uid="{2F8626FB-C2B7-4C4B-A874-A7B030C834DB}"/>
-    <hyperlink ref="B51" r:id="rId236" xr:uid="{535CCF00-68C0-462E-A26E-C4BA5A0CDDDE}"/>
-    <hyperlink ref="B12" r:id="rId237" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0008_Detail.svg" xr:uid="{D707B559-638D-4573-805C-C7D9CDB9CBC1}"/>
-    <hyperlink ref="B13" r:id="rId238" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0009_Detail.svg" xr:uid="{FECDC847-0082-45AE-981B-3DFADADF1E67}"/>
-    <hyperlink ref="B43" r:id="rId239" display="ND0034" xr:uid="{D6EE3D3A-2058-4BA6-8D8D-23CF469451F6}"/>
-    <hyperlink ref="B42" r:id="rId240" display="ND0034" xr:uid="{8D64E28D-255B-48EB-94F8-E534EE940442}"/>
-    <hyperlink ref="B41" r:id="rId241" display="ND0034" xr:uid="{E64C006D-210D-4F3B-A4C7-58677D4CA2AF}"/>
+    <hyperlink ref="B61" r:id="rId1" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA001A_Detail.svg" xr:uid="{17ADBAC8-7138-41E8-BDFB-2ED015B2E3B6}"/>
+    <hyperlink ref="B68" r:id="rId2" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA008A_Detail.svg" xr:uid="{3A518947-B6F8-4C42-81D7-7894D9144A33}"/>
+    <hyperlink ref="B147" r:id="rId3" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP001A_Detail.svg" xr:uid="{761B47C6-804C-4528-8497-BBE932BB2C49}"/>
+    <hyperlink ref="B149" r:id="rId4" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP003A_Detail.svg" xr:uid="{EC8BC23F-0549-4B47-A475-38BE73BE9CEE}"/>
+    <hyperlink ref="B203" r:id="rId5" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV012A_Detail.svg" xr:uid="{5A391EDE-1D55-4CFD-9901-A29E0591193B}"/>
+    <hyperlink ref="B15" r:id="rId6" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0006_Detail.svg" xr:uid="{975176F7-F497-4824-8376-23C959379C06}"/>
+    <hyperlink ref="B16" r:id="rId7" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0007_Detail.svg" xr:uid="{5FA11009-5EE8-4528-A809-14E1B1FB1C10}"/>
+    <hyperlink ref="B17" r:id="rId8" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0008_Detail.svg" xr:uid="{7720A7D8-16EA-4565-A935-C37587E784A7}"/>
+    <hyperlink ref="B21" r:id="rId9" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0010_Detail.svg" xr:uid="{8BCC9369-A109-4DC7-B34A-9DE621C69D33}"/>
+    <hyperlink ref="B90" r:id="rId10" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE002A_Detail.svg" xr:uid="{BD7A7DCC-BFC7-48AF-B865-B8368E55F2E6}"/>
+    <hyperlink ref="B115" r:id="rId11" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE027A_Detail.svg" xr:uid="{4ECEB4FA-D039-495A-8F42-FFC9B443FDC3}"/>
+    <hyperlink ref="B140" r:id="rId12" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF009A_Detail.svg" xr:uid="{907022FE-3A1A-45BE-8FF2-AC230B1DD29B}"/>
+    <hyperlink ref="B189" r:id="rId13" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV001A_Detail.svg" xr:uid="{A8069CA7-B440-43C6-B571-35216079CADD}"/>
+    <hyperlink ref="B194" r:id="rId14" xr:uid="{7398F614-893C-4326-BA65-62E7CEF8B17B}"/>
+    <hyperlink ref="B208" r:id="rId15" xr:uid="{86D99A6B-DD65-4D76-9524-599D4EAB2E02}"/>
+    <hyperlink ref="B211" r:id="rId16" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV018A_Detail.svg" xr:uid="{3E8578A0-8239-405C-B417-86D7CEF2DB87}"/>
+    <hyperlink ref="B215" r:id="rId17" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV021A_Detail.svg" xr:uid="{27E00768-DA9C-4DAF-98AA-2381306E4A13}"/>
+    <hyperlink ref="B231" r:id="rId18" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ013A_Detail.svg" xr:uid="{9F7EE259-EBE5-4578-86F7-E5EF694FDA65}"/>
+    <hyperlink ref="B226" r:id="rId19" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ009A_Detail.svg" xr:uid="{30065FD0-FD2C-4BF8-A534-106ECA4A05E6}"/>
+    <hyperlink ref="B246" r:id="rId20" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/STPL008_Detail.svg" xr:uid="{F132DB26-A2BF-4161-B712-08766D64B599}"/>
+    <hyperlink ref="B6" r:id="rId21" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{21C87E9B-CBD0-4B81-A925-45F9B4FD8864}"/>
+    <hyperlink ref="B66" r:id="rId22" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA006A_Detail.svg" xr:uid="{C46298F6-C022-42A8-88EB-27031801D32E}"/>
+    <hyperlink ref="B23" r:id="rId23" xr:uid="{045D2E44-4A59-4C52-AA81-3156413AFAFC}"/>
+    <hyperlink ref="B63" r:id="rId24" display="PA002A" xr:uid="{6BAE8F82-BC2B-4427-9773-0A3AE429BDE1}"/>
+    <hyperlink ref="B91" r:id="rId25" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE003A_Detail.svg" xr:uid="{4004AC67-08BF-4573-A91C-196B852BE782}"/>
+    <hyperlink ref="B96" r:id="rId26" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE008A_Detail.svg" xr:uid="{907142FB-A61F-493E-ADCC-40C2E404D844}"/>
+    <hyperlink ref="B97" r:id="rId27" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE009A_Detail.svg" xr:uid="{42D7E312-902B-45B8-B2E6-478D821615A1}"/>
+    <hyperlink ref="B98" r:id="rId28" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE010A_Detail.svg" xr:uid="{12CE6EBF-4CA8-44DF-B6FC-040DFB92731D}"/>
+    <hyperlink ref="B86" r:id="rId29" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD018A_Detail.svg" xr:uid="{D9AD65D0-256C-4FDA-AB63-641CAEF296B8}"/>
+    <hyperlink ref="B89" r:id="rId30" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE001A_Detail.svg" xr:uid="{B5B862E7-DBAB-44C9-B7B4-21949ADAF9C9}"/>
+    <hyperlink ref="B94" r:id="rId31" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE006A_Detail.svg" xr:uid="{AA6401E6-CD51-4574-ABA6-C7BB3663F989}"/>
+    <hyperlink ref="B95" r:id="rId32" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE007A_Detail.svg" xr:uid="{B35184E7-56AF-48CA-8CC6-9A61FB055044}"/>
+    <hyperlink ref="B99" r:id="rId33" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE011A_Detail.svg" xr:uid="{52A5B7C0-AD9C-472F-899E-86CD63EFB3AA}"/>
+    <hyperlink ref="B100" r:id="rId34" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE012A_Detail.svg" xr:uid="{C3016BE0-26B5-41E3-A7DB-D7C53F62C108}"/>
+    <hyperlink ref="B101" r:id="rId35" display="PE012A" xr:uid="{FFB4E872-E736-41AC-8F80-41BB1E8C57A6}"/>
+    <hyperlink ref="B105" r:id="rId36" display="PE013A" xr:uid="{69F4C8E5-12AD-463A-8F4A-4719422312A8}"/>
+    <hyperlink ref="B80" r:id="rId37" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD012A_Detail.svg" xr:uid="{F25BE2C8-8813-4940-8329-63BBA6D15B89}"/>
+    <hyperlink ref="B190" r:id="rId38" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV002A_Detail.svg" xr:uid="{EB3DD888-4A6F-42F8-AD39-FAC973963B51}"/>
+    <hyperlink ref="B192" r:id="rId39" xr:uid="{C8A2ABD8-A0CE-4FB6-BD75-7694D40F91BE}"/>
+    <hyperlink ref="B196" r:id="rId40" xr:uid="{10BB9991-94D9-43E5-9038-0AD1029C8456}"/>
+    <hyperlink ref="B198" r:id="rId41" xr:uid="{E92459C1-EFAE-4D41-A9A2-B6CBF8031302}"/>
+    <hyperlink ref="B200" r:id="rId42" xr:uid="{FB94CBE5-59E0-4451-A8F5-AF4BCA7E6242}"/>
+    <hyperlink ref="B202" r:id="rId43" display="PV008A" xr:uid="{7C2F94E7-1DC8-40D5-9F4C-AA07CD1D7F60}"/>
+    <hyperlink ref="B204" r:id="rId44" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV013A_Detail.svg" xr:uid="{D981260A-8BAC-4F90-8B22-F4387848B90B}"/>
+    <hyperlink ref="B206" r:id="rId45" xr:uid="{7AB8E356-44B8-49E6-B29B-395AA92E87A4}"/>
+    <hyperlink ref="B210" r:id="rId46" xr:uid="{27C7E718-E4EC-4B45-A105-4219CB86145A}"/>
+    <hyperlink ref="B218" r:id="rId47" xr:uid="{22BEA91F-E09D-41B1-979E-65B6D728D85F}"/>
+    <hyperlink ref="B214" r:id="rId48" xr:uid="{64580D0C-1766-4DB3-AF77-41B1C3F4FBCB}"/>
+    <hyperlink ref="B219" r:id="rId49" display="PZ001A" xr:uid="{6198CEDF-7056-49B0-8C8C-0CE4F43ED518}"/>
+    <hyperlink ref="B62" r:id="rId50" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA002A_Detail.svg" xr:uid="{0302EB7E-2FF3-47CA-B5A8-8E3511F52559}"/>
+    <hyperlink ref="B75" r:id="rId51" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD007A_Detail.svg" xr:uid="{55939466-04EF-445D-B8C5-29A1F47BFBEC}"/>
+    <hyperlink ref="B69" r:id="rId52" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD001A_Detail.svg" xr:uid="{3C931296-EFA6-4A17-ABBE-BA3CEEBAE7CD}"/>
+    <hyperlink ref="B148" r:id="rId53" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP002A_Detail.svg" xr:uid="{7B04BB8C-B4F8-4443-9951-FF9779382F5E}"/>
+    <hyperlink ref="B154" r:id="rId54" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP008A_Detail.svg" xr:uid="{B8AA4B11-0A29-4052-8E9D-3BF8D275C0C3}"/>
+    <hyperlink ref="B150" r:id="rId55" display="PP003A" xr:uid="{A0025AF4-1428-4206-B942-D976CF2EABF6}"/>
+    <hyperlink ref="B151" r:id="rId56" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP005A_Detail.svg" xr:uid="{A6177C8F-61D8-4517-924D-AC098541874E}"/>
+    <hyperlink ref="B152" r:id="rId57" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP006A_Detail.svg" xr:uid="{CCC65F5C-1709-40F0-BC1E-5E22B9EE2E8B}"/>
+    <hyperlink ref="B153" r:id="rId58" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP007A_Detail.svg" xr:uid="{CF9DC830-F3E2-46F7-BB6E-F40EE3588C98}"/>
+    <hyperlink ref="B166" r:id="rId59" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS004A_Detail.svg" xr:uid="{9053D430-E6CE-479A-9C3A-E85BE51DDA2D}"/>
+    <hyperlink ref="B156" r:id="rId60" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP010A_Detail.svg" xr:uid="{0970F33B-0575-4123-83FA-27B45C94A4A2}"/>
+    <hyperlink ref="B157" r:id="rId61" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP011A_Detail.svg" xr:uid="{0EA32245-04D0-41E6-991A-61C23D6D04D5}"/>
+    <hyperlink ref="B158" r:id="rId62" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP012A_Detail.svg" xr:uid="{FBE8CA96-6772-460A-8C03-4C086593A5CE}"/>
+    <hyperlink ref="B160" r:id="rId63" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP014A_Detail.svg" xr:uid="{9377286C-CA88-49CA-8DB6-8B4673069711}"/>
+    <hyperlink ref="B161" r:id="rId64" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP015A_Detail.svg" xr:uid="{4CF07C91-9442-4F6E-8428-DC8B0ABD88EC}"/>
+    <hyperlink ref="B162" r:id="rId65" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP016A_Detail.svg" xr:uid="{95445AC5-539C-433D-929D-1B79509AB314}"/>
+    <hyperlink ref="B163" r:id="rId66" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP017A_Detail.svg" xr:uid="{F1EAA06B-6B10-469E-BFA8-DBE8DA0E67EC}"/>
+    <hyperlink ref="B164" r:id="rId67" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS001A_Detail.svg" xr:uid="{53C8229D-2E3F-405D-A9C8-3F6FE5E0EFCC}"/>
+    <hyperlink ref="B179" r:id="rId68" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT002A_Detail.svg" xr:uid="{8ED0FE06-63C6-4619-8AFA-C21DEA756B38}"/>
+    <hyperlink ref="B183" r:id="rId69" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT006A_Detail.svg" xr:uid="{DE7E75F2-6055-421D-A22C-888A6804396D}"/>
+    <hyperlink ref="B182" r:id="rId70" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT005A_Detail.svg" xr:uid="{95A726E8-8601-4CDB-BBED-77B49873F4C0}"/>
+    <hyperlink ref="B184" r:id="rId71" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT007A_Detail.svg" xr:uid="{B6131D2E-4752-4739-997C-D3CBF679F940}"/>
+    <hyperlink ref="B186" r:id="rId72" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT009A_Detail.svg" xr:uid="{D06AD6E5-7BA2-492F-8D44-8B09ADBF6122}"/>
+    <hyperlink ref="B187" r:id="rId73" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT010A_Detail.svg" xr:uid="{52343A83-46C2-4D49-BFE5-DA8717644CD2}"/>
+    <hyperlink ref="B220" r:id="rId74" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ003A_Detail.svg" xr:uid="{335D3D40-BE42-44FE-929A-0F3D3F26D262}"/>
+    <hyperlink ref="B221" r:id="rId75" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ004A_Detail.svg" xr:uid="{45517A4C-49CF-4A14-BE92-F3323139DBA8}"/>
+    <hyperlink ref="B223" r:id="rId76" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ006A_Detail.svg" xr:uid="{92F8D01F-B6E2-40C7-970D-7EAFB7872F29}"/>
+    <hyperlink ref="B230" r:id="rId77" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ012A_Detail.svg" xr:uid="{F5F1079A-1346-46A4-BF70-9025442AFB80}"/>
+    <hyperlink ref="B228" r:id="rId78" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ011A_Detail.svg" xr:uid="{BDA2ADBE-AC37-448F-9C41-243FB16B0996}"/>
+    <hyperlink ref="B65" r:id="rId79" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA005A_Detail.svg" xr:uid="{BA3A7E34-7D5B-4A78-BB78-1727C668EB8F}"/>
+    <hyperlink ref="B64" r:id="rId80" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA004A_Detail.svg" xr:uid="{39481051-1B60-44BF-8211-0D5C1980FD4B}"/>
+    <hyperlink ref="B70" r:id="rId81" display="PD001A" xr:uid="{3969656E-C88B-42A9-9C3B-B8275B159B5B}"/>
+    <hyperlink ref="B71" r:id="rId82" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD003A_Detail.svg" xr:uid="{86AB2467-10FE-4C5F-883D-EDA03495CD55}"/>
+    <hyperlink ref="B72" r:id="rId83" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD004A_Detail.svg" xr:uid="{A3F7C2AC-969E-4A1D-87C5-6BFE5671E4DC}"/>
+    <hyperlink ref="B73" r:id="rId84" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD005A_Detail.svg" xr:uid="{6DFFDA9D-5A28-4CC7-8DE9-876E2360BFEE}"/>
+    <hyperlink ref="B74" r:id="rId85" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD006A_Detail.svg" xr:uid="{3BB6ACEF-9AAF-4C4D-9A87-FCF6EA0F91BD}"/>
+    <hyperlink ref="B85" r:id="rId86" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD017A_Detail.svg" xr:uid="{28D1C6B0-DDE6-442D-9F10-91D27566478A}"/>
+    <hyperlink ref="B76" r:id="rId87" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD008A_Detail.svg" xr:uid="{AB7B0FCA-5804-4486-8380-FBA9F83DEE66}"/>
+    <hyperlink ref="B77" r:id="rId88" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD009A_Detail.svg" xr:uid="{9D870461-08B6-4714-8A00-09714564A8DF}"/>
+    <hyperlink ref="B78" r:id="rId89" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD010A_Detail.svg" xr:uid="{BB4A6A70-CBD2-4C62-B476-1DB99A7B8C9C}"/>
+    <hyperlink ref="B79" r:id="rId90" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD011A_Detail.svg" xr:uid="{5A9D789E-5B6D-46CC-883A-8FE28112F14B}"/>
+    <hyperlink ref="B81" r:id="rId91" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD013A_Detail.svg" xr:uid="{6394051E-0C5B-4871-B946-B73195930CB1}"/>
+    <hyperlink ref="B82" r:id="rId92" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD014A_Detail.svg" xr:uid="{89E87861-2175-4BEE-A5F9-33D47934E630}"/>
+    <hyperlink ref="B83" r:id="rId93" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD015A_Detail.svg" xr:uid="{C0901CAD-B396-4045-9DFB-94C087A6E9C7}"/>
+    <hyperlink ref="B84" r:id="rId94" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD016A_Detail.svg" xr:uid="{FE18571B-26F6-45A2-AE52-5E17B76EC7F3}"/>
+    <hyperlink ref="B106" r:id="rId95" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE018A_Detail.svg" xr:uid="{6D3B7973-3EAF-4809-A3A6-949465067CBC}"/>
+    <hyperlink ref="B108" r:id="rId96" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE020A_Detail.svg" xr:uid="{39CB98B6-29C9-4B55-BB4D-C050812B9145}"/>
+    <hyperlink ref="B109" r:id="rId97" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE021A_Detail.svg" xr:uid="{50AE8AE5-DEF4-4FC6-8682-258DF3904CD7}"/>
+    <hyperlink ref="B110" r:id="rId98" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE022A_Detail.svg" xr:uid="{93F60579-BA2A-4EDC-B883-017EBA23D13F}"/>
+    <hyperlink ref="B111" r:id="rId99" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE023A_Detail.svg" xr:uid="{2F7FC80D-3FA4-4BE4-A403-E017F265775F}"/>
+    <hyperlink ref="B112" r:id="rId100" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE024A_Detail.svg" xr:uid="{212E32CA-E31F-4B52-AC82-844C20339614}"/>
+    <hyperlink ref="B114" r:id="rId101" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE026A_Detail.svg" xr:uid="{9078864B-22E7-4236-BA73-76CA46B86A31}"/>
+    <hyperlink ref="B116" r:id="rId102" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE028A_Detail.svg" xr:uid="{F436B4D7-3AA5-4126-BBD2-BACE69A4A4E0}"/>
+    <hyperlink ref="B117" r:id="rId103" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE029A_Detail.svg" xr:uid="{C7A515AB-6C11-4EA4-85E4-5091485DAA17}"/>
+    <hyperlink ref="B121" r:id="rId104" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE033A_Detail.svg" xr:uid="{34E7B3BE-E531-4018-BB45-6CCB618C0FBB}"/>
+    <hyperlink ref="B118" r:id="rId105" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE030A_Detail.svg" xr:uid="{1F74D129-65A3-4B07-BF1F-5193476A8A04}"/>
+    <hyperlink ref="B120" r:id="rId106" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE032A_Detail.svg" xr:uid="{8A8FA28E-6634-4E0D-A29F-388C878E8DB9}"/>
+    <hyperlink ref="B122" r:id="rId107" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE034A_Detail.svg" xr:uid="{6C65D9E8-788A-4EFB-B896-E4E82EAA3CB0}"/>
+    <hyperlink ref="B124" r:id="rId108" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE036A_Detail.svg" xr:uid="{6A654C5A-571F-47D9-9387-6F62409DC1B7}"/>
+    <hyperlink ref="B123" r:id="rId109" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE035A_Detail.svg" xr:uid="{8BF957E4-037D-4E36-9BCA-83538FEE7EAF}"/>
+    <hyperlink ref="B125" r:id="rId110" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE037A_Detail.svg" xr:uid="{7931F92F-DB33-458A-84AB-EEE6E7217AAA}"/>
+    <hyperlink ref="B126" r:id="rId111" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE038A_Detail.svg" xr:uid="{F73D9E2D-2341-4000-BD06-BEF7EA513332}"/>
+    <hyperlink ref="B127" r:id="rId112" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE039A_Detail.svg" xr:uid="{FB0AAC16-DEA9-41D3-8765-ACE272916988}"/>
+    <hyperlink ref="B128" r:id="rId113" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE040A_Detail.svg" xr:uid="{9D15EFC4-F96D-4011-83A8-7E4FB0A02FD4}"/>
+    <hyperlink ref="B130" r:id="rId114" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE042A_Detail.svg" xr:uid="{4DC635F0-1E08-4047-98E2-D16EA3B8D3B6}"/>
+    <hyperlink ref="B131" r:id="rId115" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE043A_Detail.svg" xr:uid="{7A91C884-B181-4AC9-8872-A5B4FEC2FA44}"/>
+    <hyperlink ref="B132" r:id="rId116" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF001A_Detail.svg" xr:uid="{226AE98E-A3DA-4D82-91A1-7CFDF93A8DE9}"/>
+    <hyperlink ref="B133" r:id="rId117" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF002A_Detail.svg" xr:uid="{467E946A-F396-4E22-A95C-421F6CE0BC8B}"/>
+    <hyperlink ref="B134" r:id="rId118" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF003A_Detail.svg" xr:uid="{55C30B46-FD0C-4081-A7D2-D7A7DFE70B52}"/>
+    <hyperlink ref="B135" r:id="rId119" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF004A_Detail.svg" xr:uid="{1127E743-3E80-461C-9E2E-11276A527952}"/>
+    <hyperlink ref="B137" r:id="rId120" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF006A_Detail.svg" xr:uid="{C896FA40-2C0C-4F45-ABB7-4A0598EF464F}"/>
+    <hyperlink ref="B138" r:id="rId121" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF007A_Detail.svg" xr:uid="{B63E94F9-6FBE-473E-BB35-4B04D8BA205A}"/>
+    <hyperlink ref="B146" r:id="rId122" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF015A_Detail.svg" xr:uid="{D0C9703A-C515-442F-88BF-811B68EF3142}"/>
+    <hyperlink ref="B141" r:id="rId123" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF010A_Detail.svg" xr:uid="{8776960A-3D62-49BB-964C-0A029249E4ED}"/>
+    <hyperlink ref="B142" r:id="rId124" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF011A_Detail.svg" xr:uid="{52198015-5884-4164-AE13-C31DC940BF9F}"/>
+    <hyperlink ref="B144" r:id="rId125" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF013A_Detail.svg" xr:uid="{1676627D-C9A1-412D-A74B-FEC1DD6ADAFC}"/>
+    <hyperlink ref="B145" r:id="rId126" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF014A_Detail.svg" xr:uid="{0AE6782A-A294-4988-A1A8-09100E831215}"/>
+    <hyperlink ref="B25" r:id="rId127" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0014_Detail.svg" xr:uid="{1F3765D3-EFE7-463A-B085-1DE36D0AE049}"/>
+    <hyperlink ref="B60" r:id="rId128" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/LZ009A_Detail.svg" xr:uid="{964B3FA4-6BEE-49FA-A53D-C16D25DADF11}"/>
+    <hyperlink ref="B24" r:id="rId129" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0013_Detail.svg" xr:uid="{5203DA34-E147-4733-BD2B-596D44AF2F0D}"/>
+    <hyperlink ref="B165" r:id="rId130" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS003A_Detail.svg" xr:uid="{D3E46F2B-78B9-41FF-AD13-E05C1AAC94AA}"/>
+    <hyperlink ref="B185" r:id="rId131" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT008A_Detail.svg" xr:uid="{A09F2ECE-A3F2-485F-89B3-392B6CCF3E0F}"/>
+    <hyperlink ref="B27" r:id="rId132" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0016_Detail.svg" xr:uid="{D78471C4-ED27-412C-838A-FDFC562E1EC3}"/>
+    <hyperlink ref="B216" r:id="rId133" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV022A_Detail.svg" xr:uid="{7F2ADD73-6C39-4114-8228-83338A629639}"/>
+    <hyperlink ref="B242" r:id="rId134" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ024A_Detail.svg" xr:uid="{D7DC9173-D444-4E60-B47B-45295B162EA3}"/>
+    <hyperlink ref="B20" r:id="rId135" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0009_Detail.svg" xr:uid="{CF5F7511-92B4-421B-B7C3-594BAC34117C}"/>
+    <hyperlink ref="B234" r:id="rId136" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ016A_Detail.svg" xr:uid="{223CCECC-C661-4D77-99FB-373C2C3EB9FD}"/>
+    <hyperlink ref="B240" r:id="rId137" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ022A_Detail.svg" xr:uid="{4E646DA6-844E-461F-A30F-E45D4A6BAEE0}"/>
+    <hyperlink ref="B235" r:id="rId138" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ017A_Detail.svg" xr:uid="{4AF15DA4-056F-4E39-B57F-D527D7C96314}"/>
+    <hyperlink ref="B236" r:id="rId139" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ018A_Detail.svg" xr:uid="{6A08BE2B-2F4A-40D0-87F1-2BF30F7E5204}"/>
+    <hyperlink ref="B237" r:id="rId140" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ019A_Detail.svg" xr:uid="{6C2DB1B2-D14C-41F7-85E9-0AD5CD60A40D}"/>
+    <hyperlink ref="B238" r:id="rId141" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ020A_Detail.svg" xr:uid="{3E5BB973-5805-404F-A772-22A577F5EA77}"/>
+    <hyperlink ref="B239" r:id="rId142" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ021A_Detail.svg" xr:uid="{96375F5D-1843-4B64-9FEB-59352041AF1C}"/>
+    <hyperlink ref="B241" r:id="rId143" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ023A_Detail.svg" xr:uid="{D811FB39-FE0C-4790-A865-54A17F50CA6D}"/>
+    <hyperlink ref="B243" r:id="rId144" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ025A_Detail.svg" xr:uid="{60163B1A-1792-49FF-9790-F2BF94ABFA4A}"/>
+    <hyperlink ref="B244" r:id="rId145" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ026A_Detail.svg" xr:uid="{0AAE0EB6-ECBB-4198-AA26-C684A0AECB97}"/>
+    <hyperlink ref="B245" r:id="rId146" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ027A_Detail.svg" xr:uid="{824407FA-7B30-4D5E-93CE-ED8122F65FFE}"/>
+    <hyperlink ref="B232" r:id="rId147" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ014A_Detail.svg" xr:uid="{F99B97AB-F1A6-4427-ABEB-25E3CC85B5DC}"/>
+    <hyperlink ref="B233" r:id="rId148" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ015A_Detail.svg" xr:uid="{12DA03AC-3D4B-49FC-B523-CC4091EF5CF4}"/>
+    <hyperlink ref="B87" r:id="rId149" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD019A_Detail.svg" xr:uid="{1FEADDE7-E396-46B6-9322-03EDCA28A99A}"/>
+    <hyperlink ref="B88" r:id="rId150" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD020A_Detail.svg" xr:uid="{1987EC41-B7CC-4E23-B295-01B52113BE11}"/>
+    <hyperlink ref="B92" r:id="rId151" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE004A_Detail.svg" xr:uid="{22A02656-E11C-40BA-93D1-A3BA2FBE802C}"/>
+    <hyperlink ref="B93" r:id="rId152" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE005A_Detail.svg" xr:uid="{D679D4B8-1D0A-498C-B0C6-64751CDFD8A9}"/>
+    <hyperlink ref="B67" r:id="rId153" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA007A_Detail.svg" xr:uid="{30DD321A-DB3E-4139-B7C6-5B72D5F41E50}"/>
+    <hyperlink ref="B102" r:id="rId154" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE014A_Detail.svg" xr:uid="{2B620BE4-F09B-478A-BDA6-76461B53049C}"/>
+    <hyperlink ref="B103" r:id="rId155" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE015A_Detail.svg" xr:uid="{57F06AB3-A2D4-42BD-8A97-785E7A9DEED3}"/>
+    <hyperlink ref="B104" r:id="rId156" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE016A_Detail.svg" xr:uid="{7714B096-A821-46A9-B38E-478AC0F60DFA}"/>
+    <hyperlink ref="B107" r:id="rId157" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE019A_Detail.svg" xr:uid="{77B288AB-A3B1-4E08-ABAC-36CEFD1274DD}"/>
+    <hyperlink ref="B119" r:id="rId158" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE031A_Detail.svg" xr:uid="{BD8A7598-0DFE-4ACB-ABFF-A23EE4147A0C}"/>
+    <hyperlink ref="B113" r:id="rId159" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE025A_Detail.svg" xr:uid="{111CB70F-38F3-4FA2-9171-155C1FE97029}"/>
+    <hyperlink ref="B167" r:id="rId160" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS005A_Detail.svg" xr:uid="{8BD8F9B2-845D-4212-B985-91349C8461AA}"/>
+    <hyperlink ref="B168" r:id="rId161" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS006A_Detail.svg" xr:uid="{616ABAAF-2406-46A1-9490-096325FB538C}"/>
+    <hyperlink ref="B169" r:id="rId162" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS007A_Detail.svg" xr:uid="{C158EBE4-9C88-4608-8165-95D1C5969FE5}"/>
+    <hyperlink ref="B170" r:id="rId163" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS008A_Detail.svg" xr:uid="{8B850863-4DBF-4261-A871-9900D82512A0}"/>
+    <hyperlink ref="B171" r:id="rId164" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS009A_Detail.svg" xr:uid="{EAA92938-1022-4B27-8A45-FC38DB3D12AB}"/>
+    <hyperlink ref="B172" r:id="rId165" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS010A_Detail.svg" xr:uid="{DE97D73F-147C-4EDC-A7D8-86145F37E03C}"/>
+    <hyperlink ref="B173" r:id="rId166" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS011A_Detail.svg" xr:uid="{006F66EF-728F-49E8-A5FE-751016748DAC}"/>
+    <hyperlink ref="B174" r:id="rId167" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS012A_Detail.svg" xr:uid="{8F448560-0B77-4837-B70F-0B9A88CD3C63}"/>
+    <hyperlink ref="B175" r:id="rId168" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS013A_Detail.svg" xr:uid="{0221699E-5F49-4DF1-B0AB-C4E5888F2A80}"/>
+    <hyperlink ref="B176" r:id="rId169" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS014A_Detail.svg" xr:uid="{C05394F3-DC5D-41A9-A414-4B0B18AAED5C}"/>
+    <hyperlink ref="B177" r:id="rId170" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS015A_Detail.svg" xr:uid="{C2CC68D8-9E61-4D94-BCC1-7A22522BAC81}"/>
+    <hyperlink ref="B178" r:id="rId171" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS016A_Detail.svg" xr:uid="{47A88BDB-E04A-43F6-992D-C76510B510EF}"/>
+    <hyperlink ref="B180" r:id="rId172" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT003A_Detail.svg" xr:uid="{7CF97CF8-3E1A-4A9E-ABE2-3A579CF8676B}"/>
+    <hyperlink ref="B181" r:id="rId173" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT004A_Detail.svg" xr:uid="{75DC4A11-DAE8-4DC6-A6D0-7E3E61B719CC}"/>
+    <hyperlink ref="B129" r:id="rId174" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE041A_Detail.svg" xr:uid="{EF9B4A93-EF2D-4E76-A4CC-16163CED7262}"/>
+    <hyperlink ref="B136" r:id="rId175" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF005A_Detail.svg" xr:uid="{3383514A-9E6D-45A7-AD65-0B18E1BAAD22}"/>
+    <hyperlink ref="B139" r:id="rId176" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF008A_Detail.svg" xr:uid="{73E8300F-62F2-4049-934B-015EDBEED287}"/>
+    <hyperlink ref="B143" r:id="rId177" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF012A_Detail.svg" xr:uid="{E9B3CC0D-A34B-4C8A-B89B-B330DAD71021}"/>
+    <hyperlink ref="B155" r:id="rId178" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP009A_Detail.svg" xr:uid="{0A13328E-0285-44BD-B9CF-A05D28AD6EAD}"/>
+    <hyperlink ref="B188" r:id="rId179" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT011A_Detail.svg" xr:uid="{E88B48B0-2B27-4600-8526-87B72CED5EC1}"/>
+    <hyperlink ref="B201" r:id="rId180" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV009A_Detail.svg" xr:uid="{25FF9022-3620-4A11-BF03-2A03200DD6CC}"/>
+    <hyperlink ref="B222" r:id="rId181" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ005A_Detail.svg" xr:uid="{92F69C2E-BC95-4B0C-9D0B-5D880C9FFE1C}"/>
+    <hyperlink ref="B224" r:id="rId182" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ007A_Detail.svg" xr:uid="{D96D22DE-45BD-4E25-A768-C8AAD05A8872}"/>
+    <hyperlink ref="B225" r:id="rId183" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ008A_Detail.svg" xr:uid="{14ADB638-7CCB-453F-BBA2-E88CDF197096}"/>
+    <hyperlink ref="B227" r:id="rId184" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ010A_Detail.svg" xr:uid="{7FE7B2D2-712E-48EB-BF5E-8AF8801ACB71}"/>
+    <hyperlink ref="B159" r:id="rId185" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP013A_Detail.svg" xr:uid="{81BF01ED-214F-4F7B-B7B6-1F88A3E341A7}"/>
+    <hyperlink ref="B5" r:id="rId186" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM005B_Detail.svg" xr:uid="{C4A57621-4274-4BF3-A654-A53519FAE7AF}"/>
+    <hyperlink ref="B7" r:id="rId187" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017B_Detail.svg" xr:uid="{8BEF6540-739A-43C4-8507-74B88B0E3308}"/>
+    <hyperlink ref="B12" r:id="rId188" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0003_Detail.svg" xr:uid="{5B095D40-6B08-42E7-9F0C-145F4A159D92}"/>
+    <hyperlink ref="B13" r:id="rId189" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0004_Detail.svg" xr:uid="{BA90B708-8CAD-4F91-A3A6-34C70C7242F4}"/>
+    <hyperlink ref="B14" r:id="rId190" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0005_Detail.svg" xr:uid="{A1CF53AA-4E63-4100-8F21-E83AA35C1604}"/>
+    <hyperlink ref="B11" r:id="rId191" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0002_Detail.svg" xr:uid="{A26CE6C0-2BFB-47C3-94E0-6267BE1C6C94}"/>
+    <hyperlink ref="B10" r:id="rId192" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0001_Detail.svg" xr:uid="{E14A7086-B4C6-4FDB-B7D4-7C18C702630A}"/>
+    <hyperlink ref="B26" r:id="rId193" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0015_Detail.svg" xr:uid="{AE8EBDA0-0651-4848-9397-12A25DA64674}"/>
+    <hyperlink ref="B28" r:id="rId194" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0017_Detail.svg" xr:uid="{0FDA170A-0CC3-4C20-BE1F-657A2C1B4131}"/>
+    <hyperlink ref="B29" r:id="rId195" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0018_Detail.svg" xr:uid="{258E20C7-8611-4032-9805-B672D23F3D38}"/>
+    <hyperlink ref="B30" r:id="rId196" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0019_Detail.svg" xr:uid="{16F5DBC3-6C32-416B-BD7D-406F3FF5549E}"/>
+    <hyperlink ref="B31" r:id="rId197" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0020_Detail.svg" xr:uid="{48785553-D98B-4E34-ABA8-058CAA66099A}"/>
+    <hyperlink ref="B32" r:id="rId198" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0021_Detail.svg" xr:uid="{139BFB00-00F8-4867-8E15-C1F2154F05F9}"/>
+    <hyperlink ref="B33" r:id="rId199" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0022_Detail.svg" xr:uid="{5494B9F9-EB11-44D9-9244-7B9E92E147F5}"/>
+    <hyperlink ref="B229" r:id="rId200" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PZ011B_Detail.svg" xr:uid="{0DC3D1D5-A861-49FB-8B82-28A6BF8D90FC}"/>
+    <hyperlink ref="B3" r:id="rId201" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PE006B_Detail.svg" xr:uid="{0C45D283-A845-475E-BF69-81FD14E9C822}"/>
+    <hyperlink ref="B34" r:id="rId202" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0023_Detail.svg" xr:uid="{4C39EC85-7752-4400-9B2C-6C4A7CF9129D}"/>
+    <hyperlink ref="B35" r:id="rId203" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0024_Detail.svg" xr:uid="{F3E501F0-9A11-487D-B608-F9A46D11F5A1}"/>
+    <hyperlink ref="B36" r:id="rId204" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0025_Detail.svg" xr:uid="{83989651-E3F6-4AA7-96A2-FD7640656CAE}"/>
+    <hyperlink ref="B37" r:id="rId205" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0026_Detail.svg" xr:uid="{8691DDEC-7612-406D-B419-95FB08A40E04}"/>
+    <hyperlink ref="B38" r:id="rId206" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0027_Detail.svg" xr:uid="{E1D1D665-0762-4836-9D4E-CFC33239EFAB}"/>
+    <hyperlink ref="B39" r:id="rId207" xr:uid="{288414F9-9549-44EE-B603-BFEE8D6BFFCA}"/>
+    <hyperlink ref="B41" r:id="rId208" xr:uid="{126A3199-30C9-44DA-A9EF-F40296E4A52B}"/>
+    <hyperlink ref="B43" r:id="rId209" xr:uid="{FEADDADD-5407-491E-99C2-A1941A1DD8B1}"/>
+    <hyperlink ref="B44" r:id="rId210" xr:uid="{B79E6062-5651-4B01-BEC5-7AE62BF9E579}"/>
+    <hyperlink ref="B4" r:id="rId211" xr:uid="{D8769202-39EC-477B-918F-91334ACD1BAB}"/>
+    <hyperlink ref="B45" r:id="rId212" xr:uid="{DA884DEF-0521-4137-A538-91F1C7FA4324}"/>
+    <hyperlink ref="B46" r:id="rId213" xr:uid="{E1ACDD90-AB13-4518-A219-F9098936AE31}"/>
+    <hyperlink ref="B8" r:id="rId214" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{7F83B0A5-0EE0-43AE-AE92-E2BAA0FD9574}"/>
+    <hyperlink ref="B22" r:id="rId215" xr:uid="{77F0653D-0E68-4330-940A-9F070D3ED346}"/>
+    <hyperlink ref="B40" r:id="rId216" xr:uid="{9365B1F6-4046-4D2E-9EF9-1AB982DE479E}"/>
+    <hyperlink ref="B42" r:id="rId217" xr:uid="{B6BE678E-A7C5-4B5B-BB06-091807E2A914}"/>
+    <hyperlink ref="B191" r:id="rId218" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV003A_Detail.svg" xr:uid="{0C8B99AD-4AA9-417E-B1B0-268F75966BCC}"/>
+    <hyperlink ref="B193" r:id="rId219" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV004A_Detail.svg" xr:uid="{BDAFB8FD-95C0-434B-AE16-15137BA37528}"/>
+    <hyperlink ref="B195" r:id="rId220" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV005A_Detail.svg" xr:uid="{0038139D-21F7-423E-87D5-9C5E62376BA1}"/>
+    <hyperlink ref="B197" r:id="rId221" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV007A_Detail.svg" xr:uid="{5EC742DE-13C4-4141-8F82-5BD0F4B990E0}"/>
+    <hyperlink ref="B199" r:id="rId222" display="PV007A" xr:uid="{830B1051-3967-43FC-B80A-74AF1570BEB9}"/>
+    <hyperlink ref="B205" r:id="rId223" display="PV013A" xr:uid="{30F95586-AB92-4653-B23F-7D3D3A962855}"/>
+    <hyperlink ref="B207" r:id="rId224" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV015A_Detail.svg" xr:uid="{F26CE65B-B76B-4D88-BDC6-01693C600359}"/>
+    <hyperlink ref="B209" r:id="rId225" display="PV007A" xr:uid="{02722343-94B7-48EC-B39E-9165025BCC28}"/>
+    <hyperlink ref="B212" r:id="rId226" xr:uid="{58E62EE8-432E-4351-BC8D-0F8B4B9357B7}"/>
+    <hyperlink ref="B213" r:id="rId227" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV019A_Detail.svg" xr:uid="{78DCB1A4-463F-4102-997B-4F6DE28990A5}"/>
+    <hyperlink ref="B217" r:id="rId228" display="PV008A" xr:uid="{6917B420-C7C7-497A-A516-FF58A19815DA}"/>
+    <hyperlink ref="B50" r:id="rId229" display="ND0034" xr:uid="{856BC43A-036F-4783-BEFB-EFFAD7B38C2F}"/>
+    <hyperlink ref="B51" r:id="rId230" xr:uid="{818DB528-76D8-4FC4-8EC1-42D46B78152C}"/>
+    <hyperlink ref="B52" r:id="rId231" xr:uid="{F49E31A7-2551-4B04-BAED-A755D94DE548}"/>
+    <hyperlink ref="B53" r:id="rId232" xr:uid="{89382148-ED37-496D-BF2A-B7BD4982B43D}"/>
+    <hyperlink ref="B54" r:id="rId233" xr:uid="{FCC63734-2BEB-4CAA-ACB1-D5C765DB6D72}"/>
+    <hyperlink ref="B55" r:id="rId234" xr:uid="{B6C12D2A-856C-4100-A4FF-9108F71FAB3F}"/>
+    <hyperlink ref="B56" r:id="rId235" xr:uid="{2F8626FB-C2B7-4C4B-A874-A7B030C834DB}"/>
+    <hyperlink ref="B57" r:id="rId236" xr:uid="{535CCF00-68C0-462E-A26E-C4BA5A0CDDDE}"/>
+    <hyperlink ref="B18" r:id="rId237" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0008_Detail.svg" xr:uid="{D707B559-638D-4573-805C-C7D9CDB9CBC1}"/>
+    <hyperlink ref="B19" r:id="rId238" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0009_Detail.svg" xr:uid="{FECDC847-0082-45AE-981B-3DFADADF1E67}"/>
+    <hyperlink ref="B49" r:id="rId239" display="ND0034" xr:uid="{D6EE3D3A-2058-4BA6-8D8D-23CF469451F6}"/>
+    <hyperlink ref="B48" r:id="rId240" display="ND0034" xr:uid="{8D64E28D-255B-48EB-94F8-E534EE940442}"/>
+    <hyperlink ref="B47" r:id="rId241" display="ND0034" xr:uid="{E64C006D-210D-4F3B-A4C7-58677D4CA2AF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId242"/>

--- a/Symbols_UpdateReferenceID.xlsx
+++ b/Symbols_UpdateReferenceID.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F6D20E-0B6B-4F49-8DF4-A9A8D066F132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F6A41F-E191-48AE-AE85-955F48868ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="1155" windowWidth="22215" windowHeight="15480" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Symbols" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Symbols!$A$2:$C$265</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Symbols!$A$2:$C$264</definedName>
     <definedName name="DEXPI_CLASS">#REF!</definedName>
     <definedName name="DEXPI_PACKAGE">#REF!</definedName>
     <definedName name="map">#REF!</definedName>
@@ -53,7 +53,7 @@
     <author>tc={FBC2CACE-2F03-4DAC-8894-89865648F172}</author>
   </authors>
   <commentList>
-    <comment ref="C30" authorId="0" shapeId="0" xr:uid="{A32D579A-03F5-456F-BA00-67936BD401D0}">
+    <comment ref="C24" authorId="0" shapeId="0" xr:uid="{A32D579A-03F5-456F-BA00-67936BD401D0}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -63,7 +63,7 @@
     Must support signal connection</t>
       </text>
     </comment>
-    <comment ref="C140" authorId="1" shapeId="0" xr:uid="{36C2758C-D037-4478-BDED-0DD258CAD031}">
+    <comment ref="C139" authorId="1" shapeId="0" xr:uid="{36C2758C-D037-4478-BDED-0DD258CAD031}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -71,7 +71,7 @@
     No signal</t>
       </text>
     </comment>
-    <comment ref="C141" authorId="2" shapeId="0" xr:uid="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
+    <comment ref="C140" authorId="2" shapeId="0" xr:uid="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="711">
   <si>
     <t>Description</t>
   </si>
@@ -2198,6 +2198,30 @@
   </si>
   <si>
     <t>ND0082B</t>
+  </si>
+  <si>
+    <t>ND0043</t>
+  </si>
+  <si>
+    <t>ND0044</t>
+  </si>
+  <si>
+    <t>ND0045</t>
+  </si>
+  <si>
+    <t>ND0046</t>
+  </si>
+  <si>
+    <t>Tie In Point Property Break</t>
+  </si>
+  <si>
+    <t>Custom Equipment Package</t>
+  </si>
+  <si>
+    <t>Mechanical Joint</t>
+  </si>
+  <si>
+    <t>Welded Joint</t>
   </si>
 </sst>
 </file>
@@ -2347,12 +2371,14 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="2">
     <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2361,40 +2387,6 @@
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2719,16 +2711,16 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C30" dT="2022-01-14T15:23:40.44" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{A32D579A-03F5-456F-BA00-67936BD401D0}">
+  <threadedComment ref="C24" dT="2022-01-14T15:23:40.44" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{A32D579A-03F5-456F-BA00-67936BD401D0}">
     <text>MCC/VSD/THY/MCS</text>
   </threadedComment>
-  <threadedComment ref="C30" dT="2022-01-14T15:24:43.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{67FB19B8-29DB-4553-BC61-721610DBDAD2}" parentId="{A32D579A-03F5-456F-BA00-67936BD401D0}">
+  <threadedComment ref="C24" dT="2022-01-14T15:24:43.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{67FB19B8-29DB-4553-BC61-721610DBDAD2}" parentId="{A32D579A-03F5-456F-BA00-67936BD401D0}">
     <text>Must support signal connection</text>
   </threadedComment>
-  <threadedComment ref="C140" dT="2022-01-14T13:33:08.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{36C2758C-D037-4478-BDED-0DD258CAD031}">
+  <threadedComment ref="C139" dT="2022-01-14T13:33:08.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{36C2758C-D037-4478-BDED-0DD258CAD031}">
     <text>No signal</text>
   </threadedComment>
-  <threadedComment ref="C141" dT="2022-01-14T13:33:16.93" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
+  <threadedComment ref="C140" dT="2022-01-14T13:33:16.93" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
     <text>No Signal - in-line</text>
   </threadedComment>
 </ThreadedComments>
@@ -2737,7 +2729,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C265"/>
+  <dimension ref="A1:C269"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
@@ -2761,396 +2753,396 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>702</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>374</v>
+      <c r="A3" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>391</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>697</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>29</v>
+      <c r="A4" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>352</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>353</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>698</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>344</v>
+      <c r="A5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>345</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>699</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>43</v>
+      <c r="A6" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>347</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>398</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>700</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>239</v>
+      <c r="A7" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>701</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>397</v>
+      <c r="A8" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>351</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>391</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>391</v>
+        <v>13</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>385</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>352</v>
+        <v>14</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>352</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>353</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>1</v>
+        <v>634</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1</v>
+        <v>634</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>347</v>
+        <v>635</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>347</v>
+        <v>635</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>348</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>349</v>
+        <v>636</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>350</v>
+        <v>636</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>351</v>
+        <v>637</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>355</v>
+        <v>637</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>15</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
-        <v>634</v>
+        <v>399</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>634</v>
+        <v>399</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>16</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
-        <v>635</v>
+        <v>53</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>635</v>
+        <v>53</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>16</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
-        <v>636</v>
+        <v>236</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>636</v>
+        <v>236</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>17</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>637</v>
+        <v>358</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>637</v>
+        <v>358</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>17</v>
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
-        <v>18</v>
+        <v>296</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>18</v>
+        <v>296</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>37</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>46</v>
+        <v>364</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>46</v>
+        <v>364</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>400</v>
+        <v>363</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>399</v>
+        <v>365</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>53</v>
+        <v>366</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>53</v>
+        <v>366</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>236</v>
+        <v>367</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>236</v>
+        <v>367</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>361</v>
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>358</v>
+        <v>369</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>369</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>296</v>
+        <v>370</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>370</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>297</v>
+        <v>359</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>369</v>
+        <v>384</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>384</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>370</v>
+        <v>386</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>386</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>359</v>
+        <v>390</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>82</v>
+        <v>407</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>354</v>
@@ -3158,923 +3150,923 @@
     </row>
     <row r="39" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>386</v>
+        <v>394</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>394</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>402</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
-        <v>404</v>
+        <v>638</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>404</v>
+        <v>638</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>403</v>
+        <v>441</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
-        <v>388</v>
+        <v>639</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>388</v>
+        <v>639</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>406</v>
+        <v>441</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
-        <v>405</v>
+        <v>640</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>405</v>
+        <v>640</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>407</v>
+        <v>441</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
-        <v>389</v>
+        <v>641</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>389</v>
+        <v>641</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>354</v>
+        <v>441</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>394</v>
+        <v>442</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>442</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>393</v>
+        <v>443</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>395</v>
+        <v>444</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>444</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>354</v>
+        <v>452</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
-        <v>638</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>638</v>
+        <v>445</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>445</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
-        <v>639</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>639</v>
+        <v>447</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>447</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
-        <v>640</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>640</v>
+        <v>449</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>449</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
-        <v>641</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>641</v>
+        <v>453</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>453</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>442</v>
+        <v>455</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>455</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="B54" s="14" t="s">
-        <v>447</v>
+      <c r="A54" t="s">
+        <v>703</v>
+      </c>
+      <c r="B54" t="s">
+        <v>703</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>449</v>
+        <v>707</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>704</v>
+      </c>
+      <c r="B55" t="s">
+        <v>704</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>453</v>
+        <v>708</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>705</v>
+      </c>
+      <c r="B56" t="s">
+        <v>705</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>455</v>
+        <v>709</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>706</v>
+      </c>
+      <c r="B57" t="s">
+        <v>706</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>457</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>461</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>238</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>459</v>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>462</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>3</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>238</v>
+        <v>47</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>3</v>
+        <v>91</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>47</v>
+        <v>147</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>89</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>146</v>
+        <v>242</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>145</v>
+        <v>343</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>45</v>
+        <v>362</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>468</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>242</v>
+        <v>470</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>93</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>343</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>469</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>6</v>
+        <v>471</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>362</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>93</v>
+        <v>149</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>471</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>95</v>
+        <v>473</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>151</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>94</v>
+        <v>150</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>472</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>149</v>
+        <v>474</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>153</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>474</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>153</v>
+        <v>476</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>475</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>155</v>
+        <v>477</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>159</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>478</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>161</v>
+        <v>480</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>165</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>163</v>
+        <v>70</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>480</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>165</v>
+        <v>482</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>166</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>482</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>166</v>
+        <v>484</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>170</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>484</v>
-      </c>
-      <c r="B83" s="8" t="s">
-        <v>170</v>
+        <v>486</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>172</v>
+        <v>56</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>173</v>
+        <v>58</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>175</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>58</v>
+        <v>313</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>488</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>243</v>
+        <v>490</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>19</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>312</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>489</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>246</v>
+        <v>491</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>59</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>313</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>59</v>
+        <v>245</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>57</v>
+        <v>314</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>49</v>
+        <v>244</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>48</v>
+        <v>315</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>493</v>
+        <v>691</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>245</v>
+        <v>60</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>314</v>
+        <v>375</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>494</v>
+      <c r="A93" s="16" t="s">
+        <v>702</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>315</v>
+        <v>376</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>691</v>
-      </c>
-      <c r="B94" s="10" t="s">
-        <v>60</v>
+        <v>495</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>496</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>50</v>
+        <v>497</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>51</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>368</v>
+        <v>52</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>241</v>
+        <v>64</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>63</v>
+        <v>252</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>64</v>
+        <v>316</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B104" s="10" t="s">
-        <v>251</v>
+        <v>65</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B105" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>506</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>68</v>
+        <v>507</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>253</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>67</v>
+        <v>319</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>507</v>
-      </c>
-      <c r="B107" s="7" t="s">
-        <v>253</v>
+        <v>508</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>319</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>509</v>
-      </c>
-      <c r="B109" s="8" t="s">
-        <v>179</v>
+        <v>510</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>182</v>
+        <v>368</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>184</v>
+        <v>254</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>368</v>
+        <v>321</v>
       </c>
     </row>
     <row r="113" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>254</v>
+        <v>185</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>321</v>
+        <v>186</v>
       </c>
     </row>
     <row r="114" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="115" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="116" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>516</v>
-      </c>
-      <c r="B116" s="7" t="s">
-        <v>191</v>
+        <v>517</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="117" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>517</v>
-      </c>
-      <c r="B117" s="8" t="s">
-        <v>192</v>
+        <v>518</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>194</v>
+        <v>255</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>193</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>320</v>
+        <v>195</v>
       </c>
     </row>
     <row r="120" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>520</v>
-      </c>
-      <c r="B120" s="7" t="s">
-        <v>197</v>
+        <v>521</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>198</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="121" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>521</v>
-      </c>
-      <c r="B121" s="8" t="s">
-        <v>198</v>
+        <v>522</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>199</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>196</v>
+        <v>368</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>368</v>
@@ -4082,1088 +4074,1088 @@
     </row>
     <row r="123" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>368</v>
+        <v>201</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>524</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>202</v>
+        <v>525</v>
+      </c>
+      <c r="B124" s="10" t="s">
+        <v>23</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>201</v>
+        <v>24</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>525</v>
-      </c>
-      <c r="B125" s="10" t="s">
-        <v>23</v>
+        <v>526</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>24</v>
+        <v>206</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>207</v>
+        <v>256</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>208</v>
+        <v>451</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>529</v>
-      </c>
-      <c r="B129" s="7" t="s">
-        <v>256</v>
+        <v>530</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>209</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>451</v>
+        <v>210</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>530</v>
-      </c>
-      <c r="B130" s="10" t="s">
-        <v>209</v>
+        <v>531</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>211</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>531</v>
-      </c>
-      <c r="B131" s="7" t="s">
-        <v>211</v>
+        <v>532</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>213</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B132" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B134" s="10" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>219</v>
+        <v>336</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B136" s="10" t="s">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>224</v>
+        <v>337</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B140" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>360</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>541</v>
-      </c>
-      <c r="B141" s="10" t="s">
-        <v>227</v>
+        <v>542</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>228</v>
+        <v>338</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>338</v>
+        <v>230</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>545</v>
-      </c>
-      <c r="B145" s="7" t="s">
-        <v>234</v>
+        <v>546</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>235</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>235</v>
+        <v>7</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>232</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>547</v>
-      </c>
-      <c r="B147" s="10" t="s">
-        <v>7</v>
+        <v>548</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>8</v>
+        <v>96</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>548</v>
-      </c>
-      <c r="B148" s="7" t="s">
-        <v>97</v>
+        <v>549</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>96</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>549</v>
-      </c>
-      <c r="B149" s="10" t="s">
-        <v>9</v>
+        <v>550</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>99</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>553</v>
-      </c>
-      <c r="B153" s="7" t="s">
-        <v>105</v>
+        <v>554</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>107</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>554</v>
-      </c>
-      <c r="B154" s="8" t="s">
-        <v>107</v>
+        <v>555</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>258</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>106</v>
+        <v>342</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>342</v>
+        <v>108</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>113</v>
+        <v>257</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>559</v>
-      </c>
-      <c r="B159" s="7" t="s">
-        <v>257</v>
+        <v>560</v>
+      </c>
+      <c r="B159" s="10" t="s">
+        <v>115</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>341</v>
+        <v>114</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>560</v>
-      </c>
-      <c r="B160" s="10" t="s">
-        <v>115</v>
+        <v>561</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>563</v>
-      </c>
-      <c r="B163" s="7" t="s">
-        <v>121</v>
+        <v>564</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>123</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B164" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B165" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>566</v>
-      </c>
-      <c r="B166" s="10" t="s">
-        <v>127</v>
+        <v>567</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>264</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>126</v>
+        <v>322</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>578</v>
-      </c>
-      <c r="B178" s="7" t="s">
-        <v>269</v>
+        <v>579</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>11</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>333</v>
+        <v>392</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>579</v>
-      </c>
-      <c r="B179" s="10" t="s">
-        <v>11</v>
+        <v>580</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>392</v>
+        <v>334</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>272</v>
+        <v>131</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>335</v>
+        <v>130</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>129</v>
+        <v>273</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>128</v>
+        <v>295</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>273</v>
+        <v>135</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>295</v>
+        <v>134</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>137</v>
+        <v>274</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>136</v>
+        <v>339</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>274</v>
+        <v>25</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>589</v>
-      </c>
-      <c r="B189" s="7" t="s">
-        <v>25</v>
+        <v>590</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>27</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>590</v>
+        <v>658</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>28</v>
+        <v>409</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>71</v>
+        <v>408</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>659</v>
-      </c>
-      <c r="B192" s="10" t="s">
-        <v>408</v>
+        <v>660</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>72</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>72</v>
+        <v>411</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="194" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>661</v>
-      </c>
-      <c r="B194" s="7" t="s">
-        <v>411</v>
+        <v>662</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>12</v>
+        <v>414</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>663</v>
-      </c>
-      <c r="B196" s="10" t="s">
-        <v>414</v>
+        <v>664</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>73</v>
+        <v>417</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>417</v>
+        <v>74</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>74</v>
+        <v>420</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>668</v>
+        <v>591</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>420</v>
+        <v>275</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>422</v>
+        <v>340</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>591</v>
-      </c>
-      <c r="B201" s="7" t="s">
-        <v>275</v>
+        <v>592</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>340</v>
+        <v>75</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B202" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>593</v>
-      </c>
-      <c r="B203" s="8" t="s">
-        <v>78</v>
+        <v>594</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>594</v>
-      </c>
-      <c r="B204" s="10" t="s">
-        <v>31</v>
+        <v>667</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>32</v>
+        <v>424</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>79</v>
+        <v>423</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>423</v>
+        <v>80</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>80</v>
+        <v>426</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>426</v>
+        <v>81</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>81</v>
+        <v>429</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>673</v>
-      </c>
-      <c r="B210" s="7" t="s">
-        <v>429</v>
+        <v>674</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>33</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>33</v>
+        <v>432</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>432</v>
+        <v>34</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>34</v>
+        <v>435</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>677</v>
-      </c>
-      <c r="B214" s="10" t="s">
-        <v>435</v>
+        <v>595</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>437</v>
+        <v>85</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>86</v>
+        <v>276</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>85</v>
+        <v>298</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>596</v>
+        <v>678</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>276</v>
+        <v>83</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>298</v>
+        <v>439</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>83</v>
+        <v>438</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>679</v>
-      </c>
-      <c r="B218" s="7" t="s">
-        <v>438</v>
+        <v>597</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>88</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>440</v>
+        <v>87</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B219" s="10" t="s">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>598</v>
-      </c>
-      <c r="B220" s="10" t="s">
-        <v>40</v>
+        <v>599</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>39</v>
+        <v>368</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>138</v>
+        <v>277</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>368</v>
@@ -5171,10 +5163,10 @@
     </row>
     <row r="222" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>277</v>
+        <v>139</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>368</v>
@@ -5182,10 +5174,10 @@
     </row>
     <row r="223" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>139</v>
+        <v>279</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>368</v>
@@ -5193,10 +5185,10 @@
     </row>
     <row r="224" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>368</v>
@@ -5204,10 +5196,10 @@
     </row>
     <row r="225" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>278</v>
+        <v>140</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>368</v>
@@ -5215,32 +5207,32 @@
     </row>
     <row r="226" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>368</v>
+        <v>643</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>605</v>
+        <v>692</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>280</v>
+        <v>143</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>643</v>
+        <v>141</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>143</v>
+        <v>373</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>141</v>
@@ -5248,663 +5240,707 @@
     </row>
     <row r="229" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>693</v>
+        <v>606</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>373</v>
+        <v>144</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>606</v>
-      </c>
-      <c r="B230" s="7" t="s">
-        <v>144</v>
+        <v>607</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>35</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>142</v>
+        <v>36</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>607</v>
-      </c>
-      <c r="B231" s="10" t="s">
-        <v>35</v>
+        <v>608</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>36</v>
+        <v>310</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B233" s="7" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B234" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>613</v>
-      </c>
-      <c r="B237" s="7" t="s">
-        <v>294</v>
+        <v>614</v>
+      </c>
+      <c r="B237" s="10" t="s">
+        <v>288</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>614</v>
-      </c>
-      <c r="B238" s="10" t="s">
-        <v>288</v>
+        <v>615</v>
+      </c>
+      <c r="B238" s="7" t="s">
+        <v>287</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="239" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B239" s="7" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
     </row>
     <row r="240" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B240" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>300</v>
+        <v>240</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B242" s="7" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B243" s="7" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>620</v>
-      </c>
-      <c r="B244" s="7" t="s">
-        <v>286</v>
+        <v>621</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>289</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>621</v>
-      </c>
-      <c r="B245" s="10" t="s">
-        <v>289</v>
+        <v>622</v>
+      </c>
+      <c r="B245" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>622</v>
-      </c>
-      <c r="B246" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A246" s="15" t="s">
+        <v>680</v>
+      </c>
+      <c r="B246" s="15" t="s">
+        <v>696</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="15" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B247" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="248" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="15" t="s">
-        <v>681</v>
+        <v>623</v>
       </c>
       <c r="B248" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="15" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B249" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="15" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B250" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="251" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="15" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B251" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>690</v>
+        <v>642</v>
       </c>
     </row>
     <row r="252" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="15" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B252" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="15" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B253" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C253" s="3" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="254" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="15" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B254" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="255" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="15" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B255" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C255" s="3" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="15" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B256" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="15" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B257" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C257" s="3" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="258" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="15" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B258" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>649</v>
+        <v>28</v>
       </c>
     </row>
     <row r="259" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="15" t="s">
-        <v>633</v>
+        <v>652</v>
       </c>
       <c r="B259" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>28</v>
+        <v>684</v>
       </c>
     </row>
     <row r="260" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="15" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B260" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="261" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="15" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B261" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="262" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="15" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B262" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="263" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="15" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="B263" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C263" s="3" t="s">
-        <v>687</v>
+        <v>656</v>
       </c>
     </row>
     <row r="264" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="15" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B264" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A265" s="15" t="s">
-        <v>651</v>
-      </c>
-      <c r="B265" s="15" t="s">
-        <v>696</v>
+        <v>657</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="16" t="s">
+        <v>697</v>
+      </c>
+      <c r="B265" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>657</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="16" t="s">
+        <v>698</v>
+      </c>
+      <c r="B266" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C266" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="16" t="s">
+        <v>699</v>
+      </c>
+      <c r="B267" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C267" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="16" t="s">
+        <v>700</v>
+      </c>
+      <c r="B268" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="C268" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="16" t="s">
+        <v>701</v>
+      </c>
+      <c r="B269" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="C269" s="3" t="s">
+        <v>397</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C265" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C265">
-      <sortCondition sortBy="cellColor" ref="A2:A265" dxfId="1"/>
+  <autoFilter ref="A2:C264" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C269">
+      <sortCondition ref="A2:A264"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+  <conditionalFormatting sqref="A270:A1048576 A1:A53 A58:A264">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B61" r:id="rId1" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA001A_Detail.svg" xr:uid="{17ADBAC8-7138-41E8-BDFB-2ED015B2E3B6}"/>
-    <hyperlink ref="B68" r:id="rId2" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA008A_Detail.svg" xr:uid="{3A518947-B6F8-4C42-81D7-7894D9144A33}"/>
-    <hyperlink ref="B147" r:id="rId3" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP001A_Detail.svg" xr:uid="{761B47C6-804C-4528-8497-BBE932BB2C49}"/>
-    <hyperlink ref="B149" r:id="rId4" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP003A_Detail.svg" xr:uid="{EC8BC23F-0549-4B47-A475-38BE73BE9CEE}"/>
-    <hyperlink ref="B203" r:id="rId5" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV012A_Detail.svg" xr:uid="{5A391EDE-1D55-4CFD-9901-A29E0591193B}"/>
-    <hyperlink ref="B15" r:id="rId6" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0006_Detail.svg" xr:uid="{975176F7-F497-4824-8376-23C959379C06}"/>
-    <hyperlink ref="B16" r:id="rId7" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0007_Detail.svg" xr:uid="{5FA11009-5EE8-4528-A809-14E1B1FB1C10}"/>
-    <hyperlink ref="B17" r:id="rId8" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0008_Detail.svg" xr:uid="{7720A7D8-16EA-4565-A935-C37587E784A7}"/>
-    <hyperlink ref="B21" r:id="rId9" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0010_Detail.svg" xr:uid="{8BCC9369-A109-4DC7-B34A-9DE621C69D33}"/>
-    <hyperlink ref="B90" r:id="rId10" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE002A_Detail.svg" xr:uid="{BD7A7DCC-BFC7-48AF-B865-B8368E55F2E6}"/>
-    <hyperlink ref="B115" r:id="rId11" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE027A_Detail.svg" xr:uid="{4ECEB4FA-D039-495A-8F42-FFC9B443FDC3}"/>
-    <hyperlink ref="B140" r:id="rId12" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF009A_Detail.svg" xr:uid="{907022FE-3A1A-45BE-8FF2-AC230B1DD29B}"/>
-    <hyperlink ref="B189" r:id="rId13" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV001A_Detail.svg" xr:uid="{A8069CA7-B440-43C6-B571-35216079CADD}"/>
-    <hyperlink ref="B194" r:id="rId14" xr:uid="{7398F614-893C-4326-BA65-62E7CEF8B17B}"/>
-    <hyperlink ref="B208" r:id="rId15" xr:uid="{86D99A6B-DD65-4D76-9524-599D4EAB2E02}"/>
-    <hyperlink ref="B211" r:id="rId16" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV018A_Detail.svg" xr:uid="{3E8578A0-8239-405C-B417-86D7CEF2DB87}"/>
-    <hyperlink ref="B215" r:id="rId17" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV021A_Detail.svg" xr:uid="{27E00768-DA9C-4DAF-98AA-2381306E4A13}"/>
-    <hyperlink ref="B231" r:id="rId18" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ013A_Detail.svg" xr:uid="{9F7EE259-EBE5-4578-86F7-E5EF694FDA65}"/>
-    <hyperlink ref="B226" r:id="rId19" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ009A_Detail.svg" xr:uid="{30065FD0-FD2C-4BF8-A534-106ECA4A05E6}"/>
-    <hyperlink ref="B246" r:id="rId20" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/STPL008_Detail.svg" xr:uid="{F132DB26-A2BF-4161-B712-08766D64B599}"/>
-    <hyperlink ref="B6" r:id="rId21" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{21C87E9B-CBD0-4B81-A925-45F9B4FD8864}"/>
-    <hyperlink ref="B66" r:id="rId22" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA006A_Detail.svg" xr:uid="{C46298F6-C022-42A8-88EB-27031801D32E}"/>
-    <hyperlink ref="B23" r:id="rId23" xr:uid="{045D2E44-4A59-4C52-AA81-3156413AFAFC}"/>
-    <hyperlink ref="B63" r:id="rId24" display="PA002A" xr:uid="{6BAE8F82-BC2B-4427-9773-0A3AE429BDE1}"/>
-    <hyperlink ref="B91" r:id="rId25" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE003A_Detail.svg" xr:uid="{4004AC67-08BF-4573-A91C-196B852BE782}"/>
-    <hyperlink ref="B96" r:id="rId26" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE008A_Detail.svg" xr:uid="{907142FB-A61F-493E-ADCC-40C2E404D844}"/>
-    <hyperlink ref="B97" r:id="rId27" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE009A_Detail.svg" xr:uid="{42D7E312-902B-45B8-B2E6-478D821615A1}"/>
-    <hyperlink ref="B98" r:id="rId28" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE010A_Detail.svg" xr:uid="{12CE6EBF-4CA8-44DF-B6FC-040DFB92731D}"/>
-    <hyperlink ref="B86" r:id="rId29" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD018A_Detail.svg" xr:uid="{D9AD65D0-256C-4FDA-AB63-641CAEF296B8}"/>
-    <hyperlink ref="B89" r:id="rId30" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE001A_Detail.svg" xr:uid="{B5B862E7-DBAB-44C9-B7B4-21949ADAF9C9}"/>
-    <hyperlink ref="B94" r:id="rId31" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE006A_Detail.svg" xr:uid="{AA6401E6-CD51-4574-ABA6-C7BB3663F989}"/>
-    <hyperlink ref="B95" r:id="rId32" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE007A_Detail.svg" xr:uid="{B35184E7-56AF-48CA-8CC6-9A61FB055044}"/>
-    <hyperlink ref="B99" r:id="rId33" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE011A_Detail.svg" xr:uid="{52A5B7C0-AD9C-472F-899E-86CD63EFB3AA}"/>
-    <hyperlink ref="B100" r:id="rId34" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE012A_Detail.svg" xr:uid="{C3016BE0-26B5-41E3-A7DB-D7C53F62C108}"/>
-    <hyperlink ref="B101" r:id="rId35" display="PE012A" xr:uid="{FFB4E872-E736-41AC-8F80-41BB1E8C57A6}"/>
-    <hyperlink ref="B105" r:id="rId36" display="PE013A" xr:uid="{69F4C8E5-12AD-463A-8F4A-4719422312A8}"/>
-    <hyperlink ref="B80" r:id="rId37" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD012A_Detail.svg" xr:uid="{F25BE2C8-8813-4940-8329-63BBA6D15B89}"/>
-    <hyperlink ref="B190" r:id="rId38" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV002A_Detail.svg" xr:uid="{EB3DD888-4A6F-42F8-AD39-FAC973963B51}"/>
-    <hyperlink ref="B192" r:id="rId39" xr:uid="{C8A2ABD8-A0CE-4FB6-BD75-7694D40F91BE}"/>
-    <hyperlink ref="B196" r:id="rId40" xr:uid="{10BB9991-94D9-43E5-9038-0AD1029C8456}"/>
-    <hyperlink ref="B198" r:id="rId41" xr:uid="{E92459C1-EFAE-4D41-A9A2-B6CBF8031302}"/>
-    <hyperlink ref="B200" r:id="rId42" xr:uid="{FB94CBE5-59E0-4451-A8F5-AF4BCA7E6242}"/>
-    <hyperlink ref="B202" r:id="rId43" display="PV008A" xr:uid="{7C2F94E7-1DC8-40D5-9F4C-AA07CD1D7F60}"/>
-    <hyperlink ref="B204" r:id="rId44" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV013A_Detail.svg" xr:uid="{D981260A-8BAC-4F90-8B22-F4387848B90B}"/>
-    <hyperlink ref="B206" r:id="rId45" xr:uid="{7AB8E356-44B8-49E6-B29B-395AA92E87A4}"/>
-    <hyperlink ref="B210" r:id="rId46" xr:uid="{27C7E718-E4EC-4B45-A105-4219CB86145A}"/>
-    <hyperlink ref="B218" r:id="rId47" xr:uid="{22BEA91F-E09D-41B1-979E-65B6D728D85F}"/>
-    <hyperlink ref="B214" r:id="rId48" xr:uid="{64580D0C-1766-4DB3-AF77-41B1C3F4FBCB}"/>
-    <hyperlink ref="B219" r:id="rId49" display="PZ001A" xr:uid="{6198CEDF-7056-49B0-8C8C-0CE4F43ED518}"/>
-    <hyperlink ref="B62" r:id="rId50" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA002A_Detail.svg" xr:uid="{0302EB7E-2FF3-47CA-B5A8-8E3511F52559}"/>
-    <hyperlink ref="B75" r:id="rId51" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD007A_Detail.svg" xr:uid="{55939466-04EF-445D-B8C5-29A1F47BFBEC}"/>
-    <hyperlink ref="B69" r:id="rId52" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD001A_Detail.svg" xr:uid="{3C931296-EFA6-4A17-ABBE-BA3CEEBAE7CD}"/>
-    <hyperlink ref="B148" r:id="rId53" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP002A_Detail.svg" xr:uid="{7B04BB8C-B4F8-4443-9951-FF9779382F5E}"/>
-    <hyperlink ref="B154" r:id="rId54" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP008A_Detail.svg" xr:uid="{B8AA4B11-0A29-4052-8E9D-3BF8D275C0C3}"/>
-    <hyperlink ref="B150" r:id="rId55" display="PP003A" xr:uid="{A0025AF4-1428-4206-B942-D976CF2EABF6}"/>
-    <hyperlink ref="B151" r:id="rId56" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP005A_Detail.svg" xr:uid="{A6177C8F-61D8-4517-924D-AC098541874E}"/>
-    <hyperlink ref="B152" r:id="rId57" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP006A_Detail.svg" xr:uid="{CCC65F5C-1709-40F0-BC1E-5E22B9EE2E8B}"/>
-    <hyperlink ref="B153" r:id="rId58" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP007A_Detail.svg" xr:uid="{CF9DC830-F3E2-46F7-BB6E-F40EE3588C98}"/>
-    <hyperlink ref="B166" r:id="rId59" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS004A_Detail.svg" xr:uid="{9053D430-E6CE-479A-9C3A-E85BE51DDA2D}"/>
-    <hyperlink ref="B156" r:id="rId60" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP010A_Detail.svg" xr:uid="{0970F33B-0575-4123-83FA-27B45C94A4A2}"/>
-    <hyperlink ref="B157" r:id="rId61" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP011A_Detail.svg" xr:uid="{0EA32245-04D0-41E6-991A-61C23D6D04D5}"/>
-    <hyperlink ref="B158" r:id="rId62" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP012A_Detail.svg" xr:uid="{FBE8CA96-6772-460A-8C03-4C086593A5CE}"/>
-    <hyperlink ref="B160" r:id="rId63" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP014A_Detail.svg" xr:uid="{9377286C-CA88-49CA-8DB6-8B4673069711}"/>
-    <hyperlink ref="B161" r:id="rId64" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP015A_Detail.svg" xr:uid="{4CF07C91-9442-4F6E-8428-DC8B0ABD88EC}"/>
-    <hyperlink ref="B162" r:id="rId65" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP016A_Detail.svg" xr:uid="{95445AC5-539C-433D-929D-1B79509AB314}"/>
-    <hyperlink ref="B163" r:id="rId66" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP017A_Detail.svg" xr:uid="{F1EAA06B-6B10-469E-BFA8-DBE8DA0E67EC}"/>
-    <hyperlink ref="B164" r:id="rId67" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS001A_Detail.svg" xr:uid="{53C8229D-2E3F-405D-A9C8-3F6FE5E0EFCC}"/>
-    <hyperlink ref="B179" r:id="rId68" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT002A_Detail.svg" xr:uid="{8ED0FE06-63C6-4619-8AFA-C21DEA756B38}"/>
-    <hyperlink ref="B183" r:id="rId69" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT006A_Detail.svg" xr:uid="{DE7E75F2-6055-421D-A22C-888A6804396D}"/>
-    <hyperlink ref="B182" r:id="rId70" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT005A_Detail.svg" xr:uid="{95A726E8-8601-4CDB-BBED-77B49873F4C0}"/>
-    <hyperlink ref="B184" r:id="rId71" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT007A_Detail.svg" xr:uid="{B6131D2E-4752-4739-997C-D3CBF679F940}"/>
-    <hyperlink ref="B186" r:id="rId72" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT009A_Detail.svg" xr:uid="{D06AD6E5-7BA2-492F-8D44-8B09ADBF6122}"/>
-    <hyperlink ref="B187" r:id="rId73" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT010A_Detail.svg" xr:uid="{52343A83-46C2-4D49-BFE5-DA8717644CD2}"/>
-    <hyperlink ref="B220" r:id="rId74" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ003A_Detail.svg" xr:uid="{335D3D40-BE42-44FE-929A-0F3D3F26D262}"/>
-    <hyperlink ref="B221" r:id="rId75" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ004A_Detail.svg" xr:uid="{45517A4C-49CF-4A14-BE92-F3323139DBA8}"/>
-    <hyperlink ref="B223" r:id="rId76" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ006A_Detail.svg" xr:uid="{92F8D01F-B6E2-40C7-970D-7EAFB7872F29}"/>
-    <hyperlink ref="B230" r:id="rId77" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ012A_Detail.svg" xr:uid="{F5F1079A-1346-46A4-BF70-9025442AFB80}"/>
-    <hyperlink ref="B228" r:id="rId78" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ011A_Detail.svg" xr:uid="{BDA2ADBE-AC37-448F-9C41-243FB16B0996}"/>
-    <hyperlink ref="B65" r:id="rId79" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA005A_Detail.svg" xr:uid="{BA3A7E34-7D5B-4A78-BB78-1727C668EB8F}"/>
-    <hyperlink ref="B64" r:id="rId80" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA004A_Detail.svg" xr:uid="{39481051-1B60-44BF-8211-0D5C1980FD4B}"/>
-    <hyperlink ref="B70" r:id="rId81" display="PD001A" xr:uid="{3969656E-C88B-42A9-9C3B-B8275B159B5B}"/>
-    <hyperlink ref="B71" r:id="rId82" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD003A_Detail.svg" xr:uid="{86AB2467-10FE-4C5F-883D-EDA03495CD55}"/>
-    <hyperlink ref="B72" r:id="rId83" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD004A_Detail.svg" xr:uid="{A3F7C2AC-969E-4A1D-87C5-6BFE5671E4DC}"/>
-    <hyperlink ref="B73" r:id="rId84" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD005A_Detail.svg" xr:uid="{6DFFDA9D-5A28-4CC7-8DE9-876E2360BFEE}"/>
-    <hyperlink ref="B74" r:id="rId85" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD006A_Detail.svg" xr:uid="{3BB6ACEF-9AAF-4C4D-9A87-FCF6EA0F91BD}"/>
-    <hyperlink ref="B85" r:id="rId86" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD017A_Detail.svg" xr:uid="{28D1C6B0-DDE6-442D-9F10-91D27566478A}"/>
-    <hyperlink ref="B76" r:id="rId87" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD008A_Detail.svg" xr:uid="{AB7B0FCA-5804-4486-8380-FBA9F83DEE66}"/>
-    <hyperlink ref="B77" r:id="rId88" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD009A_Detail.svg" xr:uid="{9D870461-08B6-4714-8A00-09714564A8DF}"/>
-    <hyperlink ref="B78" r:id="rId89" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD010A_Detail.svg" xr:uid="{BB4A6A70-CBD2-4C62-B476-1DB99A7B8C9C}"/>
-    <hyperlink ref="B79" r:id="rId90" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD011A_Detail.svg" xr:uid="{5A9D789E-5B6D-46CC-883A-8FE28112F14B}"/>
-    <hyperlink ref="B81" r:id="rId91" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD013A_Detail.svg" xr:uid="{6394051E-0C5B-4871-B946-B73195930CB1}"/>
-    <hyperlink ref="B82" r:id="rId92" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD014A_Detail.svg" xr:uid="{89E87861-2175-4BEE-A5F9-33D47934E630}"/>
-    <hyperlink ref="B83" r:id="rId93" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD015A_Detail.svg" xr:uid="{C0901CAD-B396-4045-9DFB-94C087A6E9C7}"/>
-    <hyperlink ref="B84" r:id="rId94" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD016A_Detail.svg" xr:uid="{FE18571B-26F6-45A2-AE52-5E17B76EC7F3}"/>
-    <hyperlink ref="B106" r:id="rId95" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE018A_Detail.svg" xr:uid="{6D3B7973-3EAF-4809-A3A6-949465067CBC}"/>
-    <hyperlink ref="B108" r:id="rId96" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE020A_Detail.svg" xr:uid="{39CB98B6-29C9-4B55-BB4D-C050812B9145}"/>
-    <hyperlink ref="B109" r:id="rId97" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE021A_Detail.svg" xr:uid="{50AE8AE5-DEF4-4FC6-8682-258DF3904CD7}"/>
-    <hyperlink ref="B110" r:id="rId98" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE022A_Detail.svg" xr:uid="{93F60579-BA2A-4EDC-B883-017EBA23D13F}"/>
-    <hyperlink ref="B111" r:id="rId99" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE023A_Detail.svg" xr:uid="{2F7FC80D-3FA4-4BE4-A403-E017F265775F}"/>
-    <hyperlink ref="B112" r:id="rId100" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE024A_Detail.svg" xr:uid="{212E32CA-E31F-4B52-AC82-844C20339614}"/>
-    <hyperlink ref="B114" r:id="rId101" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE026A_Detail.svg" xr:uid="{9078864B-22E7-4236-BA73-76CA46B86A31}"/>
-    <hyperlink ref="B116" r:id="rId102" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE028A_Detail.svg" xr:uid="{F436B4D7-3AA5-4126-BBD2-BACE69A4A4E0}"/>
-    <hyperlink ref="B117" r:id="rId103" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE029A_Detail.svg" xr:uid="{C7A515AB-6C11-4EA4-85E4-5091485DAA17}"/>
-    <hyperlink ref="B121" r:id="rId104" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE033A_Detail.svg" xr:uid="{34E7B3BE-E531-4018-BB45-6CCB618C0FBB}"/>
-    <hyperlink ref="B118" r:id="rId105" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE030A_Detail.svg" xr:uid="{1F74D129-65A3-4B07-BF1F-5193476A8A04}"/>
-    <hyperlink ref="B120" r:id="rId106" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE032A_Detail.svg" xr:uid="{8A8FA28E-6634-4E0D-A29F-388C878E8DB9}"/>
-    <hyperlink ref="B122" r:id="rId107" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE034A_Detail.svg" xr:uid="{6C65D9E8-788A-4EFB-B896-E4E82EAA3CB0}"/>
-    <hyperlink ref="B124" r:id="rId108" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE036A_Detail.svg" xr:uid="{6A654C5A-571F-47D9-9387-6F62409DC1B7}"/>
-    <hyperlink ref="B123" r:id="rId109" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE035A_Detail.svg" xr:uid="{8BF957E4-037D-4E36-9BCA-83538FEE7EAF}"/>
-    <hyperlink ref="B125" r:id="rId110" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE037A_Detail.svg" xr:uid="{7931F92F-DB33-458A-84AB-EEE6E7217AAA}"/>
-    <hyperlink ref="B126" r:id="rId111" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE038A_Detail.svg" xr:uid="{F73D9E2D-2341-4000-BD06-BEF7EA513332}"/>
-    <hyperlink ref="B127" r:id="rId112" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE039A_Detail.svg" xr:uid="{FB0AAC16-DEA9-41D3-8765-ACE272916988}"/>
-    <hyperlink ref="B128" r:id="rId113" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE040A_Detail.svg" xr:uid="{9D15EFC4-F96D-4011-83A8-7E4FB0A02FD4}"/>
-    <hyperlink ref="B130" r:id="rId114" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE042A_Detail.svg" xr:uid="{4DC635F0-1E08-4047-98E2-D16EA3B8D3B6}"/>
-    <hyperlink ref="B131" r:id="rId115" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE043A_Detail.svg" xr:uid="{7A91C884-B181-4AC9-8872-A5B4FEC2FA44}"/>
-    <hyperlink ref="B132" r:id="rId116" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF001A_Detail.svg" xr:uid="{226AE98E-A3DA-4D82-91A1-7CFDF93A8DE9}"/>
-    <hyperlink ref="B133" r:id="rId117" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF002A_Detail.svg" xr:uid="{467E946A-F396-4E22-A95C-421F6CE0BC8B}"/>
-    <hyperlink ref="B134" r:id="rId118" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF003A_Detail.svg" xr:uid="{55C30B46-FD0C-4081-A7D2-D7A7DFE70B52}"/>
-    <hyperlink ref="B135" r:id="rId119" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF004A_Detail.svg" xr:uid="{1127E743-3E80-461C-9E2E-11276A527952}"/>
-    <hyperlink ref="B137" r:id="rId120" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF006A_Detail.svg" xr:uid="{C896FA40-2C0C-4F45-ABB7-4A0598EF464F}"/>
-    <hyperlink ref="B138" r:id="rId121" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF007A_Detail.svg" xr:uid="{B63E94F9-6FBE-473E-BB35-4B04D8BA205A}"/>
-    <hyperlink ref="B146" r:id="rId122" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF015A_Detail.svg" xr:uid="{D0C9703A-C515-442F-88BF-811B68EF3142}"/>
-    <hyperlink ref="B141" r:id="rId123" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF010A_Detail.svg" xr:uid="{8776960A-3D62-49BB-964C-0A029249E4ED}"/>
-    <hyperlink ref="B142" r:id="rId124" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF011A_Detail.svg" xr:uid="{52198015-5884-4164-AE13-C31DC940BF9F}"/>
-    <hyperlink ref="B144" r:id="rId125" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF013A_Detail.svg" xr:uid="{1676627D-C9A1-412D-A74B-FEC1DD6ADAFC}"/>
-    <hyperlink ref="B145" r:id="rId126" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF014A_Detail.svg" xr:uid="{0AE6782A-A294-4988-A1A8-09100E831215}"/>
-    <hyperlink ref="B25" r:id="rId127" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0014_Detail.svg" xr:uid="{1F3765D3-EFE7-463A-B085-1DE36D0AE049}"/>
-    <hyperlink ref="B60" r:id="rId128" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/LZ009A_Detail.svg" xr:uid="{964B3FA4-6BEE-49FA-A53D-C16D25DADF11}"/>
-    <hyperlink ref="B24" r:id="rId129" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0013_Detail.svg" xr:uid="{5203DA34-E147-4733-BD2B-596D44AF2F0D}"/>
-    <hyperlink ref="B165" r:id="rId130" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS003A_Detail.svg" xr:uid="{D3E46F2B-78B9-41FF-AD13-E05C1AAC94AA}"/>
-    <hyperlink ref="B185" r:id="rId131" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT008A_Detail.svg" xr:uid="{A09F2ECE-A3F2-485F-89B3-392B6CCF3E0F}"/>
-    <hyperlink ref="B27" r:id="rId132" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0016_Detail.svg" xr:uid="{D78471C4-ED27-412C-838A-FDFC562E1EC3}"/>
-    <hyperlink ref="B216" r:id="rId133" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV022A_Detail.svg" xr:uid="{7F2ADD73-6C39-4114-8228-83338A629639}"/>
-    <hyperlink ref="B242" r:id="rId134" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ024A_Detail.svg" xr:uid="{D7DC9173-D444-4E60-B47B-45295B162EA3}"/>
-    <hyperlink ref="B20" r:id="rId135" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0009_Detail.svg" xr:uid="{CF5F7511-92B4-421B-B7C3-594BAC34117C}"/>
-    <hyperlink ref="B234" r:id="rId136" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ016A_Detail.svg" xr:uid="{223CCECC-C661-4D77-99FB-373C2C3EB9FD}"/>
-    <hyperlink ref="B240" r:id="rId137" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ022A_Detail.svg" xr:uid="{4E646DA6-844E-461F-A30F-E45D4A6BAEE0}"/>
-    <hyperlink ref="B235" r:id="rId138" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ017A_Detail.svg" xr:uid="{4AF15DA4-056F-4E39-B57F-D527D7C96314}"/>
-    <hyperlink ref="B236" r:id="rId139" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ018A_Detail.svg" xr:uid="{6A08BE2B-2F4A-40D0-87F1-2BF30F7E5204}"/>
-    <hyperlink ref="B237" r:id="rId140" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ019A_Detail.svg" xr:uid="{6C2DB1B2-D14C-41F7-85E9-0AD5CD60A40D}"/>
-    <hyperlink ref="B238" r:id="rId141" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ020A_Detail.svg" xr:uid="{3E5BB973-5805-404F-A772-22A577F5EA77}"/>
-    <hyperlink ref="B239" r:id="rId142" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ021A_Detail.svg" xr:uid="{96375F5D-1843-4B64-9FEB-59352041AF1C}"/>
-    <hyperlink ref="B241" r:id="rId143" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ023A_Detail.svg" xr:uid="{D811FB39-FE0C-4790-A865-54A17F50CA6D}"/>
-    <hyperlink ref="B243" r:id="rId144" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ025A_Detail.svg" xr:uid="{60163B1A-1792-49FF-9790-F2BF94ABFA4A}"/>
-    <hyperlink ref="B244" r:id="rId145" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ026A_Detail.svg" xr:uid="{0AAE0EB6-ECBB-4198-AA26-C684A0AECB97}"/>
-    <hyperlink ref="B245" r:id="rId146" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ027A_Detail.svg" xr:uid="{824407FA-7B30-4D5E-93CE-ED8122F65FFE}"/>
-    <hyperlink ref="B232" r:id="rId147" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ014A_Detail.svg" xr:uid="{F99B97AB-F1A6-4427-ABEB-25E3CC85B5DC}"/>
-    <hyperlink ref="B233" r:id="rId148" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ015A_Detail.svg" xr:uid="{12DA03AC-3D4B-49FC-B523-CC4091EF5CF4}"/>
-    <hyperlink ref="B87" r:id="rId149" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD019A_Detail.svg" xr:uid="{1FEADDE7-E396-46B6-9322-03EDCA28A99A}"/>
-    <hyperlink ref="B88" r:id="rId150" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD020A_Detail.svg" xr:uid="{1987EC41-B7CC-4E23-B295-01B52113BE11}"/>
-    <hyperlink ref="B92" r:id="rId151" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE004A_Detail.svg" xr:uid="{22A02656-E11C-40BA-93D1-A3BA2FBE802C}"/>
-    <hyperlink ref="B93" r:id="rId152" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE005A_Detail.svg" xr:uid="{D679D4B8-1D0A-498C-B0C6-64751CDFD8A9}"/>
-    <hyperlink ref="B67" r:id="rId153" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA007A_Detail.svg" xr:uid="{30DD321A-DB3E-4139-B7C6-5B72D5F41E50}"/>
-    <hyperlink ref="B102" r:id="rId154" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE014A_Detail.svg" xr:uid="{2B620BE4-F09B-478A-BDA6-76461B53049C}"/>
-    <hyperlink ref="B103" r:id="rId155" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE015A_Detail.svg" xr:uid="{57F06AB3-A2D4-42BD-8A97-785E7A9DEED3}"/>
-    <hyperlink ref="B104" r:id="rId156" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE016A_Detail.svg" xr:uid="{7714B096-A821-46A9-B38E-478AC0F60DFA}"/>
-    <hyperlink ref="B107" r:id="rId157" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE019A_Detail.svg" xr:uid="{77B288AB-A3B1-4E08-ABAC-36CEFD1274DD}"/>
-    <hyperlink ref="B119" r:id="rId158" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE031A_Detail.svg" xr:uid="{BD8A7598-0DFE-4ACB-ABFF-A23EE4147A0C}"/>
-    <hyperlink ref="B113" r:id="rId159" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE025A_Detail.svg" xr:uid="{111CB70F-38F3-4FA2-9171-155C1FE97029}"/>
-    <hyperlink ref="B167" r:id="rId160" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS005A_Detail.svg" xr:uid="{8BD8F9B2-845D-4212-B985-91349C8461AA}"/>
-    <hyperlink ref="B168" r:id="rId161" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS006A_Detail.svg" xr:uid="{616ABAAF-2406-46A1-9490-096325FB538C}"/>
-    <hyperlink ref="B169" r:id="rId162" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS007A_Detail.svg" xr:uid="{C158EBE4-9C88-4608-8165-95D1C5969FE5}"/>
-    <hyperlink ref="B170" r:id="rId163" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS008A_Detail.svg" xr:uid="{8B850863-4DBF-4261-A871-9900D82512A0}"/>
-    <hyperlink ref="B171" r:id="rId164" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS009A_Detail.svg" xr:uid="{EAA92938-1022-4B27-8A45-FC38DB3D12AB}"/>
-    <hyperlink ref="B172" r:id="rId165" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS010A_Detail.svg" xr:uid="{DE97D73F-147C-4EDC-A7D8-86145F37E03C}"/>
-    <hyperlink ref="B173" r:id="rId166" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS011A_Detail.svg" xr:uid="{006F66EF-728F-49E8-A5FE-751016748DAC}"/>
-    <hyperlink ref="B174" r:id="rId167" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS012A_Detail.svg" xr:uid="{8F448560-0B77-4837-B70F-0B9A88CD3C63}"/>
-    <hyperlink ref="B175" r:id="rId168" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS013A_Detail.svg" xr:uid="{0221699E-5F49-4DF1-B0AB-C4E5888F2A80}"/>
-    <hyperlink ref="B176" r:id="rId169" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS014A_Detail.svg" xr:uid="{C05394F3-DC5D-41A9-A414-4B0B18AAED5C}"/>
-    <hyperlink ref="B177" r:id="rId170" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS015A_Detail.svg" xr:uid="{C2CC68D8-9E61-4D94-BCC1-7A22522BAC81}"/>
-    <hyperlink ref="B178" r:id="rId171" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS016A_Detail.svg" xr:uid="{47A88BDB-E04A-43F6-992D-C76510B510EF}"/>
-    <hyperlink ref="B180" r:id="rId172" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT003A_Detail.svg" xr:uid="{7CF97CF8-3E1A-4A9E-ABE2-3A579CF8676B}"/>
-    <hyperlink ref="B181" r:id="rId173" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT004A_Detail.svg" xr:uid="{75DC4A11-DAE8-4DC6-A6D0-7E3E61B719CC}"/>
-    <hyperlink ref="B129" r:id="rId174" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE041A_Detail.svg" xr:uid="{EF9B4A93-EF2D-4E76-A4CC-16163CED7262}"/>
-    <hyperlink ref="B136" r:id="rId175" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF005A_Detail.svg" xr:uid="{3383514A-9E6D-45A7-AD65-0B18E1BAAD22}"/>
-    <hyperlink ref="B139" r:id="rId176" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF008A_Detail.svg" xr:uid="{73E8300F-62F2-4049-934B-015EDBEED287}"/>
-    <hyperlink ref="B143" r:id="rId177" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF012A_Detail.svg" xr:uid="{E9B3CC0D-A34B-4C8A-B89B-B330DAD71021}"/>
-    <hyperlink ref="B155" r:id="rId178" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP009A_Detail.svg" xr:uid="{0A13328E-0285-44BD-B9CF-A05D28AD6EAD}"/>
-    <hyperlink ref="B188" r:id="rId179" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT011A_Detail.svg" xr:uid="{E88B48B0-2B27-4600-8526-87B72CED5EC1}"/>
-    <hyperlink ref="B201" r:id="rId180" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV009A_Detail.svg" xr:uid="{25FF9022-3620-4A11-BF03-2A03200DD6CC}"/>
-    <hyperlink ref="B222" r:id="rId181" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ005A_Detail.svg" xr:uid="{92F69C2E-BC95-4B0C-9D0B-5D880C9FFE1C}"/>
-    <hyperlink ref="B224" r:id="rId182" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ007A_Detail.svg" xr:uid="{D96D22DE-45BD-4E25-A768-C8AAD05A8872}"/>
-    <hyperlink ref="B225" r:id="rId183" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ008A_Detail.svg" xr:uid="{14ADB638-7CCB-453F-BBA2-E88CDF197096}"/>
-    <hyperlink ref="B227" r:id="rId184" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ010A_Detail.svg" xr:uid="{7FE7B2D2-712E-48EB-BF5E-8AF8801ACB71}"/>
-    <hyperlink ref="B159" r:id="rId185" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP013A_Detail.svg" xr:uid="{81BF01ED-214F-4F7B-B7B6-1F88A3E341A7}"/>
-    <hyperlink ref="B5" r:id="rId186" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM005B_Detail.svg" xr:uid="{C4A57621-4274-4BF3-A654-A53519FAE7AF}"/>
-    <hyperlink ref="B7" r:id="rId187" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017B_Detail.svg" xr:uid="{8BEF6540-739A-43C4-8507-74B88B0E3308}"/>
-    <hyperlink ref="B12" r:id="rId188" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0003_Detail.svg" xr:uid="{5B095D40-6B08-42E7-9F0C-145F4A159D92}"/>
-    <hyperlink ref="B13" r:id="rId189" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0004_Detail.svg" xr:uid="{BA90B708-8CAD-4F91-A3A6-34C70C7242F4}"/>
-    <hyperlink ref="B14" r:id="rId190" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0005_Detail.svg" xr:uid="{A1CF53AA-4E63-4100-8F21-E83AA35C1604}"/>
-    <hyperlink ref="B11" r:id="rId191" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0002_Detail.svg" xr:uid="{A26CE6C0-2BFB-47C3-94E0-6267BE1C6C94}"/>
-    <hyperlink ref="B10" r:id="rId192" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0001_Detail.svg" xr:uid="{E14A7086-B4C6-4FDB-B7D4-7C18C702630A}"/>
-    <hyperlink ref="B26" r:id="rId193" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0015_Detail.svg" xr:uid="{AE8EBDA0-0651-4848-9397-12A25DA64674}"/>
-    <hyperlink ref="B28" r:id="rId194" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0017_Detail.svg" xr:uid="{0FDA170A-0CC3-4C20-BE1F-657A2C1B4131}"/>
-    <hyperlink ref="B29" r:id="rId195" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0018_Detail.svg" xr:uid="{258E20C7-8611-4032-9805-B672D23F3D38}"/>
-    <hyperlink ref="B30" r:id="rId196" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0019_Detail.svg" xr:uid="{16F5DBC3-6C32-416B-BD7D-406F3FF5549E}"/>
-    <hyperlink ref="B31" r:id="rId197" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0020_Detail.svg" xr:uid="{48785553-D98B-4E34-ABA8-058CAA66099A}"/>
-    <hyperlink ref="B32" r:id="rId198" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0021_Detail.svg" xr:uid="{139BFB00-00F8-4867-8E15-C1F2154F05F9}"/>
-    <hyperlink ref="B33" r:id="rId199" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0022_Detail.svg" xr:uid="{5494B9F9-EB11-44D9-9244-7B9E92E147F5}"/>
-    <hyperlink ref="B229" r:id="rId200" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PZ011B_Detail.svg" xr:uid="{0DC3D1D5-A861-49FB-8B82-28A6BF8D90FC}"/>
-    <hyperlink ref="B3" r:id="rId201" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PE006B_Detail.svg" xr:uid="{0C45D283-A845-475E-BF69-81FD14E9C822}"/>
-    <hyperlink ref="B34" r:id="rId202" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0023_Detail.svg" xr:uid="{4C39EC85-7752-4400-9B2C-6C4A7CF9129D}"/>
-    <hyperlink ref="B35" r:id="rId203" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0024_Detail.svg" xr:uid="{F3E501F0-9A11-487D-B608-F9A46D11F5A1}"/>
-    <hyperlink ref="B36" r:id="rId204" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0025_Detail.svg" xr:uid="{83989651-E3F6-4AA7-96A2-FD7640656CAE}"/>
-    <hyperlink ref="B37" r:id="rId205" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0026_Detail.svg" xr:uid="{8691DDEC-7612-406D-B419-95FB08A40E04}"/>
-    <hyperlink ref="B38" r:id="rId206" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0027_Detail.svg" xr:uid="{E1D1D665-0762-4836-9D4E-CFC33239EFAB}"/>
-    <hyperlink ref="B39" r:id="rId207" xr:uid="{288414F9-9549-44EE-B603-BFEE8D6BFFCA}"/>
-    <hyperlink ref="B41" r:id="rId208" xr:uid="{126A3199-30C9-44DA-A9EF-F40296E4A52B}"/>
-    <hyperlink ref="B43" r:id="rId209" xr:uid="{FEADDADD-5407-491E-99C2-A1941A1DD8B1}"/>
-    <hyperlink ref="B44" r:id="rId210" xr:uid="{B79E6062-5651-4B01-BEC5-7AE62BF9E579}"/>
-    <hyperlink ref="B4" r:id="rId211" xr:uid="{D8769202-39EC-477B-918F-91334ACD1BAB}"/>
-    <hyperlink ref="B45" r:id="rId212" xr:uid="{DA884DEF-0521-4137-A538-91F1C7FA4324}"/>
-    <hyperlink ref="B46" r:id="rId213" xr:uid="{E1ACDD90-AB13-4518-A219-F9098936AE31}"/>
-    <hyperlink ref="B8" r:id="rId214" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{7F83B0A5-0EE0-43AE-AE92-E2BAA0FD9574}"/>
-    <hyperlink ref="B22" r:id="rId215" xr:uid="{77F0653D-0E68-4330-940A-9F070D3ED346}"/>
-    <hyperlink ref="B40" r:id="rId216" xr:uid="{9365B1F6-4046-4D2E-9EF9-1AB982DE479E}"/>
-    <hyperlink ref="B42" r:id="rId217" xr:uid="{B6BE678E-A7C5-4B5B-BB06-091807E2A914}"/>
-    <hyperlink ref="B191" r:id="rId218" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV003A_Detail.svg" xr:uid="{0C8B99AD-4AA9-417E-B1B0-268F75966BCC}"/>
-    <hyperlink ref="B193" r:id="rId219" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV004A_Detail.svg" xr:uid="{BDAFB8FD-95C0-434B-AE16-15137BA37528}"/>
-    <hyperlink ref="B195" r:id="rId220" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV005A_Detail.svg" xr:uid="{0038139D-21F7-423E-87D5-9C5E62376BA1}"/>
-    <hyperlink ref="B197" r:id="rId221" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV007A_Detail.svg" xr:uid="{5EC742DE-13C4-4141-8F82-5BD0F4B990E0}"/>
-    <hyperlink ref="B199" r:id="rId222" display="PV007A" xr:uid="{830B1051-3967-43FC-B80A-74AF1570BEB9}"/>
-    <hyperlink ref="B205" r:id="rId223" display="PV013A" xr:uid="{30F95586-AB92-4653-B23F-7D3D3A962855}"/>
-    <hyperlink ref="B207" r:id="rId224" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV015A_Detail.svg" xr:uid="{F26CE65B-B76B-4D88-BDC6-01693C600359}"/>
-    <hyperlink ref="B209" r:id="rId225" display="PV007A" xr:uid="{02722343-94B7-48EC-B39E-9165025BCC28}"/>
-    <hyperlink ref="B212" r:id="rId226" xr:uid="{58E62EE8-432E-4351-BC8D-0F8B4B9357B7}"/>
-    <hyperlink ref="B213" r:id="rId227" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV019A_Detail.svg" xr:uid="{78DCB1A4-463F-4102-997B-4F6DE28990A5}"/>
-    <hyperlink ref="B217" r:id="rId228" display="PV008A" xr:uid="{6917B420-C7C7-497A-A516-FF58A19815DA}"/>
-    <hyperlink ref="B50" r:id="rId229" display="ND0034" xr:uid="{856BC43A-036F-4783-BEFB-EFFAD7B38C2F}"/>
-    <hyperlink ref="B51" r:id="rId230" xr:uid="{818DB528-76D8-4FC4-8EC1-42D46B78152C}"/>
-    <hyperlink ref="B52" r:id="rId231" xr:uid="{F49E31A7-2551-4B04-BAED-A755D94DE548}"/>
-    <hyperlink ref="B53" r:id="rId232" xr:uid="{89382148-ED37-496D-BF2A-B7BD4982B43D}"/>
-    <hyperlink ref="B54" r:id="rId233" xr:uid="{FCC63734-2BEB-4CAA-ACB1-D5C765DB6D72}"/>
-    <hyperlink ref="B55" r:id="rId234" xr:uid="{B6C12D2A-856C-4100-A4FF-9108F71FAB3F}"/>
-    <hyperlink ref="B56" r:id="rId235" xr:uid="{2F8626FB-C2B7-4C4B-A874-A7B030C834DB}"/>
-    <hyperlink ref="B57" r:id="rId236" xr:uid="{535CCF00-68C0-462E-A26E-C4BA5A0CDDDE}"/>
-    <hyperlink ref="B18" r:id="rId237" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0008_Detail.svg" xr:uid="{D707B559-638D-4573-805C-C7D9CDB9CBC1}"/>
-    <hyperlink ref="B19" r:id="rId238" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0009_Detail.svg" xr:uid="{FECDC847-0082-45AE-981B-3DFADADF1E67}"/>
-    <hyperlink ref="B49" r:id="rId239" display="ND0034" xr:uid="{D6EE3D3A-2058-4BA6-8D8D-23CF469451F6}"/>
-    <hyperlink ref="B48" r:id="rId240" display="ND0034" xr:uid="{8D64E28D-255B-48EB-94F8-E534EE940442}"/>
-    <hyperlink ref="B47" r:id="rId241" display="ND0034" xr:uid="{E64C006D-210D-4F3B-A4C7-58677D4CA2AF}"/>
+    <hyperlink ref="B59" r:id="rId1" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA001A_Detail.svg" xr:uid="{17ADBAC8-7138-41E8-BDFB-2ED015B2E3B6}"/>
+    <hyperlink ref="B66" r:id="rId2" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA008A_Detail.svg" xr:uid="{3A518947-B6F8-4C42-81D7-7894D9144A33}"/>
+    <hyperlink ref="B146" r:id="rId3" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP001A_Detail.svg" xr:uid="{761B47C6-804C-4528-8497-BBE932BB2C49}"/>
+    <hyperlink ref="B148" r:id="rId4" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP003A_Detail.svg" xr:uid="{EC8BC23F-0549-4B47-A475-38BE73BE9CEE}"/>
+    <hyperlink ref="B202" r:id="rId5" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV012A_Detail.svg" xr:uid="{5A391EDE-1D55-4CFD-9901-A29E0591193B}"/>
+    <hyperlink ref="B9" r:id="rId6" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0006_Detail.svg" xr:uid="{975176F7-F497-4824-8376-23C959379C06}"/>
+    <hyperlink ref="B10" r:id="rId7" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0007_Detail.svg" xr:uid="{5FA11009-5EE8-4528-A809-14E1B1FB1C10}"/>
+    <hyperlink ref="B11" r:id="rId8" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0008_Detail.svg" xr:uid="{7720A7D8-16EA-4565-A935-C37587E784A7}"/>
+    <hyperlink ref="B15" r:id="rId9" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0010_Detail.svg" xr:uid="{8BCC9369-A109-4DC7-B34A-9DE621C69D33}"/>
+    <hyperlink ref="B88" r:id="rId10" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE002A_Detail.svg" xr:uid="{BD7A7DCC-BFC7-48AF-B865-B8368E55F2E6}"/>
+    <hyperlink ref="B114" r:id="rId11" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE027A_Detail.svg" xr:uid="{4ECEB4FA-D039-495A-8F42-FFC9B443FDC3}"/>
+    <hyperlink ref="B139" r:id="rId12" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF009A_Detail.svg" xr:uid="{907022FE-3A1A-45BE-8FF2-AC230B1DD29B}"/>
+    <hyperlink ref="B188" r:id="rId13" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV001A_Detail.svg" xr:uid="{A8069CA7-B440-43C6-B571-35216079CADD}"/>
+    <hyperlink ref="B193" r:id="rId14" xr:uid="{7398F614-893C-4326-BA65-62E7CEF8B17B}"/>
+    <hyperlink ref="B207" r:id="rId15" xr:uid="{86D99A6B-DD65-4D76-9524-599D4EAB2E02}"/>
+    <hyperlink ref="B210" r:id="rId16" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV018A_Detail.svg" xr:uid="{3E8578A0-8239-405C-B417-86D7CEF2DB87}"/>
+    <hyperlink ref="B214" r:id="rId17" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV021A_Detail.svg" xr:uid="{27E00768-DA9C-4DAF-98AA-2381306E4A13}"/>
+    <hyperlink ref="B230" r:id="rId18" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ013A_Detail.svg" xr:uid="{9F7EE259-EBE5-4578-86F7-E5EF694FDA65}"/>
+    <hyperlink ref="B225" r:id="rId19" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ009A_Detail.svg" xr:uid="{30065FD0-FD2C-4BF8-A534-106ECA4A05E6}"/>
+    <hyperlink ref="B245" r:id="rId20" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/STPL008_Detail.svg" xr:uid="{F132DB26-A2BF-4161-B712-08766D64B599}"/>
+    <hyperlink ref="B267" r:id="rId21" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{21C87E9B-CBD0-4B81-A925-45F9B4FD8864}"/>
+    <hyperlink ref="B64" r:id="rId22" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA006A_Detail.svg" xr:uid="{C46298F6-C022-42A8-88EB-27031801D32E}"/>
+    <hyperlink ref="B17" r:id="rId23" xr:uid="{045D2E44-4A59-4C52-AA81-3156413AFAFC}"/>
+    <hyperlink ref="B61" r:id="rId24" display="PA002A" xr:uid="{6BAE8F82-BC2B-4427-9773-0A3AE429BDE1}"/>
+    <hyperlink ref="B89" r:id="rId25" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE003A_Detail.svg" xr:uid="{4004AC67-08BF-4573-A91C-196B852BE782}"/>
+    <hyperlink ref="B95" r:id="rId26" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE008A_Detail.svg" xr:uid="{907142FB-A61F-493E-ADCC-40C2E404D844}"/>
+    <hyperlink ref="B96" r:id="rId27" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE009A_Detail.svg" xr:uid="{42D7E312-902B-45B8-B2E6-478D821615A1}"/>
+    <hyperlink ref="B97" r:id="rId28" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE010A_Detail.svg" xr:uid="{12CE6EBF-4CA8-44DF-B6FC-040DFB92731D}"/>
+    <hyperlink ref="B84" r:id="rId29" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD018A_Detail.svg" xr:uid="{D9AD65D0-256C-4FDA-AB63-641CAEF296B8}"/>
+    <hyperlink ref="B87" r:id="rId30" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE001A_Detail.svg" xr:uid="{B5B862E7-DBAB-44C9-B7B4-21949ADAF9C9}"/>
+    <hyperlink ref="B92" r:id="rId31" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE006A_Detail.svg" xr:uid="{AA6401E6-CD51-4574-ABA6-C7BB3663F989}"/>
+    <hyperlink ref="B94" r:id="rId32" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE007A_Detail.svg" xr:uid="{B35184E7-56AF-48CA-8CC6-9A61FB055044}"/>
+    <hyperlink ref="B98" r:id="rId33" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE011A_Detail.svg" xr:uid="{52A5B7C0-AD9C-472F-899E-86CD63EFB3AA}"/>
+    <hyperlink ref="B99" r:id="rId34" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE012A_Detail.svg" xr:uid="{C3016BE0-26B5-41E3-A7DB-D7C53F62C108}"/>
+    <hyperlink ref="B100" r:id="rId35" display="PE012A" xr:uid="{FFB4E872-E736-41AC-8F80-41BB1E8C57A6}"/>
+    <hyperlink ref="B104" r:id="rId36" display="PE013A" xr:uid="{69F4C8E5-12AD-463A-8F4A-4719422312A8}"/>
+    <hyperlink ref="B78" r:id="rId37" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD012A_Detail.svg" xr:uid="{F25BE2C8-8813-4940-8329-63BBA6D15B89}"/>
+    <hyperlink ref="B189" r:id="rId38" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV002A_Detail.svg" xr:uid="{EB3DD888-4A6F-42F8-AD39-FAC973963B51}"/>
+    <hyperlink ref="B191" r:id="rId39" xr:uid="{C8A2ABD8-A0CE-4FB6-BD75-7694D40F91BE}"/>
+    <hyperlink ref="B195" r:id="rId40" xr:uid="{10BB9991-94D9-43E5-9038-0AD1029C8456}"/>
+    <hyperlink ref="B197" r:id="rId41" xr:uid="{E92459C1-EFAE-4D41-A9A2-B6CBF8031302}"/>
+    <hyperlink ref="B199" r:id="rId42" xr:uid="{FB94CBE5-59E0-4451-A8F5-AF4BCA7E6242}"/>
+    <hyperlink ref="B201" r:id="rId43" display="PV008A" xr:uid="{7C2F94E7-1DC8-40D5-9F4C-AA07CD1D7F60}"/>
+    <hyperlink ref="B203" r:id="rId44" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV013A_Detail.svg" xr:uid="{D981260A-8BAC-4F90-8B22-F4387848B90B}"/>
+    <hyperlink ref="B205" r:id="rId45" xr:uid="{7AB8E356-44B8-49E6-B29B-395AA92E87A4}"/>
+    <hyperlink ref="B209" r:id="rId46" xr:uid="{27C7E718-E4EC-4B45-A105-4219CB86145A}"/>
+    <hyperlink ref="B217" r:id="rId47" xr:uid="{22BEA91F-E09D-41B1-979E-65B6D728D85F}"/>
+    <hyperlink ref="B213" r:id="rId48" xr:uid="{64580D0C-1766-4DB3-AF77-41B1C3F4FBCB}"/>
+    <hyperlink ref="B218" r:id="rId49" display="PZ001A" xr:uid="{6198CEDF-7056-49B0-8C8C-0CE4F43ED518}"/>
+    <hyperlink ref="B60" r:id="rId50" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA002A_Detail.svg" xr:uid="{0302EB7E-2FF3-47CA-B5A8-8E3511F52559}"/>
+    <hyperlink ref="B73" r:id="rId51" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD007A_Detail.svg" xr:uid="{55939466-04EF-445D-B8C5-29A1F47BFBEC}"/>
+    <hyperlink ref="B67" r:id="rId52" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD001A_Detail.svg" xr:uid="{3C931296-EFA6-4A17-ABBE-BA3CEEBAE7CD}"/>
+    <hyperlink ref="B147" r:id="rId53" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP002A_Detail.svg" xr:uid="{7B04BB8C-B4F8-4443-9951-FF9779382F5E}"/>
+    <hyperlink ref="B153" r:id="rId54" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP008A_Detail.svg" xr:uid="{B8AA4B11-0A29-4052-8E9D-3BF8D275C0C3}"/>
+    <hyperlink ref="B149" r:id="rId55" display="PP003A" xr:uid="{A0025AF4-1428-4206-B942-D976CF2EABF6}"/>
+    <hyperlink ref="B150" r:id="rId56" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP005A_Detail.svg" xr:uid="{A6177C8F-61D8-4517-924D-AC098541874E}"/>
+    <hyperlink ref="B151" r:id="rId57" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP006A_Detail.svg" xr:uid="{CCC65F5C-1709-40F0-BC1E-5E22B9EE2E8B}"/>
+    <hyperlink ref="B152" r:id="rId58" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP007A_Detail.svg" xr:uid="{CF9DC830-F3E2-46F7-BB6E-F40EE3588C98}"/>
+    <hyperlink ref="B165" r:id="rId59" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS004A_Detail.svg" xr:uid="{9053D430-E6CE-479A-9C3A-E85BE51DDA2D}"/>
+    <hyperlink ref="B155" r:id="rId60" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP010A_Detail.svg" xr:uid="{0970F33B-0575-4123-83FA-27B45C94A4A2}"/>
+    <hyperlink ref="B156" r:id="rId61" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP011A_Detail.svg" xr:uid="{0EA32245-04D0-41E6-991A-61C23D6D04D5}"/>
+    <hyperlink ref="B157" r:id="rId62" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP012A_Detail.svg" xr:uid="{FBE8CA96-6772-460A-8C03-4C086593A5CE}"/>
+    <hyperlink ref="B159" r:id="rId63" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP014A_Detail.svg" xr:uid="{9377286C-CA88-49CA-8DB6-8B4673069711}"/>
+    <hyperlink ref="B160" r:id="rId64" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP015A_Detail.svg" xr:uid="{4CF07C91-9442-4F6E-8428-DC8B0ABD88EC}"/>
+    <hyperlink ref="B161" r:id="rId65" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP016A_Detail.svg" xr:uid="{95445AC5-539C-433D-929D-1B79509AB314}"/>
+    <hyperlink ref="B162" r:id="rId66" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP017A_Detail.svg" xr:uid="{F1EAA06B-6B10-469E-BFA8-DBE8DA0E67EC}"/>
+    <hyperlink ref="B163" r:id="rId67" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS001A_Detail.svg" xr:uid="{53C8229D-2E3F-405D-A9C8-3F6FE5E0EFCC}"/>
+    <hyperlink ref="B178" r:id="rId68" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT002A_Detail.svg" xr:uid="{8ED0FE06-63C6-4619-8AFA-C21DEA756B38}"/>
+    <hyperlink ref="B182" r:id="rId69" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT006A_Detail.svg" xr:uid="{DE7E75F2-6055-421D-A22C-888A6804396D}"/>
+    <hyperlink ref="B181" r:id="rId70" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT005A_Detail.svg" xr:uid="{95A726E8-8601-4CDB-BBED-77B49873F4C0}"/>
+    <hyperlink ref="B183" r:id="rId71" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT007A_Detail.svg" xr:uid="{B6131D2E-4752-4739-997C-D3CBF679F940}"/>
+    <hyperlink ref="B185" r:id="rId72" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT009A_Detail.svg" xr:uid="{D06AD6E5-7BA2-492F-8D44-8B09ADBF6122}"/>
+    <hyperlink ref="B186" r:id="rId73" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT010A_Detail.svg" xr:uid="{52343A83-46C2-4D49-BFE5-DA8717644CD2}"/>
+    <hyperlink ref="B219" r:id="rId74" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ003A_Detail.svg" xr:uid="{335D3D40-BE42-44FE-929A-0F3D3F26D262}"/>
+    <hyperlink ref="B220" r:id="rId75" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ004A_Detail.svg" xr:uid="{45517A4C-49CF-4A14-BE92-F3323139DBA8}"/>
+    <hyperlink ref="B222" r:id="rId76" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ006A_Detail.svg" xr:uid="{92F8D01F-B6E2-40C7-970D-7EAFB7872F29}"/>
+    <hyperlink ref="B229" r:id="rId77" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ012A_Detail.svg" xr:uid="{F5F1079A-1346-46A4-BF70-9025442AFB80}"/>
+    <hyperlink ref="B227" r:id="rId78" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ011A_Detail.svg" xr:uid="{BDA2ADBE-AC37-448F-9C41-243FB16B0996}"/>
+    <hyperlink ref="B63" r:id="rId79" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA005A_Detail.svg" xr:uid="{BA3A7E34-7D5B-4A78-BB78-1727C668EB8F}"/>
+    <hyperlink ref="B62" r:id="rId80" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA004A_Detail.svg" xr:uid="{39481051-1B60-44BF-8211-0D5C1980FD4B}"/>
+    <hyperlink ref="B68" r:id="rId81" display="PD001A" xr:uid="{3969656E-C88B-42A9-9C3B-B8275B159B5B}"/>
+    <hyperlink ref="B69" r:id="rId82" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD003A_Detail.svg" xr:uid="{86AB2467-10FE-4C5F-883D-EDA03495CD55}"/>
+    <hyperlink ref="B70" r:id="rId83" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD004A_Detail.svg" xr:uid="{A3F7C2AC-969E-4A1D-87C5-6BFE5671E4DC}"/>
+    <hyperlink ref="B71" r:id="rId84" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD005A_Detail.svg" xr:uid="{6DFFDA9D-5A28-4CC7-8DE9-876E2360BFEE}"/>
+    <hyperlink ref="B72" r:id="rId85" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD006A_Detail.svg" xr:uid="{3BB6ACEF-9AAF-4C4D-9A87-FCF6EA0F91BD}"/>
+    <hyperlink ref="B83" r:id="rId86" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD017A_Detail.svg" xr:uid="{28D1C6B0-DDE6-442D-9F10-91D27566478A}"/>
+    <hyperlink ref="B74" r:id="rId87" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD008A_Detail.svg" xr:uid="{AB7B0FCA-5804-4486-8380-FBA9F83DEE66}"/>
+    <hyperlink ref="B75" r:id="rId88" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD009A_Detail.svg" xr:uid="{9D870461-08B6-4714-8A00-09714564A8DF}"/>
+    <hyperlink ref="B76" r:id="rId89" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD010A_Detail.svg" xr:uid="{BB4A6A70-CBD2-4C62-B476-1DB99A7B8C9C}"/>
+    <hyperlink ref="B77" r:id="rId90" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD011A_Detail.svg" xr:uid="{5A9D789E-5B6D-46CC-883A-8FE28112F14B}"/>
+    <hyperlink ref="B79" r:id="rId91" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD013A_Detail.svg" xr:uid="{6394051E-0C5B-4871-B946-B73195930CB1}"/>
+    <hyperlink ref="B80" r:id="rId92" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD014A_Detail.svg" xr:uid="{89E87861-2175-4BEE-A5F9-33D47934E630}"/>
+    <hyperlink ref="B81" r:id="rId93" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD015A_Detail.svg" xr:uid="{C0901CAD-B396-4045-9DFB-94C087A6E9C7}"/>
+    <hyperlink ref="B82" r:id="rId94" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD016A_Detail.svg" xr:uid="{FE18571B-26F6-45A2-AE52-5E17B76EC7F3}"/>
+    <hyperlink ref="B105" r:id="rId95" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE018A_Detail.svg" xr:uid="{6D3B7973-3EAF-4809-A3A6-949465067CBC}"/>
+    <hyperlink ref="B107" r:id="rId96" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE020A_Detail.svg" xr:uid="{39CB98B6-29C9-4B55-BB4D-C050812B9145}"/>
+    <hyperlink ref="B108" r:id="rId97" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE021A_Detail.svg" xr:uid="{50AE8AE5-DEF4-4FC6-8682-258DF3904CD7}"/>
+    <hyperlink ref="B109" r:id="rId98" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE022A_Detail.svg" xr:uid="{93F60579-BA2A-4EDC-B883-017EBA23D13F}"/>
+    <hyperlink ref="B110" r:id="rId99" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE023A_Detail.svg" xr:uid="{2F7FC80D-3FA4-4BE4-A403-E017F265775F}"/>
+    <hyperlink ref="B111" r:id="rId100" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE024A_Detail.svg" xr:uid="{212E32CA-E31F-4B52-AC82-844C20339614}"/>
+    <hyperlink ref="B113" r:id="rId101" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE026A_Detail.svg" xr:uid="{9078864B-22E7-4236-BA73-76CA46B86A31}"/>
+    <hyperlink ref="B115" r:id="rId102" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE028A_Detail.svg" xr:uid="{F436B4D7-3AA5-4126-BBD2-BACE69A4A4E0}"/>
+    <hyperlink ref="B116" r:id="rId103" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE029A_Detail.svg" xr:uid="{C7A515AB-6C11-4EA4-85E4-5091485DAA17}"/>
+    <hyperlink ref="B120" r:id="rId104" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE033A_Detail.svg" xr:uid="{34E7B3BE-E531-4018-BB45-6CCB618C0FBB}"/>
+    <hyperlink ref="B117" r:id="rId105" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE030A_Detail.svg" xr:uid="{1F74D129-65A3-4B07-BF1F-5193476A8A04}"/>
+    <hyperlink ref="B119" r:id="rId106" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE032A_Detail.svg" xr:uid="{8A8FA28E-6634-4E0D-A29F-388C878E8DB9}"/>
+    <hyperlink ref="B121" r:id="rId107" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE034A_Detail.svg" xr:uid="{6C65D9E8-788A-4EFB-B896-E4E82EAA3CB0}"/>
+    <hyperlink ref="B123" r:id="rId108" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE036A_Detail.svg" xr:uid="{6A654C5A-571F-47D9-9387-6F62409DC1B7}"/>
+    <hyperlink ref="B122" r:id="rId109" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE035A_Detail.svg" xr:uid="{8BF957E4-037D-4E36-9BCA-83538FEE7EAF}"/>
+    <hyperlink ref="B124" r:id="rId110" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE037A_Detail.svg" xr:uid="{7931F92F-DB33-458A-84AB-EEE6E7217AAA}"/>
+    <hyperlink ref="B125" r:id="rId111" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE038A_Detail.svg" xr:uid="{F73D9E2D-2341-4000-BD06-BEF7EA513332}"/>
+    <hyperlink ref="B126" r:id="rId112" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE039A_Detail.svg" xr:uid="{FB0AAC16-DEA9-41D3-8765-ACE272916988}"/>
+    <hyperlink ref="B127" r:id="rId113" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE040A_Detail.svg" xr:uid="{9D15EFC4-F96D-4011-83A8-7E4FB0A02FD4}"/>
+    <hyperlink ref="B129" r:id="rId114" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE042A_Detail.svg" xr:uid="{4DC635F0-1E08-4047-98E2-D16EA3B8D3B6}"/>
+    <hyperlink ref="B130" r:id="rId115" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE043A_Detail.svg" xr:uid="{7A91C884-B181-4AC9-8872-A5B4FEC2FA44}"/>
+    <hyperlink ref="B131" r:id="rId116" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF001A_Detail.svg" xr:uid="{226AE98E-A3DA-4D82-91A1-7CFDF93A8DE9}"/>
+    <hyperlink ref="B132" r:id="rId117" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF002A_Detail.svg" xr:uid="{467E946A-F396-4E22-A95C-421F6CE0BC8B}"/>
+    <hyperlink ref="B133" r:id="rId118" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF003A_Detail.svg" xr:uid="{55C30B46-FD0C-4081-A7D2-D7A7DFE70B52}"/>
+    <hyperlink ref="B134" r:id="rId119" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF004A_Detail.svg" xr:uid="{1127E743-3E80-461C-9E2E-11276A527952}"/>
+    <hyperlink ref="B136" r:id="rId120" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF006A_Detail.svg" xr:uid="{C896FA40-2C0C-4F45-ABB7-4A0598EF464F}"/>
+    <hyperlink ref="B137" r:id="rId121" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF007A_Detail.svg" xr:uid="{B63E94F9-6FBE-473E-BB35-4B04D8BA205A}"/>
+    <hyperlink ref="B145" r:id="rId122" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF015A_Detail.svg" xr:uid="{D0C9703A-C515-442F-88BF-811B68EF3142}"/>
+    <hyperlink ref="B140" r:id="rId123" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF010A_Detail.svg" xr:uid="{8776960A-3D62-49BB-964C-0A029249E4ED}"/>
+    <hyperlink ref="B141" r:id="rId124" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF011A_Detail.svg" xr:uid="{52198015-5884-4164-AE13-C31DC940BF9F}"/>
+    <hyperlink ref="B143" r:id="rId125" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF013A_Detail.svg" xr:uid="{1676627D-C9A1-412D-A74B-FEC1DD6ADAFC}"/>
+    <hyperlink ref="B144" r:id="rId126" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF014A_Detail.svg" xr:uid="{0AE6782A-A294-4988-A1A8-09100E831215}"/>
+    <hyperlink ref="B19" r:id="rId127" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0014_Detail.svg" xr:uid="{1F3765D3-EFE7-463A-B085-1DE36D0AE049}"/>
+    <hyperlink ref="B58" r:id="rId128" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/LZ009A_Detail.svg" xr:uid="{964B3FA4-6BEE-49FA-A53D-C16D25DADF11}"/>
+    <hyperlink ref="B18" r:id="rId129" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0013_Detail.svg" xr:uid="{5203DA34-E147-4733-BD2B-596D44AF2F0D}"/>
+    <hyperlink ref="B164" r:id="rId130" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS003A_Detail.svg" xr:uid="{D3E46F2B-78B9-41FF-AD13-E05C1AAC94AA}"/>
+    <hyperlink ref="B184" r:id="rId131" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT008A_Detail.svg" xr:uid="{A09F2ECE-A3F2-485F-89B3-392B6CCF3E0F}"/>
+    <hyperlink ref="B21" r:id="rId132" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0016_Detail.svg" xr:uid="{D78471C4-ED27-412C-838A-FDFC562E1EC3}"/>
+    <hyperlink ref="B215" r:id="rId133" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV022A_Detail.svg" xr:uid="{7F2ADD73-6C39-4114-8228-83338A629639}"/>
+    <hyperlink ref="B241" r:id="rId134" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ024A_Detail.svg" xr:uid="{D7DC9173-D444-4E60-B47B-45295B162EA3}"/>
+    <hyperlink ref="B14" r:id="rId135" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0009_Detail.svg" xr:uid="{CF5F7511-92B4-421B-B7C3-594BAC34117C}"/>
+    <hyperlink ref="B233" r:id="rId136" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ016A_Detail.svg" xr:uid="{223CCECC-C661-4D77-99FB-373C2C3EB9FD}"/>
+    <hyperlink ref="B239" r:id="rId137" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ022A_Detail.svg" xr:uid="{4E646DA6-844E-461F-A30F-E45D4A6BAEE0}"/>
+    <hyperlink ref="B234" r:id="rId138" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ017A_Detail.svg" xr:uid="{4AF15DA4-056F-4E39-B57F-D527D7C96314}"/>
+    <hyperlink ref="B235" r:id="rId139" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ018A_Detail.svg" xr:uid="{6A08BE2B-2F4A-40D0-87F1-2BF30F7E5204}"/>
+    <hyperlink ref="B236" r:id="rId140" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ019A_Detail.svg" xr:uid="{6C2DB1B2-D14C-41F7-85E9-0AD5CD60A40D}"/>
+    <hyperlink ref="B237" r:id="rId141" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ020A_Detail.svg" xr:uid="{3E5BB973-5805-404F-A772-22A577F5EA77}"/>
+    <hyperlink ref="B238" r:id="rId142" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ021A_Detail.svg" xr:uid="{96375F5D-1843-4B64-9FEB-59352041AF1C}"/>
+    <hyperlink ref="B240" r:id="rId143" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ023A_Detail.svg" xr:uid="{D811FB39-FE0C-4790-A865-54A17F50CA6D}"/>
+    <hyperlink ref="B242" r:id="rId144" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ025A_Detail.svg" xr:uid="{60163B1A-1792-49FF-9790-F2BF94ABFA4A}"/>
+    <hyperlink ref="B243" r:id="rId145" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ026A_Detail.svg" xr:uid="{0AAE0EB6-ECBB-4198-AA26-C684A0AECB97}"/>
+    <hyperlink ref="B244" r:id="rId146" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ027A_Detail.svg" xr:uid="{824407FA-7B30-4D5E-93CE-ED8122F65FFE}"/>
+    <hyperlink ref="B231" r:id="rId147" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ014A_Detail.svg" xr:uid="{F99B97AB-F1A6-4427-ABEB-25E3CC85B5DC}"/>
+    <hyperlink ref="B232" r:id="rId148" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ015A_Detail.svg" xr:uid="{12DA03AC-3D4B-49FC-B523-CC4091EF5CF4}"/>
+    <hyperlink ref="B85" r:id="rId149" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD019A_Detail.svg" xr:uid="{1FEADDE7-E396-46B6-9322-03EDCA28A99A}"/>
+    <hyperlink ref="B86" r:id="rId150" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD020A_Detail.svg" xr:uid="{1987EC41-B7CC-4E23-B295-01B52113BE11}"/>
+    <hyperlink ref="B90" r:id="rId151" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE004A_Detail.svg" xr:uid="{22A02656-E11C-40BA-93D1-A3BA2FBE802C}"/>
+    <hyperlink ref="B91" r:id="rId152" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE005A_Detail.svg" xr:uid="{D679D4B8-1D0A-498C-B0C6-64751CDFD8A9}"/>
+    <hyperlink ref="B65" r:id="rId153" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA007A_Detail.svg" xr:uid="{30DD321A-DB3E-4139-B7C6-5B72D5F41E50}"/>
+    <hyperlink ref="B101" r:id="rId154" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE014A_Detail.svg" xr:uid="{2B620BE4-F09B-478A-BDA6-76461B53049C}"/>
+    <hyperlink ref="B102" r:id="rId155" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE015A_Detail.svg" xr:uid="{57F06AB3-A2D4-42BD-8A97-785E7A9DEED3}"/>
+    <hyperlink ref="B103" r:id="rId156" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE016A_Detail.svg" xr:uid="{7714B096-A821-46A9-B38E-478AC0F60DFA}"/>
+    <hyperlink ref="B106" r:id="rId157" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE019A_Detail.svg" xr:uid="{77B288AB-A3B1-4E08-ABAC-36CEFD1274DD}"/>
+    <hyperlink ref="B118" r:id="rId158" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE031A_Detail.svg" xr:uid="{BD8A7598-0DFE-4ACB-ABFF-A23EE4147A0C}"/>
+    <hyperlink ref="B112" r:id="rId159" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE025A_Detail.svg" xr:uid="{111CB70F-38F3-4FA2-9171-155C1FE97029}"/>
+    <hyperlink ref="B166" r:id="rId160" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS005A_Detail.svg" xr:uid="{8BD8F9B2-845D-4212-B985-91349C8461AA}"/>
+    <hyperlink ref="B167" r:id="rId161" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS006A_Detail.svg" xr:uid="{616ABAAF-2406-46A1-9490-096325FB538C}"/>
+    <hyperlink ref="B168" r:id="rId162" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS007A_Detail.svg" xr:uid="{C158EBE4-9C88-4608-8165-95D1C5969FE5}"/>
+    <hyperlink ref="B169" r:id="rId163" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS008A_Detail.svg" xr:uid="{8B850863-4DBF-4261-A871-9900D82512A0}"/>
+    <hyperlink ref="B170" r:id="rId164" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS009A_Detail.svg" xr:uid="{EAA92938-1022-4B27-8A45-FC38DB3D12AB}"/>
+    <hyperlink ref="B171" r:id="rId165" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS010A_Detail.svg" xr:uid="{DE97D73F-147C-4EDC-A7D8-86145F37E03C}"/>
+    <hyperlink ref="B172" r:id="rId166" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS011A_Detail.svg" xr:uid="{006F66EF-728F-49E8-A5FE-751016748DAC}"/>
+    <hyperlink ref="B173" r:id="rId167" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS012A_Detail.svg" xr:uid="{8F448560-0B77-4837-B70F-0B9A88CD3C63}"/>
+    <hyperlink ref="B174" r:id="rId168" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS013A_Detail.svg" xr:uid="{0221699E-5F49-4DF1-B0AB-C4E5888F2A80}"/>
+    <hyperlink ref="B175" r:id="rId169" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS014A_Detail.svg" xr:uid="{C05394F3-DC5D-41A9-A414-4B0B18AAED5C}"/>
+    <hyperlink ref="B176" r:id="rId170" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS015A_Detail.svg" xr:uid="{C2CC68D8-9E61-4D94-BCC1-7A22522BAC81}"/>
+    <hyperlink ref="B177" r:id="rId171" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS016A_Detail.svg" xr:uid="{47A88BDB-E04A-43F6-992D-C76510B510EF}"/>
+    <hyperlink ref="B179" r:id="rId172" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT003A_Detail.svg" xr:uid="{7CF97CF8-3E1A-4A9E-ABE2-3A579CF8676B}"/>
+    <hyperlink ref="B180" r:id="rId173" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT004A_Detail.svg" xr:uid="{75DC4A11-DAE8-4DC6-A6D0-7E3E61B719CC}"/>
+    <hyperlink ref="B128" r:id="rId174" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE041A_Detail.svg" xr:uid="{EF9B4A93-EF2D-4E76-A4CC-16163CED7262}"/>
+    <hyperlink ref="B135" r:id="rId175" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF005A_Detail.svg" xr:uid="{3383514A-9E6D-45A7-AD65-0B18E1BAAD22}"/>
+    <hyperlink ref="B138" r:id="rId176" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF008A_Detail.svg" xr:uid="{73E8300F-62F2-4049-934B-015EDBEED287}"/>
+    <hyperlink ref="B142" r:id="rId177" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF012A_Detail.svg" xr:uid="{E9B3CC0D-A34B-4C8A-B89B-B330DAD71021}"/>
+    <hyperlink ref="B154" r:id="rId178" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP009A_Detail.svg" xr:uid="{0A13328E-0285-44BD-B9CF-A05D28AD6EAD}"/>
+    <hyperlink ref="B187" r:id="rId179" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT011A_Detail.svg" xr:uid="{E88B48B0-2B27-4600-8526-87B72CED5EC1}"/>
+    <hyperlink ref="B200" r:id="rId180" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV009A_Detail.svg" xr:uid="{25FF9022-3620-4A11-BF03-2A03200DD6CC}"/>
+    <hyperlink ref="B221" r:id="rId181" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ005A_Detail.svg" xr:uid="{92F69C2E-BC95-4B0C-9D0B-5D880C9FFE1C}"/>
+    <hyperlink ref="B223" r:id="rId182" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ007A_Detail.svg" xr:uid="{D96D22DE-45BD-4E25-A768-C8AAD05A8872}"/>
+    <hyperlink ref="B224" r:id="rId183" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ008A_Detail.svg" xr:uid="{14ADB638-7CCB-453F-BBA2-E88CDF197096}"/>
+    <hyperlink ref="B226" r:id="rId184" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ010A_Detail.svg" xr:uid="{7FE7B2D2-712E-48EB-BF5E-8AF8801ACB71}"/>
+    <hyperlink ref="B158" r:id="rId185" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP013A_Detail.svg" xr:uid="{81BF01ED-214F-4F7B-B7B6-1F88A3E341A7}"/>
+    <hyperlink ref="B266" r:id="rId186" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM005B_Detail.svg" xr:uid="{C4A57621-4274-4BF3-A654-A53519FAE7AF}"/>
+    <hyperlink ref="B268" r:id="rId187" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017B_Detail.svg" xr:uid="{8BEF6540-739A-43C4-8507-74B88B0E3308}"/>
+    <hyperlink ref="B6" r:id="rId188" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0003_Detail.svg" xr:uid="{5B095D40-6B08-42E7-9F0C-145F4A159D92}"/>
+    <hyperlink ref="B7" r:id="rId189" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0004_Detail.svg" xr:uid="{BA90B708-8CAD-4F91-A3A6-34C70C7242F4}"/>
+    <hyperlink ref="B8" r:id="rId190" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0005_Detail.svg" xr:uid="{A1CF53AA-4E63-4100-8F21-E83AA35C1604}"/>
+    <hyperlink ref="B5" r:id="rId191" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0002_Detail.svg" xr:uid="{A26CE6C0-2BFB-47C3-94E0-6267BE1C6C94}"/>
+    <hyperlink ref="B4" r:id="rId192" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0001_Detail.svg" xr:uid="{E14A7086-B4C6-4FDB-B7D4-7C18C702630A}"/>
+    <hyperlink ref="B20" r:id="rId193" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0015_Detail.svg" xr:uid="{AE8EBDA0-0651-4848-9397-12A25DA64674}"/>
+    <hyperlink ref="B22" r:id="rId194" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0017_Detail.svg" xr:uid="{0FDA170A-0CC3-4C20-BE1F-657A2C1B4131}"/>
+    <hyperlink ref="B23" r:id="rId195" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0018_Detail.svg" xr:uid="{258E20C7-8611-4032-9805-B672D23F3D38}"/>
+    <hyperlink ref="B24" r:id="rId196" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0019_Detail.svg" xr:uid="{16F5DBC3-6C32-416B-BD7D-406F3FF5549E}"/>
+    <hyperlink ref="B25" r:id="rId197" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0020_Detail.svg" xr:uid="{48785553-D98B-4E34-ABA8-058CAA66099A}"/>
+    <hyperlink ref="B26" r:id="rId198" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0021_Detail.svg" xr:uid="{139BFB00-00F8-4867-8E15-C1F2154F05F9}"/>
+    <hyperlink ref="B27" r:id="rId199" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0022_Detail.svg" xr:uid="{5494B9F9-EB11-44D9-9244-7B9E92E147F5}"/>
+    <hyperlink ref="B228" r:id="rId200" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PZ011B_Detail.svg" xr:uid="{0DC3D1D5-A861-49FB-8B82-28A6BF8D90FC}"/>
+    <hyperlink ref="B93" r:id="rId201" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PE006B_Detail.svg" xr:uid="{0C45D283-A845-475E-BF69-81FD14E9C822}"/>
+    <hyperlink ref="B28" r:id="rId202" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0023_Detail.svg" xr:uid="{4C39EC85-7752-4400-9B2C-6C4A7CF9129D}"/>
+    <hyperlink ref="B29" r:id="rId203" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0024_Detail.svg" xr:uid="{F3E501F0-9A11-487D-B608-F9A46D11F5A1}"/>
+    <hyperlink ref="B30" r:id="rId204" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0025_Detail.svg" xr:uid="{83989651-E3F6-4AA7-96A2-FD7640656CAE}"/>
+    <hyperlink ref="B31" r:id="rId205" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0026_Detail.svg" xr:uid="{8691DDEC-7612-406D-B419-95FB08A40E04}"/>
+    <hyperlink ref="B32" r:id="rId206" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0027_Detail.svg" xr:uid="{E1D1D665-0762-4836-9D4E-CFC33239EFAB}"/>
+    <hyperlink ref="B33" r:id="rId207" xr:uid="{288414F9-9549-44EE-B603-BFEE8D6BFFCA}"/>
+    <hyperlink ref="B35" r:id="rId208" xr:uid="{126A3199-30C9-44DA-A9EF-F40296E4A52B}"/>
+    <hyperlink ref="B37" r:id="rId209" xr:uid="{FEADDADD-5407-491E-99C2-A1941A1DD8B1}"/>
+    <hyperlink ref="B38" r:id="rId210" xr:uid="{B79E6062-5651-4B01-BEC5-7AE62BF9E579}"/>
+    <hyperlink ref="B265" r:id="rId211" xr:uid="{D8769202-39EC-477B-918F-91334ACD1BAB}"/>
+    <hyperlink ref="B39" r:id="rId212" xr:uid="{DA884DEF-0521-4137-A538-91F1C7FA4324}"/>
+    <hyperlink ref="B40" r:id="rId213" xr:uid="{E1ACDD90-AB13-4518-A219-F9098936AE31}"/>
+    <hyperlink ref="B269" r:id="rId214" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{7F83B0A5-0EE0-43AE-AE92-E2BAA0FD9574}"/>
+    <hyperlink ref="B16" r:id="rId215" xr:uid="{77F0653D-0E68-4330-940A-9F070D3ED346}"/>
+    <hyperlink ref="B34" r:id="rId216" xr:uid="{9365B1F6-4046-4D2E-9EF9-1AB982DE479E}"/>
+    <hyperlink ref="B36" r:id="rId217" xr:uid="{B6BE678E-A7C5-4B5B-BB06-091807E2A914}"/>
+    <hyperlink ref="B190" r:id="rId218" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV003A_Detail.svg" xr:uid="{0C8B99AD-4AA9-417E-B1B0-268F75966BCC}"/>
+    <hyperlink ref="B192" r:id="rId219" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV004A_Detail.svg" xr:uid="{BDAFB8FD-95C0-434B-AE16-15137BA37528}"/>
+    <hyperlink ref="B194" r:id="rId220" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV005A_Detail.svg" xr:uid="{0038139D-21F7-423E-87D5-9C5E62376BA1}"/>
+    <hyperlink ref="B196" r:id="rId221" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV007A_Detail.svg" xr:uid="{5EC742DE-13C4-4141-8F82-5BD0F4B990E0}"/>
+    <hyperlink ref="B198" r:id="rId222" display="PV007A" xr:uid="{830B1051-3967-43FC-B80A-74AF1570BEB9}"/>
+    <hyperlink ref="B204" r:id="rId223" display="PV013A" xr:uid="{30F95586-AB92-4653-B23F-7D3D3A962855}"/>
+    <hyperlink ref="B206" r:id="rId224" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV015A_Detail.svg" xr:uid="{F26CE65B-B76B-4D88-BDC6-01693C600359}"/>
+    <hyperlink ref="B208" r:id="rId225" display="PV007A" xr:uid="{02722343-94B7-48EC-B39E-9165025BCC28}"/>
+    <hyperlink ref="B211" r:id="rId226" xr:uid="{58E62EE8-432E-4351-BC8D-0F8B4B9357B7}"/>
+    <hyperlink ref="B212" r:id="rId227" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV019A_Detail.svg" xr:uid="{78DCB1A4-463F-4102-997B-4F6DE28990A5}"/>
+    <hyperlink ref="B216" r:id="rId228" display="PV008A" xr:uid="{6917B420-C7C7-497A-A516-FF58A19815DA}"/>
+    <hyperlink ref="B44" r:id="rId229" display="ND0034" xr:uid="{856BC43A-036F-4783-BEFB-EFFAD7B38C2F}"/>
+    <hyperlink ref="B45" r:id="rId230" xr:uid="{818DB528-76D8-4FC4-8EC1-42D46B78152C}"/>
+    <hyperlink ref="B46" r:id="rId231" xr:uid="{F49E31A7-2551-4B04-BAED-A755D94DE548}"/>
+    <hyperlink ref="B47" r:id="rId232" xr:uid="{89382148-ED37-496D-BF2A-B7BD4982B43D}"/>
+    <hyperlink ref="B48" r:id="rId233" xr:uid="{FCC63734-2BEB-4CAA-ACB1-D5C765DB6D72}"/>
+    <hyperlink ref="B49" r:id="rId234" xr:uid="{B6C12D2A-856C-4100-A4FF-9108F71FAB3F}"/>
+    <hyperlink ref="B50" r:id="rId235" xr:uid="{2F8626FB-C2B7-4C4B-A874-A7B030C834DB}"/>
+    <hyperlink ref="B51" r:id="rId236" xr:uid="{535CCF00-68C0-462E-A26E-C4BA5A0CDDDE}"/>
+    <hyperlink ref="B12" r:id="rId237" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0008_Detail.svg" xr:uid="{D707B559-638D-4573-805C-C7D9CDB9CBC1}"/>
+    <hyperlink ref="B13" r:id="rId238" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0009_Detail.svg" xr:uid="{FECDC847-0082-45AE-981B-3DFADADF1E67}"/>
+    <hyperlink ref="B43" r:id="rId239" display="ND0034" xr:uid="{D6EE3D3A-2058-4BA6-8D8D-23CF469451F6}"/>
+    <hyperlink ref="B42" r:id="rId240" display="ND0034" xr:uid="{8D64E28D-255B-48EB-94F8-E534EE940442}"/>
+    <hyperlink ref="B41" r:id="rId241" display="ND0034" xr:uid="{E64C006D-210D-4F3B-A4C7-58677D4CA2AF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId242"/>

--- a/Symbols_UpdateReferenceID.xlsx
+++ b/Symbols_UpdateReferenceID.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F6A41F-E191-48AE-AE85-955F48868ED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF25E484-CEE5-43E7-8FEA-7AE7894E6738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Symbols" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Symbols!$A$2:$C$264</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Symbols!$A$2:$C$269</definedName>
     <definedName name="DEXPI_CLASS">#REF!</definedName>
     <definedName name="DEXPI_PACKAGE">#REF!</definedName>
     <definedName name="map">#REF!</definedName>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="713">
   <si>
     <t>Description</t>
   </si>
@@ -2222,6 +2222,12 @@
   </si>
   <si>
     <t>Welded Joint</t>
+  </si>
+  <si>
+    <t>ND0250</t>
+  </si>
+  <si>
+    <t>Electric Gas Heater</t>
   </si>
 </sst>
 </file>
@@ -2371,7 +2377,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2379,14 +2385,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2729,12 +2727,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C269"/>
+  <dimension ref="A1:C270"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.42578125" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="66.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="197.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -2752,7 +2750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>391</v>
       </c>
@@ -2763,7 +2761,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>352</v>
       </c>
@@ -2774,7 +2772,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>1</v>
       </c>
@@ -2785,7 +2783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>347</v>
       </c>
@@ -2796,7 +2794,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>349</v>
       </c>
@@ -2807,7 +2805,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>351</v>
       </c>
@@ -2818,7 +2816,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>13</v>
       </c>
@@ -2829,7 +2827,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>14</v>
       </c>
@@ -2840,7 +2838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>634</v>
       </c>
@@ -2851,7 +2849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>635</v>
       </c>
@@ -2862,7 +2860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>636</v>
       </c>
@@ -2873,7 +2871,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>637</v>
       </c>
@@ -2884,7 +2882,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>18</v>
       </c>
@@ -2895,7 +2893,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>46</v>
       </c>
@@ -2906,7 +2904,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>399</v>
       </c>
@@ -2917,7 +2915,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>53</v>
       </c>
@@ -2928,7 +2926,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>236</v>
       </c>
@@ -2939,7 +2937,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>358</v>
       </c>
@@ -2950,7 +2948,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>296</v>
       </c>
@@ -2961,7 +2959,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>364</v>
       </c>
@@ -2972,7 +2970,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>365</v>
       </c>
@@ -2983,7 +2981,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>366</v>
       </c>
@@ -2994,7 +2992,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>367</v>
       </c>
@@ -3005,7 +3003,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>369</v>
       </c>
@@ -3016,7 +3014,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>370</v>
       </c>
@@ -3027,7 +3025,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>377</v>
       </c>
@@ -3038,7 +3036,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>380</v>
       </c>
@@ -3049,7 +3047,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>381</v>
       </c>
@@ -3060,7 +3058,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>383</v>
       </c>
@@ -3071,7 +3069,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>384</v>
       </c>
@@ -3082,7 +3080,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>386</v>
       </c>
@@ -3093,7 +3091,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>387</v>
       </c>
@@ -3104,7 +3102,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>404</v>
       </c>
@@ -3115,7 +3113,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>388</v>
       </c>
@@ -3126,7 +3124,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>405</v>
       </c>
@@ -3137,7 +3135,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>389</v>
       </c>
@@ -3148,7 +3146,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>394</v>
       </c>
@@ -3159,7 +3157,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>395</v>
       </c>
@@ -3170,7 +3168,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>638</v>
       </c>
@@ -3181,7 +3179,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>639</v>
       </c>
@@ -3192,7 +3190,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>640</v>
       </c>
@@ -3203,7 +3201,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>641</v>
       </c>
@@ -3214,7 +3212,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>442</v>
       </c>
@@ -3225,7 +3223,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>444</v>
       </c>
@@ -3236,7 +3234,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>445</v>
       </c>
@@ -3247,7 +3245,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>447</v>
       </c>
@@ -3258,7 +3256,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
         <v>449</v>
       </c>
@@ -3269,7 +3267,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
         <v>453</v>
       </c>
@@ -3280,7 +3278,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
         <v>455</v>
       </c>
@@ -3291,7 +3289,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="15" t="s">
         <v>457</v>
       </c>
@@ -3302,7 +3300,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>459</v>
       </c>
@@ -3313,7 +3311,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>703</v>
       </c>
@@ -3324,7 +3322,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>704</v>
       </c>
@@ -3335,7 +3333,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>705</v>
       </c>
@@ -3346,7 +3344,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>706</v>
       </c>
@@ -3357,7 +3355,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>461</v>
       </c>
@@ -3368,7 +3366,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>462</v>
       </c>
@@ -3379,7 +3377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>463</v>
       </c>
@@ -3390,7 +3388,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>464</v>
       </c>
@@ -3401,7 +3399,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>465</v>
       </c>
@@ -3412,7 +3410,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>466</v>
       </c>
@@ -3423,7 +3421,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>467</v>
       </c>
@@ -3434,7 +3432,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>468</v>
       </c>
@@ -3445,7 +3443,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>469</v>
       </c>
@@ -3456,7 +3454,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>470</v>
       </c>
@@ -3467,7 +3465,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>471</v>
       </c>
@@ -3478,7 +3476,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>472</v>
       </c>
@@ -3489,7 +3487,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>473</v>
       </c>
@@ -3500,7 +3498,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>474</v>
       </c>
@@ -3511,7 +3509,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>475</v>
       </c>
@@ -3522,7 +3520,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>476</v>
       </c>
@@ -3533,7 +3531,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>477</v>
       </c>
@@ -3544,7 +3542,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>478</v>
       </c>
@@ -3555,7 +3553,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>479</v>
       </c>
@@ -3566,7 +3564,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>480</v>
       </c>
@@ -3577,7 +3575,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>481</v>
       </c>
@@ -3588,7 +3586,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>482</v>
       </c>
@@ -3599,7 +3597,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>483</v>
       </c>
@@ -3610,7 +3608,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>484</v>
       </c>
@@ -3621,7 +3619,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>485</v>
       </c>
@@ -3632,7 +3630,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>486</v>
       </c>
@@ -3643,7 +3641,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>487</v>
       </c>
@@ -3654,7 +3652,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>488</v>
       </c>
@@ -3665,7 +3663,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>489</v>
       </c>
@@ -3676,7 +3674,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>490</v>
       </c>
@@ -3687,7 +3685,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>491</v>
       </c>
@@ -3698,7 +3696,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>492</v>
       </c>
@@ -3709,7 +3707,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>493</v>
       </c>
@@ -3720,7 +3718,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>494</v>
       </c>
@@ -3731,7 +3729,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>691</v>
       </c>
@@ -3742,7 +3740,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="16" t="s">
         <v>702</v>
       </c>
@@ -3753,7 +3751,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>495</v>
       </c>
@@ -3764,7 +3762,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>496</v>
       </c>
@@ -3775,7 +3773,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>497</v>
       </c>
@@ -3786,7 +3784,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>498</v>
       </c>
@@ -3797,7 +3795,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>499</v>
       </c>
@@ -3808,7 +3806,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>500</v>
       </c>
@@ -3819,7 +3817,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>501</v>
       </c>
@@ -3830,7 +3828,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>502</v>
       </c>
@@ -3841,7 +3839,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>503</v>
       </c>
@@ -3852,7 +3850,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>504</v>
       </c>
@@ -3863,7 +3861,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>505</v>
       </c>
@@ -3874,7 +3872,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>506</v>
       </c>
@@ -3885,7 +3883,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>507</v>
       </c>
@@ -3896,7 +3894,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>508</v>
       </c>
@@ -3907,7 +3905,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>509</v>
       </c>
@@ -3918,7 +3916,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>510</v>
       </c>
@@ -3929,7 +3927,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>511</v>
       </c>
@@ -3940,7 +3938,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>512</v>
       </c>
@@ -3951,7 +3949,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>513</v>
       </c>
@@ -3962,7 +3960,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>514</v>
       </c>
@@ -3973,7 +3971,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>515</v>
       </c>
@@ -3984,7 +3982,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>516</v>
       </c>
@@ -3995,7 +3993,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>517</v>
       </c>
@@ -4006,7 +4004,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>518</v>
       </c>
@@ -4017,7 +4015,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>519</v>
       </c>
@@ -4028,7 +4026,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>520</v>
       </c>
@@ -4039,7 +4037,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>521</v>
       </c>
@@ -4050,7 +4048,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>522</v>
       </c>
@@ -4061,7 +4059,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>523</v>
       </c>
@@ -4072,7 +4070,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>524</v>
       </c>
@@ -4083,7 +4081,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>525</v>
       </c>
@@ -4094,7 +4092,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>526</v>
       </c>
@@ -4105,7 +4103,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>527</v>
       </c>
@@ -4116,7 +4114,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>528</v>
       </c>
@@ -4127,7 +4125,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>529</v>
       </c>
@@ -4138,7 +4136,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>530</v>
       </c>
@@ -4149,7 +4147,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>531</v>
       </c>
@@ -4160,7 +4158,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>532</v>
       </c>
@@ -4171,7 +4169,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>533</v>
       </c>
@@ -4182,7 +4180,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>534</v>
       </c>
@@ -4193,7 +4191,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>535</v>
       </c>
@@ -4204,7 +4202,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>536</v>
       </c>
@@ -4215,7 +4213,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>537</v>
       </c>
@@ -4226,7 +4224,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>538</v>
       </c>
@@ -4237,7 +4235,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>539</v>
       </c>
@@ -4248,7 +4246,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>540</v>
       </c>
@@ -4259,7 +4257,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>541</v>
       </c>
@@ -4270,7 +4268,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>542</v>
       </c>
@@ -4281,7 +4279,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>543</v>
       </c>
@@ -4292,7 +4290,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>544</v>
       </c>
@@ -4303,7 +4301,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>545</v>
       </c>
@@ -4314,7 +4312,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>546</v>
       </c>
@@ -4325,7 +4323,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>547</v>
       </c>
@@ -4336,7 +4334,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>548</v>
       </c>
@@ -4347,7 +4345,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>549</v>
       </c>
@@ -4358,7 +4356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>550</v>
       </c>
@@ -4369,7 +4367,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>551</v>
       </c>
@@ -4380,7 +4378,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>552</v>
       </c>
@@ -4391,7 +4389,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>553</v>
       </c>
@@ -4402,7 +4400,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>554</v>
       </c>
@@ -4413,7 +4411,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>555</v>
       </c>
@@ -4424,7 +4422,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>556</v>
       </c>
@@ -4435,7 +4433,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>557</v>
       </c>
@@ -4446,7 +4444,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>558</v>
       </c>
@@ -4457,7 +4455,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>559</v>
       </c>
@@ -4468,7 +4466,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>560</v>
       </c>
@@ -4479,7 +4477,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>561</v>
       </c>
@@ -4490,7 +4488,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>562</v>
       </c>
@@ -4501,7 +4499,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>563</v>
       </c>
@@ -4512,7 +4510,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>564</v>
       </c>
@@ -4523,7 +4521,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>565</v>
       </c>
@@ -4534,7 +4532,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>566</v>
       </c>
@@ -4545,7 +4543,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>567</v>
       </c>
@@ -4556,7 +4554,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>568</v>
       </c>
@@ -4567,7 +4565,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>569</v>
       </c>
@@ -4578,7 +4576,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>570</v>
       </c>
@@ -4589,7 +4587,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>571</v>
       </c>
@@ -4600,7 +4598,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>572</v>
       </c>
@@ -4611,7 +4609,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>573</v>
       </c>
@@ -4622,7 +4620,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>574</v>
       </c>
@@ -4633,7 +4631,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>575</v>
       </c>
@@ -4644,7 +4642,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>576</v>
       </c>
@@ -4655,7 +4653,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>577</v>
       </c>
@@ -4666,7 +4664,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>578</v>
       </c>
@@ -4677,7 +4675,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>579</v>
       </c>
@@ -4688,7 +4686,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>580</v>
       </c>
@@ -4699,7 +4697,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>581</v>
       </c>
@@ -4710,7 +4708,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>582</v>
       </c>
@@ -4721,7 +4719,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>583</v>
       </c>
@@ -4732,7 +4730,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>584</v>
       </c>
@@ -4743,7 +4741,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>585</v>
       </c>
@@ -4754,7 +4752,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>586</v>
       </c>
@@ -4765,7 +4763,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>587</v>
       </c>
@@ -4776,7 +4774,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>588</v>
       </c>
@@ -4787,7 +4785,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>589</v>
       </c>
@@ -4798,7 +4796,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>590</v>
       </c>
@@ -4809,7 +4807,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>658</v>
       </c>
@@ -4820,7 +4818,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>659</v>
       </c>
@@ -4831,7 +4829,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>660</v>
       </c>
@@ -4842,7 +4840,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>661</v>
       </c>
@@ -4853,7 +4851,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>662</v>
       </c>
@@ -4864,7 +4862,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>663</v>
       </c>
@@ -4875,7 +4873,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>664</v>
       </c>
@@ -4886,7 +4884,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>665</v>
       </c>
@@ -4897,7 +4895,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>666</v>
       </c>
@@ -4908,7 +4906,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>668</v>
       </c>
@@ -4919,7 +4917,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>591</v>
       </c>
@@ -4930,7 +4928,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>592</v>
       </c>
@@ -4941,7 +4939,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>593</v>
       </c>
@@ -4952,7 +4950,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>594</v>
       </c>
@@ -4963,7 +4961,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>667</v>
       </c>
@@ -4974,7 +4972,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>669</v>
       </c>
@@ -4985,7 +4983,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>670</v>
       </c>
@@ -4996,7 +4994,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>671</v>
       </c>
@@ -5007,7 +5005,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>672</v>
       </c>
@@ -5018,7 +5016,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>673</v>
       </c>
@@ -5029,7 +5027,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>674</v>
       </c>
@@ -5040,7 +5038,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>675</v>
       </c>
@@ -5051,7 +5049,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>676</v>
       </c>
@@ -5062,7 +5060,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>677</v>
       </c>
@@ -5073,7 +5071,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>595</v>
       </c>
@@ -5084,7 +5082,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>596</v>
       </c>
@@ -5095,7 +5093,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>678</v>
       </c>
@@ -5106,7 +5104,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>679</v>
       </c>
@@ -5117,7 +5115,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>597</v>
       </c>
@@ -5128,7 +5126,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>598</v>
       </c>
@@ -5139,7 +5137,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>599</v>
       </c>
@@ -5150,7 +5148,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>600</v>
       </c>
@@ -5161,7 +5159,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>601</v>
       </c>
@@ -5172,7 +5170,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>602</v>
       </c>
@@ -5183,7 +5181,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>603</v>
       </c>
@@ -5194,7 +5192,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>604</v>
       </c>
@@ -5205,7 +5203,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>605</v>
       </c>
@@ -5216,7 +5214,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>692</v>
       </c>
@@ -5227,7 +5225,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>693</v>
       </c>
@@ -5238,7 +5236,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>606</v>
       </c>
@@ -5249,7 +5247,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>607</v>
       </c>
@@ -5260,7 +5258,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>608</v>
       </c>
@@ -5271,7 +5269,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>609</v>
       </c>
@@ -5282,7 +5280,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>610</v>
       </c>
@@ -5293,7 +5291,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>611</v>
       </c>
@@ -5304,7 +5302,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>612</v>
       </c>
@@ -5315,7 +5313,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>613</v>
       </c>
@@ -5326,7 +5324,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>614</v>
       </c>
@@ -5337,7 +5335,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>615</v>
       </c>
@@ -5348,7 +5346,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>616</v>
       </c>
@@ -5359,7 +5357,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>617</v>
       </c>
@@ -5370,7 +5368,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>618</v>
       </c>
@@ -5381,7 +5379,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>619</v>
       </c>
@@ -5392,7 +5390,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>620</v>
       </c>
@@ -5403,7 +5401,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>621</v>
       </c>
@@ -5414,7 +5412,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>622</v>
       </c>
@@ -5425,7 +5423,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="15" t="s">
         <v>680</v>
       </c>
@@ -5436,7 +5434,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="15" t="s">
         <v>681</v>
       </c>
@@ -5447,7 +5445,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="15" t="s">
         <v>623</v>
       </c>
@@ -5458,7 +5456,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="15" t="s">
         <v>624</v>
       </c>
@@ -5469,7 +5467,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="15" t="s">
         <v>625</v>
       </c>
@@ -5480,7 +5478,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="15" t="s">
         <v>626</v>
       </c>
@@ -5491,7 +5489,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="15" t="s">
         <v>627</v>
       </c>
@@ -5502,7 +5500,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="15" t="s">
         <v>628</v>
       </c>
@@ -5513,7 +5511,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="15" t="s">
         <v>629</v>
       </c>
@@ -5524,7 +5522,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="15" t="s">
         <v>630</v>
       </c>
@@ -5535,7 +5533,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="15" t="s">
         <v>631</v>
       </c>
@@ -5546,7 +5544,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="15" t="s">
         <v>632</v>
       </c>
@@ -5557,7 +5555,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="15" t="s">
         <v>633</v>
       </c>
@@ -5568,7 +5566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="15" t="s">
         <v>652</v>
       </c>
@@ -5579,7 +5577,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="15" t="s">
         <v>653</v>
       </c>
@@ -5590,7 +5588,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="15" t="s">
         <v>654</v>
       </c>
@@ -5601,7 +5599,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="15" t="s">
         <v>655</v>
       </c>
@@ -5612,7 +5610,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="15" t="s">
         <v>650</v>
       </c>
@@ -5623,7 +5621,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="15" t="s">
         <v>651</v>
       </c>
@@ -5689,14 +5687,25 @@
         <v>397</v>
       </c>
     </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="15" t="s">
+        <v>711</v>
+      </c>
+      <c r="B270" s="15" t="s">
+        <v>696</v>
+      </c>
+      <c r="C270" s="3" t="s">
+        <v>712</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:C264" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A2:C269" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C269">
-      <sortCondition ref="A2:A264"/>
+      <sortCondition ref="A2:A269"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A270:A1048576 A1:A53 A58:A264">
+  <conditionalFormatting sqref="A1:A53 A58:A264 A270:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>

--- a/Symbols_UpdateReferenceID.xlsx
+++ b/Symbols_UpdateReferenceID.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DISCDEXPI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mso\Desktop\todo\discII\github\DISCDEXPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF25E484-CEE5-43E7-8FEA-7AE7894E6738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{D5E47F2D-020A-4A1E-8973-8478EA58E23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Symbols" sheetId="1" r:id="rId1"/>
@@ -25,9 +25,9 @@
     <definedName name="RowEnd">Symbols!$B$1</definedName>
     <definedName name="RowStart">Symbols!$A$1</definedName>
     <definedName name="TR1970id">#REF!</definedName>
-    <definedName name="Z004id">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -55,27 +55,27 @@
   <commentList>
     <comment ref="C24" authorId="0" shapeId="0" xr:uid="{A32D579A-03F5-456F-BA00-67936BD401D0}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     MCC/VSD/THY/MCS
-Reply:
+Antwort:
     Must support signal connection</t>
       </text>
     </comment>
     <comment ref="C139" authorId="1" shapeId="0" xr:uid="{36C2758C-D037-4478-BDED-0DD258CAD031}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     No signal</t>
       </text>
     </comment>
     <comment ref="C140" authorId="2" shapeId="0" xr:uid="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     No Signal - in-line</t>
       </text>
     </comment>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="719">
   <si>
     <t>Description</t>
   </si>
@@ -2228,6 +2228,24 @@
   </si>
   <si>
     <t>Electric Gas Heater</t>
+  </si>
+  <si>
+    <t>ND0251</t>
+  </si>
+  <si>
+    <t>Nozzle Hose Connector</t>
+  </si>
+  <si>
+    <t>ND0252</t>
+  </si>
+  <si>
+    <t>Demisting Cyclone Part</t>
+  </si>
+  <si>
+    <t>ND0253</t>
+  </si>
+  <si>
+    <t>Vessel Insulation</t>
   </si>
 </sst>
 </file>
@@ -2348,7 +2366,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2372,10 +2390,12 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -2413,9 +2433,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2453,7 +2473,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2559,7 +2579,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2727,19 +2747,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C270"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C273"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="9" customWidth="1"/>
-    <col min="3" max="3" width="197.42578125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="197.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="6"/>
       <c r="C1" s="4"/>
     </row>
-    <row r="2" spans="1:3" s="1" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>694</v>
       </c>
@@ -2750,7 +2770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>391</v>
       </c>
@@ -2761,7 +2781,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>352</v>
       </c>
@@ -2772,7 +2792,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>1</v>
       </c>
@@ -2783,7 +2803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>347</v>
       </c>
@@ -2794,7 +2814,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>349</v>
       </c>
@@ -2805,7 +2825,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>351</v>
       </c>
@@ -2816,7 +2836,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>13</v>
       </c>
@@ -2827,7 +2847,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>14</v>
       </c>
@@ -2838,7 +2858,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>634</v>
       </c>
@@ -2849,7 +2869,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>635</v>
       </c>
@@ -2860,7 +2880,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>636</v>
       </c>
@@ -2871,7 +2891,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>637</v>
       </c>
@@ -2882,7 +2902,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>18</v>
       </c>
@@ -2893,7 +2913,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>46</v>
       </c>
@@ -2904,7 +2924,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>399</v>
       </c>
@@ -2915,7 +2935,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>53</v>
       </c>
@@ -2926,7 +2946,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>236</v>
       </c>
@@ -2937,7 +2957,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>358</v>
       </c>
@@ -2948,7 +2968,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>296</v>
       </c>
@@ -2959,7 +2979,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>364</v>
       </c>
@@ -2970,7 +2990,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>365</v>
       </c>
@@ -2981,7 +3001,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>366</v>
       </c>
@@ -2992,7 +3012,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>367</v>
       </c>
@@ -3003,7 +3023,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>369</v>
       </c>
@@ -3014,7 +3034,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>370</v>
       </c>
@@ -3025,7 +3045,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>377</v>
       </c>
@@ -3036,7 +3056,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
         <v>380</v>
       </c>
@@ -3047,7 +3067,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
         <v>381</v>
       </c>
@@ -3058,7 +3078,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
         <v>383</v>
       </c>
@@ -3069,7 +3089,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
         <v>384</v>
       </c>
@@ -3080,7 +3100,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
         <v>386</v>
       </c>
@@ -3091,7 +3111,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>387</v>
       </c>
@@ -3102,7 +3122,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
         <v>404</v>
       </c>
@@ -3113,7 +3133,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
         <v>388</v>
       </c>
@@ -3124,7 +3144,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
         <v>405</v>
       </c>
@@ -3135,7 +3155,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="15" t="s">
         <v>389</v>
       </c>
@@ -3146,7 +3166,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
         <v>394</v>
       </c>
@@ -3157,7 +3177,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="15" t="s">
         <v>395</v>
       </c>
@@ -3168,7 +3188,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
         <v>638</v>
       </c>
@@ -3179,7 +3199,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="15" t="s">
         <v>639</v>
       </c>
@@ -3190,7 +3210,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
         <v>640</v>
       </c>
@@ -3201,7 +3221,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="15" t="s">
         <v>641</v>
       </c>
@@ -3212,7 +3232,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
         <v>442</v>
       </c>
@@ -3223,7 +3243,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="15" t="s">
         <v>444</v>
       </c>
@@ -3234,7 +3254,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="15" t="s">
         <v>445</v>
       </c>
@@ -3245,7 +3265,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="15" t="s">
         <v>447</v>
       </c>
@@ -3256,7 +3276,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
         <v>449</v>
       </c>
@@ -3267,7 +3287,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
         <v>453</v>
       </c>
@@ -3278,7 +3298,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="15" t="s">
         <v>455</v>
       </c>
@@ -3289,7 +3309,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="15" t="s">
         <v>457</v>
       </c>
@@ -3300,7 +3320,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
         <v>459</v>
       </c>
@@ -3311,7 +3331,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>703</v>
       </c>
@@ -3322,7 +3342,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>704</v>
       </c>
@@ -3333,7 +3353,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>705</v>
       </c>
@@ -3344,7 +3364,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>706</v>
       </c>
@@ -3355,7 +3375,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>461</v>
       </c>
@@ -3366,7 +3386,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>462</v>
       </c>
@@ -3377,7 +3397,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>463</v>
       </c>
@@ -3388,7 +3408,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>464</v>
       </c>
@@ -3399,7 +3419,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>465</v>
       </c>
@@ -3410,7 +3430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>466</v>
       </c>
@@ -3421,7 +3441,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>467</v>
       </c>
@@ -3432,7 +3452,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>468</v>
       </c>
@@ -3443,7 +3463,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>469</v>
       </c>
@@ -3454,7 +3474,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>470</v>
       </c>
@@ -3465,7 +3485,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>471</v>
       </c>
@@ -3476,7 +3496,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>472</v>
       </c>
@@ -3487,7 +3507,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>473</v>
       </c>
@@ -3498,7 +3518,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>474</v>
       </c>
@@ -3509,7 +3529,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>475</v>
       </c>
@@ -3520,7 +3540,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>476</v>
       </c>
@@ -3531,7 +3551,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>477</v>
       </c>
@@ -3542,7 +3562,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>478</v>
       </c>
@@ -3553,7 +3573,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>479</v>
       </c>
@@ -3564,7 +3584,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>480</v>
       </c>
@@ -3575,7 +3595,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>481</v>
       </c>
@@ -3586,7 +3606,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>482</v>
       </c>
@@ -3597,7 +3617,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>483</v>
       </c>
@@ -3608,7 +3628,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>484</v>
       </c>
@@ -3619,7 +3639,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>485</v>
       </c>
@@ -3630,7 +3650,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>486</v>
       </c>
@@ -3641,7 +3661,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>487</v>
       </c>
@@ -3652,7 +3672,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>488</v>
       </c>
@@ -3663,7 +3683,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>489</v>
       </c>
@@ -3674,7 +3694,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>490</v>
       </c>
@@ -3685,7 +3705,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>491</v>
       </c>
@@ -3696,7 +3716,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>492</v>
       </c>
@@ -3707,7 +3727,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>493</v>
       </c>
@@ -3718,7 +3738,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>494</v>
       </c>
@@ -3729,7 +3749,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>691</v>
       </c>
@@ -3740,7 +3760,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93" s="16" t="s">
         <v>702</v>
       </c>
@@ -3751,7 +3771,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>495</v>
       </c>
@@ -3762,7 +3782,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>496</v>
       </c>
@@ -3773,7 +3793,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>497</v>
       </c>
@@ -3784,7 +3804,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>498</v>
       </c>
@@ -3795,7 +3815,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>499</v>
       </c>
@@ -3806,7 +3826,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>500</v>
       </c>
@@ -3817,7 +3837,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>501</v>
       </c>
@@ -3828,7 +3848,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>502</v>
       </c>
@@ -3839,7 +3859,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>503</v>
       </c>
@@ -3850,7 +3870,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>504</v>
       </c>
@@ -3861,7 +3881,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>505</v>
       </c>
@@ -3872,7 +3892,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>506</v>
       </c>
@@ -3883,7 +3903,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>507</v>
       </c>
@@ -3894,7 +3914,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>508</v>
       </c>
@@ -3905,7 +3925,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>509</v>
       </c>
@@ -3916,7 +3936,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>510</v>
       </c>
@@ -3927,7 +3947,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>511</v>
       </c>
@@ -3938,7 +3958,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>512</v>
       </c>
@@ -3949,7 +3969,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>513</v>
       </c>
@@ -3960,7 +3980,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>514</v>
       </c>
@@ -3971,7 +3991,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>515</v>
       </c>
@@ -3982,7 +4002,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>516</v>
       </c>
@@ -3993,7 +4013,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>517</v>
       </c>
@@ -4004,7 +4024,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>518</v>
       </c>
@@ -4015,7 +4035,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>519</v>
       </c>
@@ -4026,7 +4046,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>520</v>
       </c>
@@ -4037,7 +4057,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>521</v>
       </c>
@@ -4048,7 +4068,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>522</v>
       </c>
@@ -4059,7 +4079,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>523</v>
       </c>
@@ -4070,7 +4090,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>524</v>
       </c>
@@ -4081,7 +4101,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>525</v>
       </c>
@@ -4092,7 +4112,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>526</v>
       </c>
@@ -4103,7 +4123,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>527</v>
       </c>
@@ -4114,7 +4134,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>528</v>
       </c>
@@ -4125,7 +4145,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>529</v>
       </c>
@@ -4136,7 +4156,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>530</v>
       </c>
@@ -4147,7 +4167,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>531</v>
       </c>
@@ -4158,7 +4178,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>532</v>
       </c>
@@ -4169,7 +4189,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>533</v>
       </c>
@@ -4180,7 +4200,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>534</v>
       </c>
@@ -4191,7 +4211,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>535</v>
       </c>
@@ -4202,7 +4222,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>536</v>
       </c>
@@ -4213,7 +4233,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>537</v>
       </c>
@@ -4224,7 +4244,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>538</v>
       </c>
@@ -4235,7 +4255,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>539</v>
       </c>
@@ -4246,7 +4266,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>540</v>
       </c>
@@ -4257,7 +4277,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>541</v>
       </c>
@@ -4268,7 +4288,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>542</v>
       </c>
@@ -4279,7 +4299,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>543</v>
       </c>
@@ -4290,7 +4310,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>544</v>
       </c>
@@ -4301,7 +4321,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>545</v>
       </c>
@@ -4312,7 +4332,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>546</v>
       </c>
@@ -4323,7 +4343,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>547</v>
       </c>
@@ -4334,7 +4354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>548</v>
       </c>
@@ -4345,7 +4365,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>549</v>
       </c>
@@ -4356,7 +4376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>550</v>
       </c>
@@ -4367,7 +4387,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>551</v>
       </c>
@@ -4378,7 +4398,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>552</v>
       </c>
@@ -4389,7 +4409,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>553</v>
       </c>
@@ -4400,7 +4420,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>554</v>
       </c>
@@ -4411,7 +4431,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>555</v>
       </c>
@@ -4422,7 +4442,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>556</v>
       </c>
@@ -4433,7 +4453,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>557</v>
       </c>
@@ -4444,7 +4464,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>558</v>
       </c>
@@ -4455,7 +4475,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>559</v>
       </c>
@@ -4466,7 +4486,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>560</v>
       </c>
@@ -4477,7 +4497,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>561</v>
       </c>
@@ -4488,7 +4508,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>562</v>
       </c>
@@ -4499,7 +4519,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>563</v>
       </c>
@@ -4510,7 +4530,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>564</v>
       </c>
@@ -4521,7 +4541,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>565</v>
       </c>
@@ -4532,7 +4552,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>566</v>
       </c>
@@ -4543,7 +4563,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>567</v>
       </c>
@@ -4554,7 +4574,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>568</v>
       </c>
@@ -4565,7 +4585,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>569</v>
       </c>
@@ -4576,7 +4596,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>570</v>
       </c>
@@ -4587,7 +4607,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>571</v>
       </c>
@@ -4598,7 +4618,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>572</v>
       </c>
@@ -4609,7 +4629,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>573</v>
       </c>
@@ -4620,7 +4640,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>574</v>
       </c>
@@ -4631,7 +4651,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>575</v>
       </c>
@@ -4642,7 +4662,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>576</v>
       </c>
@@ -4653,7 +4673,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>577</v>
       </c>
@@ -4664,7 +4684,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>578</v>
       </c>
@@ -4675,7 +4695,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>579</v>
       </c>
@@ -4686,7 +4706,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>580</v>
       </c>
@@ -4697,7 +4717,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>581</v>
       </c>
@@ -4708,7 +4728,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>582</v>
       </c>
@@ -4719,7 +4739,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>583</v>
       </c>
@@ -4730,7 +4750,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>584</v>
       </c>
@@ -4741,7 +4761,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>585</v>
       </c>
@@ -4752,7 +4772,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>586</v>
       </c>
@@ -4763,7 +4783,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>587</v>
       </c>
@@ -4774,7 +4794,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>588</v>
       </c>
@@ -4785,7 +4805,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>589</v>
       </c>
@@ -4796,7 +4816,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>590</v>
       </c>
@@ -4807,7 +4827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>658</v>
       </c>
@@ -4818,7 +4838,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>659</v>
       </c>
@@ -4829,7 +4849,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>660</v>
       </c>
@@ -4840,7 +4860,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>661</v>
       </c>
@@ -4851,7 +4871,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>662</v>
       </c>
@@ -4862,7 +4882,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>663</v>
       </c>
@@ -4873,7 +4893,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>664</v>
       </c>
@@ -4884,7 +4904,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>665</v>
       </c>
@@ -4895,7 +4915,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>666</v>
       </c>
@@ -4906,7 +4926,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>668</v>
       </c>
@@ -4917,7 +4937,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>591</v>
       </c>
@@ -4928,7 +4948,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>592</v>
       </c>
@@ -4939,7 +4959,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>593</v>
       </c>
@@ -4950,7 +4970,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>594</v>
       </c>
@@ -4961,7 +4981,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>667</v>
       </c>
@@ -4972,7 +4992,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>669</v>
       </c>
@@ -4983,7 +5003,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>670</v>
       </c>
@@ -4994,7 +5014,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>671</v>
       </c>
@@ -5005,7 +5025,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>672</v>
       </c>
@@ -5016,7 +5036,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>673</v>
       </c>
@@ -5027,7 +5047,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>674</v>
       </c>
@@ -5038,7 +5058,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>675</v>
       </c>
@@ -5049,7 +5069,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>676</v>
       </c>
@@ -5060,7 +5080,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>677</v>
       </c>
@@ -5071,7 +5091,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>595</v>
       </c>
@@ -5082,7 +5102,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>596</v>
       </c>
@@ -5093,7 +5113,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>678</v>
       </c>
@@ -5104,7 +5124,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>679</v>
       </c>
@@ -5115,7 +5135,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>597</v>
       </c>
@@ -5126,7 +5146,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>598</v>
       </c>
@@ -5137,7 +5157,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>599</v>
       </c>
@@ -5148,7 +5168,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>600</v>
       </c>
@@ -5159,7 +5179,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>601</v>
       </c>
@@ -5170,7 +5190,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>602</v>
       </c>
@@ -5181,7 +5201,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>603</v>
       </c>
@@ -5192,7 +5212,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>604</v>
       </c>
@@ -5203,7 +5223,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>605</v>
       </c>
@@ -5214,7 +5234,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>692</v>
       </c>
@@ -5225,7 +5245,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>693</v>
       </c>
@@ -5236,7 +5256,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>606</v>
       </c>
@@ -5247,7 +5267,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>607</v>
       </c>
@@ -5258,7 +5278,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>608</v>
       </c>
@@ -5269,7 +5289,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>609</v>
       </c>
@@ -5280,7 +5300,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>610</v>
       </c>
@@ -5291,7 +5311,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>611</v>
       </c>
@@ -5302,7 +5322,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>612</v>
       </c>
@@ -5313,7 +5333,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>613</v>
       </c>
@@ -5324,7 +5344,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>614</v>
       </c>
@@ -5335,7 +5355,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>615</v>
       </c>
@@ -5346,7 +5366,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>616</v>
       </c>
@@ -5357,7 +5377,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>617</v>
       </c>
@@ -5368,7 +5388,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>618</v>
       </c>
@@ -5379,7 +5399,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>619</v>
       </c>
@@ -5390,7 +5410,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>620</v>
       </c>
@@ -5401,7 +5421,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>621</v>
       </c>
@@ -5412,7 +5432,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>622</v>
       </c>
@@ -5423,7 +5443,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A246" s="15" t="s">
         <v>680</v>
       </c>
@@ -5434,7 +5454,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247" s="15" t="s">
         <v>681</v>
       </c>
@@ -5445,7 +5465,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" s="15" t="s">
         <v>623</v>
       </c>
@@ -5456,7 +5476,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A249" s="15" t="s">
         <v>624</v>
       </c>
@@ -5467,7 +5487,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" s="15" t="s">
         <v>625</v>
       </c>
@@ -5478,7 +5498,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" s="15" t="s">
         <v>626</v>
       </c>
@@ -5489,7 +5509,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252" s="15" t="s">
         <v>627</v>
       </c>
@@ -5500,7 +5520,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A253" s="15" t="s">
         <v>628</v>
       </c>
@@ -5511,7 +5531,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" s="15" t="s">
         <v>629</v>
       </c>
@@ -5522,7 +5542,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" s="15" t="s">
         <v>630</v>
       </c>
@@ -5533,7 +5553,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" s="15" t="s">
         <v>631</v>
       </c>
@@ -5544,7 +5564,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257" s="15" t="s">
         <v>632</v>
       </c>
@@ -5555,7 +5575,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A258" s="15" t="s">
         <v>633</v>
       </c>
@@ -5566,7 +5586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259" s="15" t="s">
         <v>652</v>
       </c>
@@ -5577,7 +5597,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260" s="15" t="s">
         <v>653</v>
       </c>
@@ -5588,7 +5608,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" s="15" t="s">
         <v>654</v>
       </c>
@@ -5599,7 +5619,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" s="15" t="s">
         <v>655</v>
       </c>
@@ -5610,7 +5630,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263" s="15" t="s">
         <v>650</v>
       </c>
@@ -5621,7 +5641,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264" s="15" t="s">
         <v>651</v>
       </c>
@@ -5632,7 +5652,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" s="16" t="s">
         <v>697</v>
       </c>
@@ -5643,7 +5663,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A266" s="16" t="s">
         <v>698</v>
       </c>
@@ -5654,7 +5674,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" s="16" t="s">
         <v>699</v>
       </c>
@@ -5665,7 +5685,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" s="16" t="s">
         <v>700</v>
       </c>
@@ -5676,7 +5696,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269" s="16" t="s">
         <v>701</v>
       </c>
@@ -5687,7 +5707,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" s="15" t="s">
         <v>711</v>
       </c>
@@ -5696,6 +5716,39 @@
       </c>
       <c r="C270" s="3" t="s">
         <v>712</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" s="17" t="s">
+        <v>713</v>
+      </c>
+      <c r="B271" s="18" t="s">
+        <v>696</v>
+      </c>
+      <c r="C271" s="3" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" s="17" t="s">
+        <v>715</v>
+      </c>
+      <c r="B272" s="18" t="s">
+        <v>696</v>
+      </c>
+      <c r="C272" s="3" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="B273" s="18" t="s">
+        <v>696</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>718</v>
       </c>
     </row>
   </sheetData>

--- a/Symbols_UpdateReferenceID.xlsx
+++ b/Symbols_UpdateReferenceID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mso\Desktop\todo\discII\github\DISCDEXPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{D5E47F2D-020A-4A1E-8973-8478EA58E23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FC214E-C1B0-4464-A3D9-8D1AAE8A5120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,6 @@
     <definedName name="TR1970id">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -84,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="723">
   <si>
     <t>Description</t>
   </si>
@@ -2246,6 +2245,18 @@
   </si>
   <si>
     <t>Vessel Insulation</t>
+  </si>
+  <si>
+    <t>ND0254</t>
+  </si>
+  <si>
+    <t>Bunded Area</t>
+  </si>
+  <si>
+    <t>ND0255</t>
+  </si>
+  <si>
+    <t>General Pump</t>
   </si>
 </sst>
 </file>
@@ -2366,7 +2377,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2390,7 +2401,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -2747,7 +2757,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C273"/>
+  <dimension ref="A1:C275"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
@@ -5719,10 +5729,10 @@
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A271" s="17" t="s">
+      <c r="A271" t="s">
         <v>713</v>
       </c>
-      <c r="B271" s="18" t="s">
+      <c r="B271" s="17" t="s">
         <v>696</v>
       </c>
       <c r="C271" s="3" t="s">
@@ -5730,10 +5740,10 @@
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A272" s="17" t="s">
+      <c r="A272" t="s">
         <v>715</v>
       </c>
-      <c r="B272" s="18" t="s">
+      <c r="B272" s="17" t="s">
         <v>696</v>
       </c>
       <c r="C272" s="3" t="s">
@@ -5741,14 +5751,36 @@
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A273" s="17" t="s">
+      <c r="A273" t="s">
         <v>717</v>
       </c>
-      <c r="B273" s="18" t="s">
+      <c r="B273" s="17" t="s">
         <v>696</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>718</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>719</v>
+      </c>
+      <c r="B274" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="C274" s="3" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>721</v>
+      </c>
+      <c r="B275" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="C275" s="3" t="s">
+        <v>722</v>
       </c>
     </row>
   </sheetData>

--- a/Symbols_UpdateReferenceID.xlsx
+++ b/Symbols_UpdateReferenceID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mso\Desktop\todo\discII\github\DISCDEXPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FC214E-C1B0-4464-A3D9-8D1AAE8A5120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC800FE-EF02-405A-BF31-3467F0D55AE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="524" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Symbols" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Symbols!$A$2:$C$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Symbols!$A$2:$C$195</definedName>
     <definedName name="DEXPI_CLASS">#REF!</definedName>
     <definedName name="DEXPI_PACKAGE">#REF!</definedName>
     <definedName name="map">#REF!</definedName>
@@ -47,22 +47,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={A32D579A-03F5-456F-BA00-67936BD401D0}</author>
     <author>tc={36C2758C-D037-4478-BDED-0DD258CAD031}</author>
     <author>tc={FBC2CACE-2F03-4DAC-8894-89865648F172}</author>
   </authors>
   <commentList>
-    <comment ref="C24" authorId="0" shapeId="0" xr:uid="{A32D579A-03F5-456F-BA00-67936BD401D0}">
-      <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
-    MCC/VSD/THY/MCS
-Antwort:
-    Must support signal connection</t>
-      </text>
-    </comment>
-    <comment ref="C139" authorId="1" shapeId="0" xr:uid="{36C2758C-D037-4478-BDED-0DD258CAD031}">
+    <comment ref="C84" authorId="0" shapeId="0" xr:uid="{36C2758C-D037-4478-BDED-0DD258CAD031}">
       <text>
         <t>[Kommentarthread]
 Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -70,7 +59,7 @@
     No signal</t>
       </text>
     </comment>
-    <comment ref="C140" authorId="2" shapeId="0" xr:uid="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
+    <comment ref="C85" authorId="1" shapeId="0" xr:uid="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
       <text>
         <t>[Kommentarthread]
 Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
@@ -83,17 +72,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="581">
   <si>
     <t>Description</t>
   </si>
   <si>
-    <t>ND0002</t>
-  </si>
-  <si>
-    <t>NozzleTee</t>
-  </si>
-  <si>
     <t>PA001A</t>
   </si>
   <si>
@@ -124,24 +107,6 @@
     <t>PV005A</t>
   </si>
   <si>
-    <t>ND0006</t>
-  </si>
-  <si>
-    <t>ND0007</t>
-  </si>
-  <si>
-    <t>Property Break</t>
-  </si>
-  <si>
-    <t>OPC Flow Right</t>
-  </si>
-  <si>
-    <t>OPC Flow Left</t>
-  </si>
-  <si>
-    <t>ND0010</t>
-  </si>
-  <si>
     <t>PE001A</t>
   </si>
   <si>
@@ -196,12 +161,6 @@
     <t>Open or Tundish Drain</t>
   </si>
   <si>
-    <t>Flow Direction</t>
-  </si>
-  <si>
-    <t>Function available on VDU</t>
-  </si>
-  <si>
     <t>Manway</t>
   </si>
   <si>
@@ -223,9 +182,6 @@
     <t>Piston</t>
   </si>
   <si>
-    <t>ND0012</t>
-  </si>
-  <si>
     <t>PA002A</t>
   </si>
   <si>
@@ -244,9 +200,6 @@
     <t>Exch. Compact Heat</t>
   </si>
   <si>
-    <t>ND0013</t>
-  </si>
-  <si>
     <t>PE011A</t>
   </si>
   <si>
@@ -331,15 +284,9 @@
     <t>PV016A</t>
   </si>
   <si>
-    <t>Valve Plug</t>
-  </si>
-  <si>
     <t>PV023A</t>
   </si>
   <si>
-    <t>Self Acting Reduction Valve</t>
-  </si>
-  <si>
     <t>Valve Block Bleed</t>
   </si>
   <si>
@@ -742,9 +689,6 @@
     <t>Flow T. Vortex</t>
   </si>
   <si>
-    <t>Flowmeter</t>
-  </si>
-  <si>
     <t>PF004A</t>
   </si>
   <si>
@@ -793,9 +737,6 @@
     <t>PF015A</t>
   </si>
   <si>
-    <t>ND0014</t>
-  </si>
-  <si>
     <t>Special Item</t>
   </si>
   <si>
@@ -973,12 +914,6 @@
     <t>Tank Tote</t>
   </si>
   <si>
-    <t>ND0016</t>
-  </si>
-  <si>
-    <t>Radioactive Source</t>
-  </si>
-  <si>
     <t>Flow Control Check Valve</t>
   </si>
   <si>
@@ -1126,84 +1061,12 @@
     <t>IM017B</t>
   </si>
   <si>
-    <t>ND0003</t>
-  </si>
-  <si>
-    <t>Non SAS Function in CCR</t>
-  </si>
-  <si>
-    <t>ND0004</t>
-  </si>
-  <si>
-    <t>Modular Valve Double Isolation and Bleed</t>
-  </si>
-  <si>
-    <t>ND0005</t>
-  </si>
-  <si>
-    <t>ND0001</t>
-  </si>
-  <si>
-    <t>Flexible Hose With Couplings</t>
-  </si>
-  <si>
-    <t>Nozzle</t>
-  </si>
-  <si>
-    <t>Modular Valve Double Block Bleed and Check</t>
-  </si>
-  <si>
-    <t>Thermowell</t>
-  </si>
-  <si>
-    <t>Misc Vessel Column</t>
-  </si>
-  <si>
-    <t>ND0015</t>
-  </si>
-  <si>
-    <t>Level Profiler</t>
-  </si>
-  <si>
     <t>Flow T. Flow Glass</t>
   </si>
   <si>
-    <t>Coriolis Flowmeter</t>
-  </si>
-  <si>
     <t>Diaphragm Actuator</t>
   </si>
   <si>
-    <t>Pressure Safety Valve</t>
-  </si>
-  <si>
-    <t>ND0017</t>
-  </si>
-  <si>
-    <t>ND0018</t>
-  </si>
-  <si>
-    <t>ND0019</t>
-  </si>
-  <si>
-    <t>ND0020</t>
-  </si>
-  <si>
-    <t>Not In Use for NOAKA DEXPI</t>
-  </si>
-  <si>
-    <t>ND0021</t>
-  </si>
-  <si>
-    <t>ND0022</t>
-  </si>
-  <si>
-    <t>Instrument Electrical Powered Equipment</t>
-  </si>
-  <si>
-    <t>Field Operated PSV</t>
-  </si>
-  <si>
     <t>PZ011B</t>
   </si>
   <si>
@@ -1216,63 +1079,9 @@
     <t>Ejector</t>
   </si>
   <si>
-    <t>ND0023</t>
-  </si>
-  <si>
-    <t>Field Instrument Primary Mounted Accessable</t>
-  </si>
-  <si>
-    <t>Field Instrument Auxillary Mounted Accessable</t>
-  </si>
-  <si>
-    <t>ND0024</t>
-  </si>
-  <si>
-    <t>ND0025</t>
-  </si>
-  <si>
-    <t>Field Instrument Primary Mounted Inaccessable</t>
-  </si>
-  <si>
-    <t>ND0026</t>
-  </si>
-  <si>
-    <t>ND0027</t>
-  </si>
-  <si>
-    <t>Virtual Piping Connector</t>
-  </si>
-  <si>
-    <t>ND0028</t>
-  </si>
-  <si>
-    <t>ND0029</t>
-  </si>
-  <si>
-    <t>ND0030</t>
-  </si>
-  <si>
-    <t>ND0031</t>
-  </si>
-  <si>
-    <t>Flow in nozzle</t>
-  </si>
-  <si>
-    <t>ND0000</t>
-  </si>
-  <si>
     <t>Pressure Vessel</t>
   </si>
   <si>
-    <t>Clamp-on</t>
-  </si>
-  <si>
-    <t>ND0032</t>
-  </si>
-  <si>
-    <t>ND0033</t>
-  </si>
-  <si>
     <t>IM017C</t>
   </si>
   <si>
@@ -1282,37 +1091,6 @@
     <t>Shut Down - Arrow Down</t>
   </si>
   <si>
-    <t>ND0012A</t>
-  </si>
-  <si>
-    <t>Wedge Gate Valve (Manual Valve)</t>
-  </si>
-  <si>
-    <t>Wedge Gate Valve (actuated valve)</t>
-  </si>
-  <si>
-    <t>Double Isolation Ball Valve (DIB-2)
-1 double piston and 1 self relieving seat. (Manual valve)</t>
-  </si>
-  <si>
-    <t>Double Isolation Ball Valve (DIB-2)
-1 double piston and 1 self relieving seat. (Actuated Valve)</t>
-  </si>
-  <si>
-    <t>ND0029A</t>
-  </si>
-  <si>
-    <t>ND0030A</t>
-  </si>
-  <si>
-    <t>Double Isolation Ball Valve (DIB-1)
-2 double piston effect. (Manual Valve)</t>
-  </si>
-  <si>
-    <t>Double Isolation Ball Valve (DIB-1)
-2 double piston effect. (Actuated Valve)</t>
-  </si>
-  <si>
     <t>PV003B</t>
   </si>
   <si>
@@ -1412,67 +1190,9 @@
     <t>Valve Plug (Actuated Valve)</t>
   </si>
   <si>
-    <t>OPC Flow Out</t>
-  </si>
-  <si>
-    <t>ND0035</t>
-  </si>
-  <si>
-    <t>Level Element</t>
-  </si>
-  <si>
-    <t>ND0036</t>
-  </si>
-  <si>
-    <t>ND0037</t>
-  </si>
-  <si>
-    <t>Special Item (Piping Component)</t>
-  </si>
-  <si>
-    <t>ND0038</t>
-  </si>
-  <si>
-    <t>Unspecified Signal Connector: used as a signal line connection point to fix current drafting standard of signal connecting directly to another signal</t>
-  </si>
-  <si>
-    <t>ND0039</t>
-  </si>
-  <si>
-    <t>Special nozzle to be used to provide a 'mount-on' point.
-**Note: that the connection &amp; origo point is below the symbol - this displays graphically as a small gap between the mounted element and the base element.</t>
-  </si>
-  <si>
     <t>Separator Membrane</t>
   </si>
   <si>
-    <t>Level Well</t>
-  </si>
-  <si>
-    <t>ND0040</t>
-  </si>
-  <si>
-    <t>Label for pipeline</t>
-  </si>
-  <si>
-    <t>ND0041</t>
-  </si>
-  <si>
-    <t>Label for elevation</t>
-  </si>
-  <si>
-    <t>ND0042A</t>
-  </si>
-  <si>
-    <t>Axial Valve (Manual Valve)</t>
-  </si>
-  <si>
-    <t>ND0042B</t>
-  </si>
-  <si>
-    <t>Axial Valve (Actuated Valve)</t>
-  </si>
-  <si>
     <t>ND0048</t>
   </si>
   <si>
@@ -1959,111 +1679,9 @@
     <t>ND0224</t>
   </si>
   <si>
-    <t>ND0226</t>
-  </si>
-  <si>
-    <t>ND0227</t>
-  </si>
-  <si>
-    <t>ND0228</t>
-  </si>
-  <si>
-    <t>ND0236</t>
-  </si>
-  <si>
-    <t>ND0237</t>
-  </si>
-  <si>
-    <t>ND0238</t>
-  </si>
-  <si>
-    <t>ND0239</t>
-  </si>
-  <si>
-    <t>ND0240</t>
-  </si>
-  <si>
-    <t>ND0241</t>
-  </si>
-  <si>
-    <t>ND0242</t>
-  </si>
-  <si>
-    <t>ND0243</t>
-  </si>
-  <si>
-    <t>ND0008A</t>
-  </si>
-  <si>
-    <t>ND0008B</t>
-  </si>
-  <si>
-    <t>ND0009A</t>
-  </si>
-  <si>
-    <t>ND0009B</t>
-  </si>
-  <si>
-    <t>ND0034A</t>
-  </si>
-  <si>
-    <t>ND0034B</t>
-  </si>
-  <si>
-    <t>ND0034C</t>
-  </si>
-  <si>
-    <t>ND0034D</t>
-  </si>
-  <si>
-    <t>Vent To Safe</t>
-  </si>
-  <si>
     <t>Tray Tower</t>
   </si>
   <si>
-    <t>Monoflange Valve</t>
-  </si>
-  <si>
-    <t>Bucket Filter</t>
-  </si>
-  <si>
-    <t>Vane Type Distributer</t>
-  </si>
-  <si>
-    <t>Cyclone Mat</t>
-  </si>
-  <si>
-    <t>Electro Hydraulic Actuator</t>
-  </si>
-  <si>
-    <t>Area Break</t>
-  </si>
-  <si>
-    <t>ND0246</t>
-  </si>
-  <si>
-    <t>ND0247</t>
-  </si>
-  <si>
-    <t>ND0244A</t>
-  </si>
-  <si>
-    <t>ND0244B</t>
-  </si>
-  <si>
-    <t>ND0245A</t>
-  </si>
-  <si>
-    <t>ND0245B</t>
-  </si>
-  <si>
-    <t>Bird Screen</t>
-  </si>
-  <si>
-    <t>Vent Bird Screen</t>
-  </si>
-  <si>
     <t>ND0180A</t>
   </si>
   <si>
@@ -2130,39 +1748,6 @@
     <t>ND0196B</t>
   </si>
   <si>
-    <t>ND0225A</t>
-  </si>
-  <si>
-    <t>ND0225B</t>
-  </si>
-  <si>
-    <t>OPC Header Piping Flow In</t>
-  </si>
-  <si>
-    <t>OPC Header Piping Flow Out</t>
-  </si>
-  <si>
-    <t>OPC Piping Flow Bottom In</t>
-  </si>
-  <si>
-    <t>OPC Piping Flow Bottom Out</t>
-  </si>
-  <si>
-    <t>OPC Piping Flow Top In</t>
-  </si>
-  <si>
-    <t>OPC Piping Flow Top Out</t>
-  </si>
-  <si>
-    <t>Caisson</t>
-  </si>
-  <si>
-    <t>Strainer T Temporary</t>
-  </si>
-  <si>
-    <t>Wiremesh Demister</t>
-  </si>
-  <si>
     <t>ND0082A</t>
   </si>
   <si>
@@ -2178,9 +1763,6 @@
     <t>OLD SYMBOL ID</t>
   </si>
   <si>
-    <t>New symbol</t>
-  </si>
-  <si>
     <t>ND0248A</t>
   </si>
   <si>
@@ -2199,71 +1781,47 @@
     <t>ND0082B</t>
   </si>
   <si>
-    <t>ND0043</t>
-  </si>
-  <si>
-    <t>ND0044</t>
-  </si>
-  <si>
-    <t>ND0045</t>
-  </si>
-  <si>
-    <t>ND0046</t>
-  </si>
-  <si>
-    <t>Tie In Point Property Break</t>
-  </si>
-  <si>
-    <t>Custom Equipment Package</t>
-  </si>
-  <si>
-    <t>Mechanical Joint</t>
-  </si>
-  <si>
-    <t>Welded Joint</t>
-  </si>
-  <si>
-    <t>ND0250</t>
-  </si>
-  <si>
-    <t>Electric Gas Heater</t>
-  </si>
-  <si>
-    <t>ND0251</t>
-  </si>
-  <si>
-    <t>Nozzle Hose Connector</t>
-  </si>
-  <si>
-    <t>ND0252</t>
-  </si>
-  <si>
-    <t>Demisting Cyclone Part</t>
-  </si>
-  <si>
-    <t>ND0253</t>
-  </si>
-  <si>
-    <t>Vessel Insulation</t>
-  </si>
-  <si>
-    <t>ND0254</t>
-  </si>
-  <si>
-    <t>Bunded Area</t>
-  </si>
-  <si>
-    <t>ND0255</t>
-  </si>
-  <si>
-    <t>General Pump</t>
+    <t>VesselBoot</t>
+  </si>
+  <si>
+    <t>Internal heating coil</t>
+  </si>
+  <si>
+    <t>Drip pan</t>
+  </si>
+  <si>
+    <t>Insulation</t>
+  </si>
+  <si>
+    <t>Generic Exchanger</t>
+  </si>
+  <si>
+    <t>Vortex Breaker</t>
+  </si>
+  <si>
+    <t>Direct Heating Heater</t>
+  </si>
+  <si>
+    <t>Washing System</t>
+  </si>
+  <si>
+    <t>Chimney Tray</t>
+  </si>
+  <si>
+    <t>Internal Spray Nozzle</t>
+  </si>
+  <si>
+    <t>Tower packing</t>
+  </si>
+  <si>
+    <t>Inline Measuring Element</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2294,12 +1852,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF0070C0"/>
@@ -2323,30 +1875,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -2377,7 +1911,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2387,21 +1921,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -2739,16 +2262,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C24" dT="2022-01-14T15:23:40.44" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{A32D579A-03F5-456F-BA00-67936BD401D0}">
-    <text>MCC/VSD/THY/MCS</text>
-  </threadedComment>
-  <threadedComment ref="C24" dT="2022-01-14T15:24:43.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{67FB19B8-29DB-4553-BC61-721610DBDAD2}" parentId="{A32D579A-03F5-456F-BA00-67936BD401D0}">
-    <text>Must support signal connection</text>
-  </threadedComment>
-  <threadedComment ref="C139" dT="2022-01-14T13:33:08.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{36C2758C-D037-4478-BDED-0DD258CAD031}">
+  <threadedComment ref="C84" dT="2022-01-14T13:33:08.20" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{36C2758C-D037-4478-BDED-0DD258CAD031}">
     <text>No signal</text>
   </threadedComment>
-  <threadedComment ref="C140" dT="2022-01-14T13:33:16.93" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
+  <threadedComment ref="C85" dT="2022-01-14T13:33:16.93" personId="{3F66633E-8F29-4F58-8E88-3C7E28007978}" id="{FBC2CACE-2F03-4DAC-8894-89865648F172}">
     <text>No Signal - in-line</text>
   </threadedComment>
 </ThreadedComments>
@@ -2757,3288 +2274,2360 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C275"/>
+  <dimension ref="A1:C195"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
-    <col min="2" max="2" width="22.5546875" style="9" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" style="7" customWidth="1"/>
     <col min="3" max="3" width="197.44140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="6"/>
+      <c r="B1" s="5"/>
       <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:3" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>694</v>
+        <v>561</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>695</v>
+        <v>562</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>378</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>379</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>381</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>382</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>383</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>384</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>385</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>386</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>387</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>388</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>389</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>390</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>391</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>352</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
-        <v>347</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>349</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="B21" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>392</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>393</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>394</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>395</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>396</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>397</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>398</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>399</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>400</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>401</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>402</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>403</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>404</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>405</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>406</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>558</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>568</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>407</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>408</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>409</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>410</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="C42" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
-        <v>634</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>634</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
-        <v>635</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>635</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
-        <v>636</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>636</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
-        <v>637</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>637</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>411</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>412</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>413</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>414</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>415</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>416</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>417</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
-        <v>358</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>296</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
-        <v>364</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="15" t="s">
-        <v>365</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="15" t="s">
-        <v>366</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
-        <v>367</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>369</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
-        <v>370</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>370</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
-        <v>377</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="15" t="s">
-        <v>380</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="15" t="s">
-        <v>381</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="15" t="s">
-        <v>383</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="15" t="s">
-        <v>384</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="15" t="s">
-        <v>387</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>404</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A36" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>405</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>394</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>395</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="15" t="s">
-        <v>638</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>638</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="15" t="s">
-        <v>639</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>639</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="15" t="s">
-        <v>640</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>640</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
-        <v>641</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>641</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>444</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>445</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>447</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>449</v>
-      </c>
       <c r="C49" s="3" t="s">
-        <v>450</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="15" t="s">
-        <v>453</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>453</v>
+      <c r="A50" t="s">
+        <v>418</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>454</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="15" t="s">
-        <v>455</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>455</v>
+      <c r="A51" t="s">
+        <v>419</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>237</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>456</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="15" t="s">
-        <v>457</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>457</v>
+      <c r="A52" t="s">
+        <v>420</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>458</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>459</v>
+      <c r="A53" t="s">
+        <v>421</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>460</v>
+        <v>164</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>703</v>
-      </c>
-      <c r="B54" t="s">
-        <v>703</v>
+        <v>422</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>707</v>
+        <v>166</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>704</v>
-      </c>
-      <c r="B55" t="s">
-        <v>704</v>
+        <v>423</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>708</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>705</v>
-      </c>
-      <c r="B56" t="s">
-        <v>705</v>
+        <v>424</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>709</v>
+        <v>571</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>706</v>
-      </c>
-      <c r="B57" t="s">
-        <v>706</v>
+        <v>425</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>238</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>710</v>
+        <v>303</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>461</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>238</v>
+        <v>426</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>237</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>462</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>3</v>
+        <v>427</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>4</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>463</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>47</v>
+        <v>428</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>177</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>89</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>464</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>91</v>
+        <v>429</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>90</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>465</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>147</v>
+        <v>430</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>180</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>5</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>466</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>146</v>
+        <v>431</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>239</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>145</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>467</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>44</v>
+        <v>432</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>45</v>
+        <v>181</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>468</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>242</v>
+        <v>433</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>343</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>469</v>
-      </c>
-      <c r="B66" s="10" t="s">
-        <v>6</v>
+        <v>434</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>362</v>
+        <v>572</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>470</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>93</v>
+        <v>435</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>186</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>92</v>
+        <v>573</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>471</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>95</v>
+        <v>436</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>94</v>
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>472</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>149</v>
+        <v>437</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>473</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>151</v>
+        <v>438</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>150</v>
+        <v>192</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>474</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>153</v>
+        <v>439</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>475</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>155</v>
+        <v>440</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>154</v>
+        <v>194</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>476</v>
-      </c>
-      <c r="B73" s="7" t="s">
-        <v>157</v>
+        <v>441</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>156</v>
+        <v>372</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>477</v>
-      </c>
-      <c r="B74" s="7" t="s">
-        <v>159</v>
+        <v>442</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>478</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>161</v>
+        <v>443</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>479</v>
-      </c>
-      <c r="B76" s="7" t="s">
-        <v>163</v>
+        <v>444</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>480</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>165</v>
+        <v>445</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>481</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>70</v>
+        <v>446</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>203</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>69</v>
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>482</v>
-      </c>
-      <c r="B79" s="7" t="s">
-        <v>166</v>
+        <v>447</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>205</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>167</v>
+        <v>580</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>483</v>
-      </c>
-      <c r="B80" s="7" t="s">
-        <v>168</v>
+        <v>448</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>169</v>
+        <v>318</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>484</v>
-      </c>
-      <c r="B81" s="8" t="s">
-        <v>170</v>
+        <v>449</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>207</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>485</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>172</v>
+        <v>450</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>486</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>174</v>
+        <v>451</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>175</v>
+        <v>319</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>487</v>
-      </c>
-      <c r="B84" s="7" t="s">
-        <v>56</v>
+        <v>452</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>58</v>
+        <v>329</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>488</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>243</v>
+        <v>453</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>212</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>312</v>
+        <v>211</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>489</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>246</v>
+        <v>454</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>313</v>
+        <v>213</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>490</v>
-      </c>
-      <c r="B87" s="10" t="s">
-        <v>19</v>
+        <v>455</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>233</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>20</v>
+        <v>320</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>491</v>
-      </c>
-      <c r="B88" s="10" t="s">
-        <v>59</v>
+        <v>456</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>218</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>57</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>492</v>
-      </c>
-      <c r="B89" s="10" t="s">
-        <v>49</v>
+        <v>457</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>48</v>
+        <v>216</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>493</v>
-      </c>
-      <c r="B90" s="10" t="s">
-        <v>245</v>
+        <v>458</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>220</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>314</v>
+        <v>217</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>494</v>
-      </c>
-      <c r="B91" s="10" t="s">
-        <v>244</v>
+        <v>459</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>315</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>691</v>
-      </c>
-      <c r="B92" s="10" t="s">
-        <v>60</v>
+        <v>460</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>375</v>
+        <v>82</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="16" t="s">
-        <v>702</v>
-      </c>
-      <c r="B93" s="10" t="s">
-        <v>374</v>
+      <c r="A93" t="s">
+        <v>461</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>7</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>376</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>495</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>61</v>
+        <v>462</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>368</v>
+        <v>84</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>496</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>50</v>
+        <v>463</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>368</v>
+        <v>86</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>497</v>
-      </c>
-      <c r="B96" s="10" t="s">
-        <v>51</v>
+        <v>464</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>498</v>
-      </c>
-      <c r="B97" s="10" t="s">
-        <v>21</v>
+        <v>465</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>499</v>
-      </c>
-      <c r="B98" s="10" t="s">
-        <v>54</v>
+        <v>466</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>500</v>
-      </c>
-      <c r="B99" s="10" t="s">
-        <v>62</v>
+        <v>467</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>241</v>
+        <v>324</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>501</v>
-      </c>
-      <c r="B100" s="10" t="s">
-        <v>63</v>
+        <v>468</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>502</v>
-      </c>
-      <c r="B101" s="10" t="s">
-        <v>252</v>
+        <v>469</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>316</v>
+        <v>96</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>503</v>
-      </c>
-      <c r="B102" s="10" t="s">
-        <v>250</v>
+        <v>470</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>317</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>504</v>
-      </c>
-      <c r="B103" s="10" t="s">
-        <v>251</v>
+        <v>471</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>505</v>
-      </c>
-      <c r="B104" s="10" t="s">
-        <v>65</v>
+        <v>472</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>506</v>
-      </c>
-      <c r="B105" s="10" t="s">
-        <v>68</v>
+        <v>473</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>507</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>253</v>
+        <v>474</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>319</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>508</v>
-      </c>
-      <c r="B107" s="8" t="s">
-        <v>176</v>
+        <v>475</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>177</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>509</v>
-      </c>
-      <c r="B108" s="8" t="s">
-        <v>179</v>
+        <v>476</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>510</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>181</v>
+        <v>477</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>511</v>
-      </c>
-      <c r="B110" s="7" t="s">
-        <v>183</v>
+        <v>478</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>182</v>
+        <v>112</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>512</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>184</v>
+        <v>479</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>368</v>
+        <v>304</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>513</v>
-      </c>
-      <c r="B112" s="7" t="s">
-        <v>254</v>
+        <v>480</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>246</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>514</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>185</v>
+        <v>481</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>247</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>186</v>
+        <v>306</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>515</v>
-      </c>
-      <c r="B114" s="7" t="s">
-        <v>188</v>
+        <v>482</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>243</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>187</v>
+        <v>307</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>516</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>191</v>
+        <v>483</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>250</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>189</v>
+        <v>308</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>517</v>
-      </c>
-      <c r="B116" s="8" t="s">
-        <v>192</v>
+        <v>484</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>245</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>190</v>
+        <v>309</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>518</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>194</v>
+        <v>485</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>244</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>193</v>
+        <v>310</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>519</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>255</v>
+        <v>486</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>249</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>520</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>197</v>
+        <v>487</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>251</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>195</v>
+        <v>312</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>521</v>
-      </c>
-      <c r="B120" s="8" t="s">
-        <v>198</v>
+        <v>488</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>252</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>196</v>
+        <v>313</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>522</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>199</v>
+        <v>489</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>368</v>
+        <v>314</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>523</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>200</v>
+        <v>490</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>368</v>
+        <v>315</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>524</v>
-      </c>
-      <c r="B123" s="7" t="s">
-        <v>202</v>
+        <v>491</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>201</v>
+        <v>335</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>525</v>
-      </c>
-      <c r="B124" s="10" t="s">
-        <v>23</v>
+        <v>492</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>24</v>
+        <v>316</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>526</v>
-      </c>
-      <c r="B125" s="7" t="s">
-        <v>203</v>
+        <v>493</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>206</v>
+        <v>317</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>527</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>205</v>
+        <v>494</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>528</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>207</v>
+        <v>495</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>208</v>
+        <v>118</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>529</v>
-      </c>
-      <c r="B128" s="7" t="s">
-        <v>256</v>
+        <v>496</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>451</v>
+        <v>114</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>530</v>
-      </c>
-      <c r="B129" s="10" t="s">
-        <v>209</v>
+        <v>497</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>257</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>210</v>
+        <v>279</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>531</v>
-      </c>
-      <c r="B130" s="7" t="s">
-        <v>211</v>
+        <v>498</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>212</v>
+        <v>120</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>532</v>
-      </c>
-      <c r="B131" s="10" t="s">
-        <v>213</v>
+        <v>499</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>214</v>
+        <v>122</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>533</v>
-      </c>
-      <c r="B132" s="10" t="s">
-        <v>215</v>
+        <v>500</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>258</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>216</v>
+        <v>321</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>534</v>
-      </c>
-      <c r="B133" s="10" t="s">
-        <v>217</v>
+        <v>501</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>218</v>
+        <v>18</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>535</v>
-      </c>
-      <c r="B134" s="10" t="s">
-        <v>220</v>
+        <v>502</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>219</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>536</v>
       </c>
-      <c r="B135" s="10" t="s">
-        <v>247</v>
+      <c r="B135" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>537</v>
       </c>
-      <c r="B136" s="10" t="s">
-        <v>222</v>
+      <c r="B136" s="6" t="s">
+        <v>339</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>221</v>
+        <v>341</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>538</v>
       </c>
-      <c r="B137" s="10" t="s">
-        <v>223</v>
+      <c r="B137" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>224</v>
+        <v>343</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>539</v>
       </c>
-      <c r="B138" s="10" t="s">
-        <v>248</v>
+      <c r="B138" s="6" t="s">
+        <v>342</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>540</v>
       </c>
-      <c r="B139" s="10" t="s">
-        <v>225</v>
+      <c r="B139" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>541</v>
       </c>
-      <c r="B140" s="10" t="s">
-        <v>227</v>
+      <c r="B140" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>226</v>
+        <v>347</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>542</v>
       </c>
-      <c r="B141" s="7" t="s">
-        <v>229</v>
+      <c r="B141" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>228</v>
+        <v>349</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>543</v>
       </c>
-      <c r="B142" s="7" t="s">
-        <v>249</v>
+      <c r="B142" s="6" t="s">
+        <v>348</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>544</v>
       </c>
-      <c r="B143" s="7" t="s">
-        <v>233</v>
+      <c r="B143" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>230</v>
+        <v>352</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>545</v>
-      </c>
-      <c r="B144" s="7" t="s">
-        <v>234</v>
+        <v>546</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>351</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>231</v>
+        <v>353</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>546</v>
-      </c>
-      <c r="B145" s="10" t="s">
-        <v>235</v>
+        <v>503</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>259</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>232</v>
+        <v>322</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>547</v>
-      </c>
-      <c r="B146" s="10" t="s">
-        <v>7</v>
+        <v>504</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>548</v>
-      </c>
-      <c r="B147" s="7" t="s">
-        <v>97</v>
+        <v>505</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>549</v>
-      </c>
-      <c r="B148" s="10" t="s">
-        <v>9</v>
+        <v>506</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>550</v>
-      </c>
-      <c r="B149" s="7" t="s">
-        <v>99</v>
+        <v>545</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>98</v>
+        <v>355</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>551</v>
-      </c>
-      <c r="B150" s="7" t="s">
-        <v>101</v>
+        <v>547</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>354</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>100</v>
+        <v>356</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>552</v>
-      </c>
-      <c r="B151" s="7" t="s">
-        <v>103</v>
+        <v>548</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>102</v>
+        <v>358</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>553</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>105</v>
+        <v>549</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>357</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>104</v>
+        <v>359</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>554</v>
-      </c>
-      <c r="B153" s="8" t="s">
-        <v>107</v>
+        <v>550</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>106</v>
+        <v>361</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>555</v>
-      </c>
-      <c r="B154" s="7" t="s">
-        <v>258</v>
+        <v>551</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>360</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>556</v>
-      </c>
-      <c r="B155" s="7" t="s">
-        <v>109</v>
+        <v>552</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>108</v>
+        <v>364</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>557</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>111</v>
+        <v>553</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>363</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>110</v>
+        <v>365</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>558</v>
-      </c>
-      <c r="B157" s="7" t="s">
-        <v>113</v>
+        <v>554</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>112</v>
+        <v>367</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>559</v>
-      </c>
-      <c r="B158" s="7" t="s">
-        <v>257</v>
+        <v>555</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>366</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>341</v>
+        <v>368</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>560</v>
-      </c>
-      <c r="B159" s="10" t="s">
-        <v>115</v>
+        <v>507</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>561</v>
-      </c>
-      <c r="B160" s="7" t="s">
-        <v>117</v>
+        <v>508</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>116</v>
+        <v>280</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>562</v>
-      </c>
-      <c r="B161" s="7" t="s">
-        <v>119</v>
+        <v>556</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>118</v>
+        <v>370</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>563</v>
-      </c>
-      <c r="B162" s="7" t="s">
-        <v>121</v>
+        <v>557</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>369</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>120</v>
+        <v>371</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>564</v>
-      </c>
-      <c r="B163" s="10" t="s">
-        <v>123</v>
+        <v>509</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>565</v>
-      </c>
-      <c r="B164" s="10" t="s">
-        <v>125</v>
+        <v>510</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>566</v>
-      </c>
-      <c r="B165" s="10" t="s">
-        <v>127</v>
+        <v>511</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>126</v>
+        <v>574</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>567</v>
-      </c>
-      <c r="B166" s="7" t="s">
-        <v>264</v>
+        <v>512</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>261</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>322</v>
+        <v>575</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>568</v>
-      </c>
-      <c r="B167" s="7" t="s">
-        <v>262</v>
+        <v>513</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>323</v>
+        <v>576</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>569</v>
-      </c>
-      <c r="B168" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="B168" s="6" t="s">
         <v>263</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>324</v>
+        <v>577</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>570</v>
-      </c>
-      <c r="B169" s="7" t="s">
-        <v>259</v>
+        <v>515</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>262</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>325</v>
+        <v>578</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>571</v>
-      </c>
-      <c r="B170" s="7" t="s">
-        <v>266</v>
+        <v>516</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>326</v>
+        <v>579</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>572</v>
-      </c>
-      <c r="B171" s="7" t="s">
-        <v>261</v>
+        <v>517</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>264</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>327</v>
+        <v>535</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>573</v>
-      </c>
-      <c r="B172" s="7" t="s">
-        <v>260</v>
+        <v>559</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>328</v>
+        <v>127</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>574</v>
-      </c>
-      <c r="B173" s="7" t="s">
-        <v>265</v>
+        <v>560</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>331</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>329</v>
+        <v>127</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>575</v>
-      </c>
-      <c r="B174" s="7" t="s">
-        <v>267</v>
+        <v>518</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>330</v>
+        <v>128</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>576</v>
-      </c>
-      <c r="B175" s="7" t="s">
-        <v>268</v>
+        <v>519</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>577</v>
-      </c>
-      <c r="B176" s="7" t="s">
-        <v>270</v>
+        <v>520</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>277</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>578</v>
-      </c>
-      <c r="B177" s="7" t="s">
-        <v>269</v>
+        <v>521</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>275</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>333</v>
+        <v>293</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>579</v>
-      </c>
-      <c r="B178" s="10" t="s">
-        <v>11</v>
+        <v>522</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>268</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>392</v>
+        <v>281</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>580</v>
-      </c>
-      <c r="B179" s="7" t="s">
-        <v>271</v>
+        <v>523</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>269</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>334</v>
+        <v>283</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>581</v>
-      </c>
-      <c r="B180" s="7" t="s">
-        <v>272</v>
+        <v>524</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>274</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>335</v>
+        <v>284</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>582</v>
-      </c>
-      <c r="B181" s="7" t="s">
-        <v>131</v>
+        <v>525</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>278</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>130</v>
+        <v>285</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>583</v>
-      </c>
-      <c r="B182" s="7" t="s">
-        <v>133</v>
+        <v>526</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>272</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>132</v>
+        <v>286</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>584</v>
-      </c>
-      <c r="B183" s="7" t="s">
-        <v>129</v>
+        <v>527</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>128</v>
+        <v>287</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>585</v>
-      </c>
-      <c r="B184" s="7" t="s">
-        <v>273</v>
+        <v>528</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>586</v>
-      </c>
-      <c r="B185" s="7" t="s">
-        <v>135</v>
+        <v>529</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>266</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>134</v>
+        <v>224</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>587</v>
-      </c>
-      <c r="B186" s="7" t="s">
-        <v>137</v>
+        <v>530</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>276</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>136</v>
+        <v>288</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>588</v>
-      </c>
-      <c r="B187" s="7" t="s">
-        <v>274</v>
+        <v>531</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>265</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>589</v>
-      </c>
-      <c r="B188" s="7" t="s">
-        <v>25</v>
+        <v>532</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>26</v>
+        <v>290</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>590</v>
-      </c>
-      <c r="B189" s="10" t="s">
-        <v>27</v>
+        <v>533</v>
+      </c>
+      <c r="B189" s="6" t="s">
+        <v>273</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>28</v>
+        <v>291</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>658</v>
-      </c>
-      <c r="B190" s="10" t="s">
-        <v>71</v>
+        <v>534</v>
+      </c>
+      <c r="B190" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>409</v>
+        <v>32</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>659</v>
-      </c>
-      <c r="B191" s="10" t="s">
-        <v>408</v>
+        <v>563</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>410</v>
+        <v>22</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>660</v>
-      </c>
-      <c r="B192" s="7" t="s">
-        <v>72</v>
+        <v>564</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>326</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>412</v>
+        <v>327</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>661</v>
-      </c>
-      <c r="B193" s="7" t="s">
-        <v>411</v>
+        <v>565</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>413</v>
+        <v>338</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>662</v>
-      </c>
-      <c r="B194" s="10" t="s">
-        <v>12</v>
+        <v>566</v>
+      </c>
+      <c r="B194" s="6" t="s">
+        <v>328</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>415</v>
+        <v>223</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>663</v>
-      </c>
-      <c r="B195" s="10" t="s">
-        <v>414</v>
+        <v>567</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>336</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
-        <v>664</v>
-      </c>
-      <c r="B196" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C196" s="3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>665</v>
-      </c>
-      <c r="B197" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="C197" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>666</v>
-      </c>
-      <c r="B198" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C198" s="3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
-        <v>668</v>
-      </c>
-      <c r="B199" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="C199" s="3" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>591</v>
-      </c>
-      <c r="B200" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C200" s="3" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
-        <v>592</v>
-      </c>
-      <c r="B201" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C201" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
-        <v>593</v>
-      </c>
-      <c r="B202" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C202" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
-        <v>594</v>
-      </c>
-      <c r="B203" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C203" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>667</v>
-      </c>
-      <c r="B204" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C204" s="3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>669</v>
-      </c>
-      <c r="B205" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="C205" s="3" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>670</v>
-      </c>
-      <c r="B206" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C206" s="3" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>671</v>
-      </c>
-      <c r="B207" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="C207" s="3" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>672</v>
-      </c>
-      <c r="B208" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C208" s="3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>673</v>
-      </c>
-      <c r="B209" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="C209" s="3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>674</v>
-      </c>
-      <c r="B210" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C210" s="3" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
-        <v>675</v>
-      </c>
-      <c r="B211" s="10" t="s">
-        <v>432</v>
-      </c>
-      <c r="C211" s="3" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>676</v>
-      </c>
-      <c r="B212" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C212" s="3" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
-        <v>677</v>
-      </c>
-      <c r="B213" s="10" t="s">
-        <v>435</v>
-      </c>
-      <c r="C213" s="3" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
-        <v>595</v>
-      </c>
-      <c r="B214" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C214" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
-        <v>596</v>
-      </c>
-      <c r="B215" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C215" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A216" t="s">
-        <v>678</v>
-      </c>
-      <c r="B216" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C216" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A217" t="s">
-        <v>679</v>
-      </c>
-      <c r="B217" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="C217" s="3" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A218" t="s">
-        <v>597</v>
-      </c>
-      <c r="B218" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C218" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A219" t="s">
-        <v>598</v>
-      </c>
-      <c r="B219" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C219" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A220" t="s">
-        <v>599</v>
-      </c>
-      <c r="B220" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C220" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A221" t="s">
-        <v>600</v>
-      </c>
-      <c r="B221" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="C221" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A222" t="s">
-        <v>601</v>
-      </c>
-      <c r="B222" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A223" t="s">
-        <v>602</v>
-      </c>
-      <c r="B223" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A224" t="s">
-        <v>603</v>
-      </c>
-      <c r="B224" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="C224" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A225" t="s">
-        <v>604</v>
-      </c>
-      <c r="B225" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C225" s="3" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
-        <v>605</v>
-      </c>
-      <c r="B226" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A227" t="s">
-        <v>692</v>
-      </c>
-      <c r="B227" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A228" t="s">
-        <v>693</v>
-      </c>
-      <c r="B228" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="C228" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
-        <v>606</v>
-      </c>
-      <c r="B229" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C229" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A230" t="s">
-        <v>607</v>
-      </c>
-      <c r="B230" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A231" t="s">
-        <v>608</v>
-      </c>
-      <c r="B231" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C231" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
-        <v>609</v>
-      </c>
-      <c r="B232" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="C232" s="3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
-        <v>610</v>
-      </c>
-      <c r="B233" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="C233" s="3" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
-        <v>611</v>
-      </c>
-      <c r="B234" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="C234" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A235" t="s">
-        <v>612</v>
-      </c>
-      <c r="B235" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C235" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
-        <v>613</v>
-      </c>
-      <c r="B236" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="C236" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A237" t="s">
-        <v>614</v>
-      </c>
-      <c r="B237" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="C237" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A238" t="s">
-        <v>615</v>
-      </c>
-      <c r="B238" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C238" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
-        <v>616</v>
-      </c>
-      <c r="B239" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C239" s="3" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A240" t="s">
-        <v>617</v>
-      </c>
-      <c r="B240" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="C240" s="3" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
-        <v>618</v>
-      </c>
-      <c r="B241" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C241" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A242" t="s">
-        <v>619</v>
-      </c>
-      <c r="B242" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="C242" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A243" t="s">
-        <v>620</v>
-      </c>
-      <c r="B243" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="C243" s="3" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A244" t="s">
-        <v>621</v>
-      </c>
-      <c r="B244" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="C244" s="3" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A245" t="s">
-        <v>622</v>
-      </c>
-      <c r="B245" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="C245" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A246" s="15" t="s">
-        <v>680</v>
-      </c>
-      <c r="B246" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C246" s="3" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A247" s="15" t="s">
-        <v>681</v>
-      </c>
-      <c r="B247" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C247" s="3" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A248" s="15" t="s">
-        <v>623</v>
-      </c>
-      <c r="B248" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C248" s="3" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A249" s="15" t="s">
-        <v>624</v>
-      </c>
-      <c r="B249" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C249" s="3" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A250" s="15" t="s">
-        <v>625</v>
-      </c>
-      <c r="B250" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C250" s="3" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A251" s="15" t="s">
-        <v>626</v>
-      </c>
-      <c r="B251" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C251" s="3" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A252" s="15" t="s">
-        <v>627</v>
-      </c>
-      <c r="B252" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C252" s="3" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A253" s="15" t="s">
-        <v>628</v>
-      </c>
-      <c r="B253" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C253" s="3" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A254" s="15" t="s">
-        <v>629</v>
-      </c>
-      <c r="B254" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C254" s="3" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A255" s="15" t="s">
-        <v>630</v>
-      </c>
-      <c r="B255" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C255" s="3" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A256" s="15" t="s">
-        <v>631</v>
-      </c>
-      <c r="B256" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A257" s="15" t="s">
-        <v>632</v>
-      </c>
-      <c r="B257" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C257" s="3" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A258" s="15" t="s">
-        <v>633</v>
-      </c>
-      <c r="B258" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C258" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A259" s="15" t="s">
-        <v>652</v>
-      </c>
-      <c r="B259" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C259" s="3" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A260" s="15" t="s">
-        <v>653</v>
-      </c>
-      <c r="B260" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C260" s="3" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A261" s="15" t="s">
-        <v>654</v>
-      </c>
-      <c r="B261" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C261" s="3" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A262" s="15" t="s">
-        <v>655</v>
-      </c>
-      <c r="B262" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C262" s="3" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A263" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="B263" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C263" s="3" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A264" s="15" t="s">
-        <v>651</v>
-      </c>
-      <c r="B264" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A265" s="16" t="s">
-        <v>697</v>
-      </c>
-      <c r="B265" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C265" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A266" s="16" t="s">
-        <v>698</v>
-      </c>
-      <c r="B266" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="C266" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A267" s="16" t="s">
-        <v>699</v>
-      </c>
-      <c r="B267" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C267" s="3" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A268" s="16" t="s">
-        <v>700</v>
-      </c>
-      <c r="B268" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="C268" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A269" s="16" t="s">
-        <v>701</v>
-      </c>
-      <c r="B269" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="C269" s="3" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A270" s="15" t="s">
-        <v>711</v>
-      </c>
-      <c r="B270" s="15" t="s">
-        <v>696</v>
-      </c>
-      <c r="C270" s="3" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A271" t="s">
-        <v>713</v>
-      </c>
-      <c r="B271" s="17" t="s">
-        <v>696</v>
-      </c>
-      <c r="C271" s="3" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A272" t="s">
-        <v>715</v>
-      </c>
-      <c r="B272" s="17" t="s">
-        <v>696</v>
-      </c>
-      <c r="C272" s="3" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
-        <v>717</v>
-      </c>
-      <c r="B273" s="17" t="s">
-        <v>696</v>
-      </c>
-      <c r="C273" s="3" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
-        <v>719</v>
-      </c>
-      <c r="B274" s="17" t="s">
-        <v>696</v>
-      </c>
-      <c r="C274" s="3" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
-        <v>721</v>
-      </c>
-      <c r="B275" s="17" t="s">
-        <v>696</v>
-      </c>
-      <c r="C275" s="3" t="s">
-        <v>722</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:C269" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C269">
-      <sortCondition ref="A2:A269"/>
+  <autoFilter ref="A2:C195" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C195">
+      <sortCondition ref="A2:A195"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A53 A58:A264 A270:A1048576">
+  <conditionalFormatting sqref="A196:A1048576 A1:A190">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B59" r:id="rId1" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA001A_Detail.svg" xr:uid="{17ADBAC8-7138-41E8-BDFB-2ED015B2E3B6}"/>
-    <hyperlink ref="B66" r:id="rId2" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA008A_Detail.svg" xr:uid="{3A518947-B6F8-4C42-81D7-7894D9144A33}"/>
-    <hyperlink ref="B146" r:id="rId3" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP001A_Detail.svg" xr:uid="{761B47C6-804C-4528-8497-BBE932BB2C49}"/>
-    <hyperlink ref="B148" r:id="rId4" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP003A_Detail.svg" xr:uid="{EC8BC23F-0549-4B47-A475-38BE73BE9CEE}"/>
-    <hyperlink ref="B202" r:id="rId5" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV012A_Detail.svg" xr:uid="{5A391EDE-1D55-4CFD-9901-A29E0591193B}"/>
-    <hyperlink ref="B9" r:id="rId6" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0006_Detail.svg" xr:uid="{975176F7-F497-4824-8376-23C959379C06}"/>
-    <hyperlink ref="B10" r:id="rId7" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0007_Detail.svg" xr:uid="{5FA11009-5EE8-4528-A809-14E1B1FB1C10}"/>
-    <hyperlink ref="B11" r:id="rId8" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0008_Detail.svg" xr:uid="{7720A7D8-16EA-4565-A935-C37587E784A7}"/>
-    <hyperlink ref="B15" r:id="rId9" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0010_Detail.svg" xr:uid="{8BCC9369-A109-4DC7-B34A-9DE621C69D33}"/>
-    <hyperlink ref="B88" r:id="rId10" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE002A_Detail.svg" xr:uid="{BD7A7DCC-BFC7-48AF-B865-B8368E55F2E6}"/>
-    <hyperlink ref="B114" r:id="rId11" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE027A_Detail.svg" xr:uid="{4ECEB4FA-D039-495A-8F42-FFC9B443FDC3}"/>
-    <hyperlink ref="B139" r:id="rId12" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF009A_Detail.svg" xr:uid="{907022FE-3A1A-45BE-8FF2-AC230B1DD29B}"/>
-    <hyperlink ref="B188" r:id="rId13" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV001A_Detail.svg" xr:uid="{A8069CA7-B440-43C6-B571-35216079CADD}"/>
-    <hyperlink ref="B193" r:id="rId14" xr:uid="{7398F614-893C-4326-BA65-62E7CEF8B17B}"/>
-    <hyperlink ref="B207" r:id="rId15" xr:uid="{86D99A6B-DD65-4D76-9524-599D4EAB2E02}"/>
-    <hyperlink ref="B210" r:id="rId16" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV018A_Detail.svg" xr:uid="{3E8578A0-8239-405C-B417-86D7CEF2DB87}"/>
-    <hyperlink ref="B214" r:id="rId17" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV021A_Detail.svg" xr:uid="{27E00768-DA9C-4DAF-98AA-2381306E4A13}"/>
-    <hyperlink ref="B230" r:id="rId18" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ013A_Detail.svg" xr:uid="{9F7EE259-EBE5-4578-86F7-E5EF694FDA65}"/>
-    <hyperlink ref="B225" r:id="rId19" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ009A_Detail.svg" xr:uid="{30065FD0-FD2C-4BF8-A534-106ECA4A05E6}"/>
-    <hyperlink ref="B245" r:id="rId20" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/STPL008_Detail.svg" xr:uid="{F132DB26-A2BF-4161-B712-08766D64B599}"/>
-    <hyperlink ref="B267" r:id="rId21" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{21C87E9B-CBD0-4B81-A925-45F9B4FD8864}"/>
-    <hyperlink ref="B64" r:id="rId22" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA006A_Detail.svg" xr:uid="{C46298F6-C022-42A8-88EB-27031801D32E}"/>
-    <hyperlink ref="B17" r:id="rId23" xr:uid="{045D2E44-4A59-4C52-AA81-3156413AFAFC}"/>
-    <hyperlink ref="B61" r:id="rId24" display="PA002A" xr:uid="{6BAE8F82-BC2B-4427-9773-0A3AE429BDE1}"/>
-    <hyperlink ref="B89" r:id="rId25" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE003A_Detail.svg" xr:uid="{4004AC67-08BF-4573-A91C-196B852BE782}"/>
-    <hyperlink ref="B95" r:id="rId26" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE008A_Detail.svg" xr:uid="{907142FB-A61F-493E-ADCC-40C2E404D844}"/>
-    <hyperlink ref="B96" r:id="rId27" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE009A_Detail.svg" xr:uid="{42D7E312-902B-45B8-B2E6-478D821615A1}"/>
-    <hyperlink ref="B97" r:id="rId28" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE010A_Detail.svg" xr:uid="{12CE6EBF-4CA8-44DF-B6FC-040DFB92731D}"/>
-    <hyperlink ref="B84" r:id="rId29" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD018A_Detail.svg" xr:uid="{D9AD65D0-256C-4FDA-AB63-641CAEF296B8}"/>
-    <hyperlink ref="B87" r:id="rId30" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE001A_Detail.svg" xr:uid="{B5B862E7-DBAB-44C9-B7B4-21949ADAF9C9}"/>
-    <hyperlink ref="B92" r:id="rId31" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE006A_Detail.svg" xr:uid="{AA6401E6-CD51-4574-ABA6-C7BB3663F989}"/>
-    <hyperlink ref="B94" r:id="rId32" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE007A_Detail.svg" xr:uid="{B35184E7-56AF-48CA-8CC6-9A61FB055044}"/>
-    <hyperlink ref="B98" r:id="rId33" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE011A_Detail.svg" xr:uid="{52A5B7C0-AD9C-472F-899E-86CD63EFB3AA}"/>
-    <hyperlink ref="B99" r:id="rId34" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE012A_Detail.svg" xr:uid="{C3016BE0-26B5-41E3-A7DB-D7C53F62C108}"/>
-    <hyperlink ref="B100" r:id="rId35" display="PE012A" xr:uid="{FFB4E872-E736-41AC-8F80-41BB1E8C57A6}"/>
-    <hyperlink ref="B104" r:id="rId36" display="PE013A" xr:uid="{69F4C8E5-12AD-463A-8F4A-4719422312A8}"/>
-    <hyperlink ref="B78" r:id="rId37" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD012A_Detail.svg" xr:uid="{F25BE2C8-8813-4940-8329-63BBA6D15B89}"/>
-    <hyperlink ref="B189" r:id="rId38" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV002A_Detail.svg" xr:uid="{EB3DD888-4A6F-42F8-AD39-FAC973963B51}"/>
-    <hyperlink ref="B191" r:id="rId39" xr:uid="{C8A2ABD8-A0CE-4FB6-BD75-7694D40F91BE}"/>
-    <hyperlink ref="B195" r:id="rId40" xr:uid="{10BB9991-94D9-43E5-9038-0AD1029C8456}"/>
-    <hyperlink ref="B197" r:id="rId41" xr:uid="{E92459C1-EFAE-4D41-A9A2-B6CBF8031302}"/>
-    <hyperlink ref="B199" r:id="rId42" xr:uid="{FB94CBE5-59E0-4451-A8F5-AF4BCA7E6242}"/>
-    <hyperlink ref="B201" r:id="rId43" display="PV008A" xr:uid="{7C2F94E7-1DC8-40D5-9F4C-AA07CD1D7F60}"/>
-    <hyperlink ref="B203" r:id="rId44" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV013A_Detail.svg" xr:uid="{D981260A-8BAC-4F90-8B22-F4387848B90B}"/>
-    <hyperlink ref="B205" r:id="rId45" xr:uid="{7AB8E356-44B8-49E6-B29B-395AA92E87A4}"/>
-    <hyperlink ref="B209" r:id="rId46" xr:uid="{27C7E718-E4EC-4B45-A105-4219CB86145A}"/>
-    <hyperlink ref="B217" r:id="rId47" xr:uid="{22BEA91F-E09D-41B1-979E-65B6D728D85F}"/>
-    <hyperlink ref="B213" r:id="rId48" xr:uid="{64580D0C-1766-4DB3-AF77-41B1C3F4FBCB}"/>
-    <hyperlink ref="B218" r:id="rId49" display="PZ001A" xr:uid="{6198CEDF-7056-49B0-8C8C-0CE4F43ED518}"/>
-    <hyperlink ref="B60" r:id="rId50" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA002A_Detail.svg" xr:uid="{0302EB7E-2FF3-47CA-B5A8-8E3511F52559}"/>
-    <hyperlink ref="B73" r:id="rId51" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD007A_Detail.svg" xr:uid="{55939466-04EF-445D-B8C5-29A1F47BFBEC}"/>
-    <hyperlink ref="B67" r:id="rId52" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD001A_Detail.svg" xr:uid="{3C931296-EFA6-4A17-ABBE-BA3CEEBAE7CD}"/>
-    <hyperlink ref="B147" r:id="rId53" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP002A_Detail.svg" xr:uid="{7B04BB8C-B4F8-4443-9951-FF9779382F5E}"/>
-    <hyperlink ref="B153" r:id="rId54" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP008A_Detail.svg" xr:uid="{B8AA4B11-0A29-4052-8E9D-3BF8D275C0C3}"/>
-    <hyperlink ref="B149" r:id="rId55" display="PP003A" xr:uid="{A0025AF4-1428-4206-B942-D976CF2EABF6}"/>
-    <hyperlink ref="B150" r:id="rId56" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP005A_Detail.svg" xr:uid="{A6177C8F-61D8-4517-924D-AC098541874E}"/>
-    <hyperlink ref="B151" r:id="rId57" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP006A_Detail.svg" xr:uid="{CCC65F5C-1709-40F0-BC1E-5E22B9EE2E8B}"/>
-    <hyperlink ref="B152" r:id="rId58" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP007A_Detail.svg" xr:uid="{CF9DC830-F3E2-46F7-BB6E-F40EE3588C98}"/>
-    <hyperlink ref="B165" r:id="rId59" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS004A_Detail.svg" xr:uid="{9053D430-E6CE-479A-9C3A-E85BE51DDA2D}"/>
-    <hyperlink ref="B155" r:id="rId60" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP010A_Detail.svg" xr:uid="{0970F33B-0575-4123-83FA-27B45C94A4A2}"/>
-    <hyperlink ref="B156" r:id="rId61" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP011A_Detail.svg" xr:uid="{0EA32245-04D0-41E6-991A-61C23D6D04D5}"/>
-    <hyperlink ref="B157" r:id="rId62" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP012A_Detail.svg" xr:uid="{FBE8CA96-6772-460A-8C03-4C086593A5CE}"/>
-    <hyperlink ref="B159" r:id="rId63" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP014A_Detail.svg" xr:uid="{9377286C-CA88-49CA-8DB6-8B4673069711}"/>
-    <hyperlink ref="B160" r:id="rId64" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP015A_Detail.svg" xr:uid="{4CF07C91-9442-4F6E-8428-DC8B0ABD88EC}"/>
-    <hyperlink ref="B161" r:id="rId65" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP016A_Detail.svg" xr:uid="{95445AC5-539C-433D-929D-1B79509AB314}"/>
-    <hyperlink ref="B162" r:id="rId66" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP017A_Detail.svg" xr:uid="{F1EAA06B-6B10-469E-BFA8-DBE8DA0E67EC}"/>
-    <hyperlink ref="B163" r:id="rId67" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS001A_Detail.svg" xr:uid="{53C8229D-2E3F-405D-A9C8-3F6FE5E0EFCC}"/>
-    <hyperlink ref="B178" r:id="rId68" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT002A_Detail.svg" xr:uid="{8ED0FE06-63C6-4619-8AFA-C21DEA756B38}"/>
-    <hyperlink ref="B182" r:id="rId69" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT006A_Detail.svg" xr:uid="{DE7E75F2-6055-421D-A22C-888A6804396D}"/>
-    <hyperlink ref="B181" r:id="rId70" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT005A_Detail.svg" xr:uid="{95A726E8-8601-4CDB-BBED-77B49873F4C0}"/>
-    <hyperlink ref="B183" r:id="rId71" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT007A_Detail.svg" xr:uid="{B6131D2E-4752-4739-997C-D3CBF679F940}"/>
-    <hyperlink ref="B185" r:id="rId72" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT009A_Detail.svg" xr:uid="{D06AD6E5-7BA2-492F-8D44-8B09ADBF6122}"/>
-    <hyperlink ref="B186" r:id="rId73" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT010A_Detail.svg" xr:uid="{52343A83-46C2-4D49-BFE5-DA8717644CD2}"/>
-    <hyperlink ref="B219" r:id="rId74" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ003A_Detail.svg" xr:uid="{335D3D40-BE42-44FE-929A-0F3D3F26D262}"/>
-    <hyperlink ref="B220" r:id="rId75" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ004A_Detail.svg" xr:uid="{45517A4C-49CF-4A14-BE92-F3323139DBA8}"/>
-    <hyperlink ref="B222" r:id="rId76" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ006A_Detail.svg" xr:uid="{92F8D01F-B6E2-40C7-970D-7EAFB7872F29}"/>
-    <hyperlink ref="B229" r:id="rId77" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ012A_Detail.svg" xr:uid="{F5F1079A-1346-46A4-BF70-9025442AFB80}"/>
-    <hyperlink ref="B227" r:id="rId78" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ011A_Detail.svg" xr:uid="{BDA2ADBE-AC37-448F-9C41-243FB16B0996}"/>
-    <hyperlink ref="B63" r:id="rId79" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA005A_Detail.svg" xr:uid="{BA3A7E34-7D5B-4A78-BB78-1727C668EB8F}"/>
-    <hyperlink ref="B62" r:id="rId80" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA004A_Detail.svg" xr:uid="{39481051-1B60-44BF-8211-0D5C1980FD4B}"/>
-    <hyperlink ref="B68" r:id="rId81" display="PD001A" xr:uid="{3969656E-C88B-42A9-9C3B-B8275B159B5B}"/>
-    <hyperlink ref="B69" r:id="rId82" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD003A_Detail.svg" xr:uid="{86AB2467-10FE-4C5F-883D-EDA03495CD55}"/>
-    <hyperlink ref="B70" r:id="rId83" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD004A_Detail.svg" xr:uid="{A3F7C2AC-969E-4A1D-87C5-6BFE5671E4DC}"/>
-    <hyperlink ref="B71" r:id="rId84" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD005A_Detail.svg" xr:uid="{6DFFDA9D-5A28-4CC7-8DE9-876E2360BFEE}"/>
-    <hyperlink ref="B72" r:id="rId85" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD006A_Detail.svg" xr:uid="{3BB6ACEF-9AAF-4C4D-9A87-FCF6EA0F91BD}"/>
-    <hyperlink ref="B83" r:id="rId86" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD017A_Detail.svg" xr:uid="{28D1C6B0-DDE6-442D-9F10-91D27566478A}"/>
-    <hyperlink ref="B74" r:id="rId87" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD008A_Detail.svg" xr:uid="{AB7B0FCA-5804-4486-8380-FBA9F83DEE66}"/>
-    <hyperlink ref="B75" r:id="rId88" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD009A_Detail.svg" xr:uid="{9D870461-08B6-4714-8A00-09714564A8DF}"/>
-    <hyperlink ref="B76" r:id="rId89" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD010A_Detail.svg" xr:uid="{BB4A6A70-CBD2-4C62-B476-1DB99A7B8C9C}"/>
-    <hyperlink ref="B77" r:id="rId90" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD011A_Detail.svg" xr:uid="{5A9D789E-5B6D-46CC-883A-8FE28112F14B}"/>
-    <hyperlink ref="B79" r:id="rId91" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD013A_Detail.svg" xr:uid="{6394051E-0C5B-4871-B946-B73195930CB1}"/>
-    <hyperlink ref="B80" r:id="rId92" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD014A_Detail.svg" xr:uid="{89E87861-2175-4BEE-A5F9-33D47934E630}"/>
-    <hyperlink ref="B81" r:id="rId93" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD015A_Detail.svg" xr:uid="{C0901CAD-B396-4045-9DFB-94C087A6E9C7}"/>
-    <hyperlink ref="B82" r:id="rId94" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD016A_Detail.svg" xr:uid="{FE18571B-26F6-45A2-AE52-5E17B76EC7F3}"/>
-    <hyperlink ref="B105" r:id="rId95" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE018A_Detail.svg" xr:uid="{6D3B7973-3EAF-4809-A3A6-949465067CBC}"/>
-    <hyperlink ref="B107" r:id="rId96" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE020A_Detail.svg" xr:uid="{39CB98B6-29C9-4B55-BB4D-C050812B9145}"/>
-    <hyperlink ref="B108" r:id="rId97" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE021A_Detail.svg" xr:uid="{50AE8AE5-DEF4-4FC6-8682-258DF3904CD7}"/>
-    <hyperlink ref="B109" r:id="rId98" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE022A_Detail.svg" xr:uid="{93F60579-BA2A-4EDC-B883-017EBA23D13F}"/>
-    <hyperlink ref="B110" r:id="rId99" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE023A_Detail.svg" xr:uid="{2F7FC80D-3FA4-4BE4-A403-E017F265775F}"/>
-    <hyperlink ref="B111" r:id="rId100" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE024A_Detail.svg" xr:uid="{212E32CA-E31F-4B52-AC82-844C20339614}"/>
-    <hyperlink ref="B113" r:id="rId101" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE026A_Detail.svg" xr:uid="{9078864B-22E7-4236-BA73-76CA46B86A31}"/>
-    <hyperlink ref="B115" r:id="rId102" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE028A_Detail.svg" xr:uid="{F436B4D7-3AA5-4126-BBD2-BACE69A4A4E0}"/>
-    <hyperlink ref="B116" r:id="rId103" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE029A_Detail.svg" xr:uid="{C7A515AB-6C11-4EA4-85E4-5091485DAA17}"/>
-    <hyperlink ref="B120" r:id="rId104" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE033A_Detail.svg" xr:uid="{34E7B3BE-E531-4018-BB45-6CCB618C0FBB}"/>
-    <hyperlink ref="B117" r:id="rId105" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE030A_Detail.svg" xr:uid="{1F74D129-65A3-4B07-BF1F-5193476A8A04}"/>
-    <hyperlink ref="B119" r:id="rId106" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE032A_Detail.svg" xr:uid="{8A8FA28E-6634-4E0D-A29F-388C878E8DB9}"/>
-    <hyperlink ref="B121" r:id="rId107" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE034A_Detail.svg" xr:uid="{6C65D9E8-788A-4EFB-B896-E4E82EAA3CB0}"/>
-    <hyperlink ref="B123" r:id="rId108" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE036A_Detail.svg" xr:uid="{6A654C5A-571F-47D9-9387-6F62409DC1B7}"/>
-    <hyperlink ref="B122" r:id="rId109" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE035A_Detail.svg" xr:uid="{8BF957E4-037D-4E36-9BCA-83538FEE7EAF}"/>
-    <hyperlink ref="B124" r:id="rId110" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE037A_Detail.svg" xr:uid="{7931F92F-DB33-458A-84AB-EEE6E7217AAA}"/>
-    <hyperlink ref="B125" r:id="rId111" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE038A_Detail.svg" xr:uid="{F73D9E2D-2341-4000-BD06-BEF7EA513332}"/>
-    <hyperlink ref="B126" r:id="rId112" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE039A_Detail.svg" xr:uid="{FB0AAC16-DEA9-41D3-8765-ACE272916988}"/>
-    <hyperlink ref="B127" r:id="rId113" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE040A_Detail.svg" xr:uid="{9D15EFC4-F96D-4011-83A8-7E4FB0A02FD4}"/>
-    <hyperlink ref="B129" r:id="rId114" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE042A_Detail.svg" xr:uid="{4DC635F0-1E08-4047-98E2-D16EA3B8D3B6}"/>
-    <hyperlink ref="B130" r:id="rId115" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE043A_Detail.svg" xr:uid="{7A91C884-B181-4AC9-8872-A5B4FEC2FA44}"/>
-    <hyperlink ref="B131" r:id="rId116" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF001A_Detail.svg" xr:uid="{226AE98E-A3DA-4D82-91A1-7CFDF93A8DE9}"/>
-    <hyperlink ref="B132" r:id="rId117" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF002A_Detail.svg" xr:uid="{467E946A-F396-4E22-A95C-421F6CE0BC8B}"/>
-    <hyperlink ref="B133" r:id="rId118" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF003A_Detail.svg" xr:uid="{55C30B46-FD0C-4081-A7D2-D7A7DFE70B52}"/>
-    <hyperlink ref="B134" r:id="rId119" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF004A_Detail.svg" xr:uid="{1127E743-3E80-461C-9E2E-11276A527952}"/>
-    <hyperlink ref="B136" r:id="rId120" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF006A_Detail.svg" xr:uid="{C896FA40-2C0C-4F45-ABB7-4A0598EF464F}"/>
-    <hyperlink ref="B137" r:id="rId121" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF007A_Detail.svg" xr:uid="{B63E94F9-6FBE-473E-BB35-4B04D8BA205A}"/>
-    <hyperlink ref="B145" r:id="rId122" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF015A_Detail.svg" xr:uid="{D0C9703A-C515-442F-88BF-811B68EF3142}"/>
-    <hyperlink ref="B140" r:id="rId123" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF010A_Detail.svg" xr:uid="{8776960A-3D62-49BB-964C-0A029249E4ED}"/>
-    <hyperlink ref="B141" r:id="rId124" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF011A_Detail.svg" xr:uid="{52198015-5884-4164-AE13-C31DC940BF9F}"/>
-    <hyperlink ref="B143" r:id="rId125" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF013A_Detail.svg" xr:uid="{1676627D-C9A1-412D-A74B-FEC1DD6ADAFC}"/>
-    <hyperlink ref="B144" r:id="rId126" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF014A_Detail.svg" xr:uid="{0AE6782A-A294-4988-A1A8-09100E831215}"/>
-    <hyperlink ref="B19" r:id="rId127" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0014_Detail.svg" xr:uid="{1F3765D3-EFE7-463A-B085-1DE36D0AE049}"/>
-    <hyperlink ref="B58" r:id="rId128" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/LZ009A_Detail.svg" xr:uid="{964B3FA4-6BEE-49FA-A53D-C16D25DADF11}"/>
-    <hyperlink ref="B18" r:id="rId129" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0013_Detail.svg" xr:uid="{5203DA34-E147-4733-BD2B-596D44AF2F0D}"/>
-    <hyperlink ref="B164" r:id="rId130" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS003A_Detail.svg" xr:uid="{D3E46F2B-78B9-41FF-AD13-E05C1AAC94AA}"/>
-    <hyperlink ref="B184" r:id="rId131" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT008A_Detail.svg" xr:uid="{A09F2ECE-A3F2-485F-89B3-392B6CCF3E0F}"/>
-    <hyperlink ref="B21" r:id="rId132" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0016_Detail.svg" xr:uid="{D78471C4-ED27-412C-838A-FDFC562E1EC3}"/>
-    <hyperlink ref="B215" r:id="rId133" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV022A_Detail.svg" xr:uid="{7F2ADD73-6C39-4114-8228-83338A629639}"/>
-    <hyperlink ref="B241" r:id="rId134" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ024A_Detail.svg" xr:uid="{D7DC9173-D444-4E60-B47B-45295B162EA3}"/>
-    <hyperlink ref="B14" r:id="rId135" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0009_Detail.svg" xr:uid="{CF5F7511-92B4-421B-B7C3-594BAC34117C}"/>
-    <hyperlink ref="B233" r:id="rId136" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ016A_Detail.svg" xr:uid="{223CCECC-C661-4D77-99FB-373C2C3EB9FD}"/>
-    <hyperlink ref="B239" r:id="rId137" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ022A_Detail.svg" xr:uid="{4E646DA6-844E-461F-A30F-E45D4A6BAEE0}"/>
-    <hyperlink ref="B234" r:id="rId138" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ017A_Detail.svg" xr:uid="{4AF15DA4-056F-4E39-B57F-D527D7C96314}"/>
-    <hyperlink ref="B235" r:id="rId139" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ018A_Detail.svg" xr:uid="{6A08BE2B-2F4A-40D0-87F1-2BF30F7E5204}"/>
-    <hyperlink ref="B236" r:id="rId140" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ019A_Detail.svg" xr:uid="{6C2DB1B2-D14C-41F7-85E9-0AD5CD60A40D}"/>
-    <hyperlink ref="B237" r:id="rId141" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ020A_Detail.svg" xr:uid="{3E5BB973-5805-404F-A772-22A577F5EA77}"/>
-    <hyperlink ref="B238" r:id="rId142" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ021A_Detail.svg" xr:uid="{96375F5D-1843-4B64-9FEB-59352041AF1C}"/>
-    <hyperlink ref="B240" r:id="rId143" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ023A_Detail.svg" xr:uid="{D811FB39-FE0C-4790-A865-54A17F50CA6D}"/>
-    <hyperlink ref="B242" r:id="rId144" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ025A_Detail.svg" xr:uid="{60163B1A-1792-49FF-9790-F2BF94ABFA4A}"/>
-    <hyperlink ref="B243" r:id="rId145" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ026A_Detail.svg" xr:uid="{0AAE0EB6-ECBB-4198-AA26-C684A0AECB97}"/>
-    <hyperlink ref="B244" r:id="rId146" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ027A_Detail.svg" xr:uid="{824407FA-7B30-4D5E-93CE-ED8122F65FFE}"/>
-    <hyperlink ref="B231" r:id="rId147" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ014A_Detail.svg" xr:uid="{F99B97AB-F1A6-4427-ABEB-25E3CC85B5DC}"/>
-    <hyperlink ref="B232" r:id="rId148" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ015A_Detail.svg" xr:uid="{12DA03AC-3D4B-49FC-B523-CC4091EF5CF4}"/>
-    <hyperlink ref="B85" r:id="rId149" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD019A_Detail.svg" xr:uid="{1FEADDE7-E396-46B6-9322-03EDCA28A99A}"/>
-    <hyperlink ref="B86" r:id="rId150" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD020A_Detail.svg" xr:uid="{1987EC41-B7CC-4E23-B295-01B52113BE11}"/>
-    <hyperlink ref="B90" r:id="rId151" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE004A_Detail.svg" xr:uid="{22A02656-E11C-40BA-93D1-A3BA2FBE802C}"/>
-    <hyperlink ref="B91" r:id="rId152" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE005A_Detail.svg" xr:uid="{D679D4B8-1D0A-498C-B0C6-64751CDFD8A9}"/>
-    <hyperlink ref="B65" r:id="rId153" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA007A_Detail.svg" xr:uid="{30DD321A-DB3E-4139-B7C6-5B72D5F41E50}"/>
-    <hyperlink ref="B101" r:id="rId154" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE014A_Detail.svg" xr:uid="{2B620BE4-F09B-478A-BDA6-76461B53049C}"/>
-    <hyperlink ref="B102" r:id="rId155" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE015A_Detail.svg" xr:uid="{57F06AB3-A2D4-42BD-8A97-785E7A9DEED3}"/>
-    <hyperlink ref="B103" r:id="rId156" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE016A_Detail.svg" xr:uid="{7714B096-A821-46A9-B38E-478AC0F60DFA}"/>
-    <hyperlink ref="B106" r:id="rId157" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE019A_Detail.svg" xr:uid="{77B288AB-A3B1-4E08-ABAC-36CEFD1274DD}"/>
-    <hyperlink ref="B118" r:id="rId158" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE031A_Detail.svg" xr:uid="{BD8A7598-0DFE-4ACB-ABFF-A23EE4147A0C}"/>
-    <hyperlink ref="B112" r:id="rId159" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE025A_Detail.svg" xr:uid="{111CB70F-38F3-4FA2-9171-155C1FE97029}"/>
-    <hyperlink ref="B166" r:id="rId160" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS005A_Detail.svg" xr:uid="{8BD8F9B2-845D-4212-B985-91349C8461AA}"/>
-    <hyperlink ref="B167" r:id="rId161" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS006A_Detail.svg" xr:uid="{616ABAAF-2406-46A1-9490-096325FB538C}"/>
-    <hyperlink ref="B168" r:id="rId162" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS007A_Detail.svg" xr:uid="{C158EBE4-9C88-4608-8165-95D1C5969FE5}"/>
-    <hyperlink ref="B169" r:id="rId163" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS008A_Detail.svg" xr:uid="{8B850863-4DBF-4261-A871-9900D82512A0}"/>
-    <hyperlink ref="B170" r:id="rId164" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS009A_Detail.svg" xr:uid="{EAA92938-1022-4B27-8A45-FC38DB3D12AB}"/>
-    <hyperlink ref="B171" r:id="rId165" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS010A_Detail.svg" xr:uid="{DE97D73F-147C-4EDC-A7D8-86145F37E03C}"/>
-    <hyperlink ref="B172" r:id="rId166" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS011A_Detail.svg" xr:uid="{006F66EF-728F-49E8-A5FE-751016748DAC}"/>
-    <hyperlink ref="B173" r:id="rId167" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS012A_Detail.svg" xr:uid="{8F448560-0B77-4837-B70F-0B9A88CD3C63}"/>
-    <hyperlink ref="B174" r:id="rId168" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS013A_Detail.svg" xr:uid="{0221699E-5F49-4DF1-B0AB-C4E5888F2A80}"/>
-    <hyperlink ref="B175" r:id="rId169" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS014A_Detail.svg" xr:uid="{C05394F3-DC5D-41A9-A414-4B0B18AAED5C}"/>
-    <hyperlink ref="B176" r:id="rId170" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS015A_Detail.svg" xr:uid="{C2CC68D8-9E61-4D94-BCC1-7A22522BAC81}"/>
-    <hyperlink ref="B177" r:id="rId171" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS016A_Detail.svg" xr:uid="{47A88BDB-E04A-43F6-992D-C76510B510EF}"/>
-    <hyperlink ref="B179" r:id="rId172" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT003A_Detail.svg" xr:uid="{7CF97CF8-3E1A-4A9E-ABE2-3A579CF8676B}"/>
-    <hyperlink ref="B180" r:id="rId173" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT004A_Detail.svg" xr:uid="{75DC4A11-DAE8-4DC6-A6D0-7E3E61B719CC}"/>
-    <hyperlink ref="B128" r:id="rId174" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE041A_Detail.svg" xr:uid="{EF9B4A93-EF2D-4E76-A4CC-16163CED7262}"/>
-    <hyperlink ref="B135" r:id="rId175" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF005A_Detail.svg" xr:uid="{3383514A-9E6D-45A7-AD65-0B18E1BAAD22}"/>
-    <hyperlink ref="B138" r:id="rId176" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF008A_Detail.svg" xr:uid="{73E8300F-62F2-4049-934B-015EDBEED287}"/>
-    <hyperlink ref="B142" r:id="rId177" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF012A_Detail.svg" xr:uid="{E9B3CC0D-A34B-4C8A-B89B-B330DAD71021}"/>
-    <hyperlink ref="B154" r:id="rId178" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP009A_Detail.svg" xr:uid="{0A13328E-0285-44BD-B9CF-A05D28AD6EAD}"/>
-    <hyperlink ref="B187" r:id="rId179" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT011A_Detail.svg" xr:uid="{E88B48B0-2B27-4600-8526-87B72CED5EC1}"/>
-    <hyperlink ref="B200" r:id="rId180" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV009A_Detail.svg" xr:uid="{25FF9022-3620-4A11-BF03-2A03200DD6CC}"/>
-    <hyperlink ref="B221" r:id="rId181" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ005A_Detail.svg" xr:uid="{92F69C2E-BC95-4B0C-9D0B-5D880C9FFE1C}"/>
-    <hyperlink ref="B223" r:id="rId182" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ007A_Detail.svg" xr:uid="{D96D22DE-45BD-4E25-A768-C8AAD05A8872}"/>
-    <hyperlink ref="B224" r:id="rId183" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ008A_Detail.svg" xr:uid="{14ADB638-7CCB-453F-BBA2-E88CDF197096}"/>
-    <hyperlink ref="B226" r:id="rId184" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ010A_Detail.svg" xr:uid="{7FE7B2D2-712E-48EB-BF5E-8AF8801ACB71}"/>
-    <hyperlink ref="B158" r:id="rId185" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP013A_Detail.svg" xr:uid="{81BF01ED-214F-4F7B-B7B6-1F88A3E341A7}"/>
-    <hyperlink ref="B266" r:id="rId186" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM005B_Detail.svg" xr:uid="{C4A57621-4274-4BF3-A654-A53519FAE7AF}"/>
-    <hyperlink ref="B268" r:id="rId187" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017B_Detail.svg" xr:uid="{8BEF6540-739A-43C4-8507-74B88B0E3308}"/>
-    <hyperlink ref="B6" r:id="rId188" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0003_Detail.svg" xr:uid="{5B095D40-6B08-42E7-9F0C-145F4A159D92}"/>
-    <hyperlink ref="B7" r:id="rId189" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0004_Detail.svg" xr:uid="{BA90B708-8CAD-4F91-A3A6-34C70C7242F4}"/>
-    <hyperlink ref="B8" r:id="rId190" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0005_Detail.svg" xr:uid="{A1CF53AA-4E63-4100-8F21-E83AA35C1604}"/>
-    <hyperlink ref="B5" r:id="rId191" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0002_Detail.svg" xr:uid="{A26CE6C0-2BFB-47C3-94E0-6267BE1C6C94}"/>
-    <hyperlink ref="B4" r:id="rId192" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0001_Detail.svg" xr:uid="{E14A7086-B4C6-4FDB-B7D4-7C18C702630A}"/>
-    <hyperlink ref="B20" r:id="rId193" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0015_Detail.svg" xr:uid="{AE8EBDA0-0651-4848-9397-12A25DA64674}"/>
-    <hyperlink ref="B22" r:id="rId194" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0017_Detail.svg" xr:uid="{0FDA170A-0CC3-4C20-BE1F-657A2C1B4131}"/>
-    <hyperlink ref="B23" r:id="rId195" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0018_Detail.svg" xr:uid="{258E20C7-8611-4032-9805-B672D23F3D38}"/>
-    <hyperlink ref="B24" r:id="rId196" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0019_Detail.svg" xr:uid="{16F5DBC3-6C32-416B-BD7D-406F3FF5549E}"/>
-    <hyperlink ref="B25" r:id="rId197" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0020_Detail.svg" xr:uid="{48785553-D98B-4E34-ABA8-058CAA66099A}"/>
-    <hyperlink ref="B26" r:id="rId198" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0021_Detail.svg" xr:uid="{139BFB00-00F8-4867-8E15-C1F2154F05F9}"/>
-    <hyperlink ref="B27" r:id="rId199" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0022_Detail.svg" xr:uid="{5494B9F9-EB11-44D9-9244-7B9E92E147F5}"/>
-    <hyperlink ref="B228" r:id="rId200" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PZ011B_Detail.svg" xr:uid="{0DC3D1D5-A861-49FB-8B82-28A6BF8D90FC}"/>
-    <hyperlink ref="B93" r:id="rId201" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PE006B_Detail.svg" xr:uid="{0C45D283-A845-475E-BF69-81FD14E9C822}"/>
-    <hyperlink ref="B28" r:id="rId202" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0023_Detail.svg" xr:uid="{4C39EC85-7752-4400-9B2C-6C4A7CF9129D}"/>
-    <hyperlink ref="B29" r:id="rId203" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0024_Detail.svg" xr:uid="{F3E501F0-9A11-487D-B608-F9A46D11F5A1}"/>
-    <hyperlink ref="B30" r:id="rId204" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0025_Detail.svg" xr:uid="{83989651-E3F6-4AA7-96A2-FD7640656CAE}"/>
-    <hyperlink ref="B31" r:id="rId205" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0026_Detail.svg" xr:uid="{8691DDEC-7612-406D-B419-95FB08A40E04}"/>
-    <hyperlink ref="B32" r:id="rId206" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/ND0027_Detail.svg" xr:uid="{E1D1D665-0762-4836-9D4E-CFC33239EFAB}"/>
-    <hyperlink ref="B33" r:id="rId207" xr:uid="{288414F9-9549-44EE-B603-BFEE8D6BFFCA}"/>
-    <hyperlink ref="B35" r:id="rId208" xr:uid="{126A3199-30C9-44DA-A9EF-F40296E4A52B}"/>
-    <hyperlink ref="B37" r:id="rId209" xr:uid="{FEADDADD-5407-491E-99C2-A1941A1DD8B1}"/>
-    <hyperlink ref="B38" r:id="rId210" xr:uid="{B79E6062-5651-4B01-BEC5-7AE62BF9E579}"/>
-    <hyperlink ref="B265" r:id="rId211" xr:uid="{D8769202-39EC-477B-918F-91334ACD1BAB}"/>
-    <hyperlink ref="B39" r:id="rId212" xr:uid="{DA884DEF-0521-4137-A538-91F1C7FA4324}"/>
-    <hyperlink ref="B40" r:id="rId213" xr:uid="{E1ACDD90-AB13-4518-A219-F9098936AE31}"/>
-    <hyperlink ref="B269" r:id="rId214" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{7F83B0A5-0EE0-43AE-AE92-E2BAA0FD9574}"/>
-    <hyperlink ref="B16" r:id="rId215" xr:uid="{77F0653D-0E68-4330-940A-9F070D3ED346}"/>
-    <hyperlink ref="B34" r:id="rId216" xr:uid="{9365B1F6-4046-4D2E-9EF9-1AB982DE479E}"/>
-    <hyperlink ref="B36" r:id="rId217" xr:uid="{B6BE678E-A7C5-4B5B-BB06-091807E2A914}"/>
-    <hyperlink ref="B190" r:id="rId218" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV003A_Detail.svg" xr:uid="{0C8B99AD-4AA9-417E-B1B0-268F75966BCC}"/>
-    <hyperlink ref="B192" r:id="rId219" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV004A_Detail.svg" xr:uid="{BDAFB8FD-95C0-434B-AE16-15137BA37528}"/>
-    <hyperlink ref="B194" r:id="rId220" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV005A_Detail.svg" xr:uid="{0038139D-21F7-423E-87D5-9C5E62376BA1}"/>
-    <hyperlink ref="B196" r:id="rId221" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV007A_Detail.svg" xr:uid="{5EC742DE-13C4-4141-8F82-5BD0F4B990E0}"/>
-    <hyperlink ref="B198" r:id="rId222" display="PV007A" xr:uid="{830B1051-3967-43FC-B80A-74AF1570BEB9}"/>
-    <hyperlink ref="B204" r:id="rId223" display="PV013A" xr:uid="{30F95586-AB92-4653-B23F-7D3D3A962855}"/>
-    <hyperlink ref="B206" r:id="rId224" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV015A_Detail.svg" xr:uid="{F26CE65B-B76B-4D88-BDC6-01693C600359}"/>
-    <hyperlink ref="B208" r:id="rId225" display="PV007A" xr:uid="{02722343-94B7-48EC-B39E-9165025BCC28}"/>
-    <hyperlink ref="B211" r:id="rId226" xr:uid="{58E62EE8-432E-4351-BC8D-0F8B4B9357B7}"/>
-    <hyperlink ref="B212" r:id="rId227" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV019A_Detail.svg" xr:uid="{78DCB1A4-463F-4102-997B-4F6DE28990A5}"/>
-    <hyperlink ref="B216" r:id="rId228" display="PV008A" xr:uid="{6917B420-C7C7-497A-A516-FF58A19815DA}"/>
-    <hyperlink ref="B44" r:id="rId229" display="ND0034" xr:uid="{856BC43A-036F-4783-BEFB-EFFAD7B38C2F}"/>
-    <hyperlink ref="B45" r:id="rId230" xr:uid="{818DB528-76D8-4FC4-8EC1-42D46B78152C}"/>
-    <hyperlink ref="B46" r:id="rId231" xr:uid="{F49E31A7-2551-4B04-BAED-A755D94DE548}"/>
-    <hyperlink ref="B47" r:id="rId232" xr:uid="{89382148-ED37-496D-BF2A-B7BD4982B43D}"/>
-    <hyperlink ref="B48" r:id="rId233" xr:uid="{FCC63734-2BEB-4CAA-ACB1-D5C765DB6D72}"/>
-    <hyperlink ref="B49" r:id="rId234" xr:uid="{B6C12D2A-856C-4100-A4FF-9108F71FAB3F}"/>
-    <hyperlink ref="B50" r:id="rId235" xr:uid="{2F8626FB-C2B7-4C4B-A874-A7B030C834DB}"/>
-    <hyperlink ref="B51" r:id="rId236" xr:uid="{535CCF00-68C0-462E-A26E-C4BA5A0CDDDE}"/>
-    <hyperlink ref="B12" r:id="rId237" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0008_Detail.svg" xr:uid="{D707B559-638D-4573-805C-C7D9CDB9CBC1}"/>
-    <hyperlink ref="B13" r:id="rId238" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/ND0009_Detail.svg" xr:uid="{FECDC847-0082-45AE-981B-3DFADADF1E67}"/>
-    <hyperlink ref="B43" r:id="rId239" display="ND0034" xr:uid="{D6EE3D3A-2058-4BA6-8D8D-23CF469451F6}"/>
-    <hyperlink ref="B42" r:id="rId240" display="ND0034" xr:uid="{8D64E28D-255B-48EB-94F8-E534EE940442}"/>
-    <hyperlink ref="B41" r:id="rId241" display="ND0034" xr:uid="{E64C006D-210D-4F3B-A4C7-58677D4CA2AF}"/>
+    <hyperlink ref="B4" r:id="rId1" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA001A_Detail.svg" xr:uid="{17ADBAC8-7138-41E8-BDFB-2ED015B2E3B6}"/>
+    <hyperlink ref="B11" r:id="rId2" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA008A_Detail.svg" xr:uid="{3A518947-B6F8-4C42-81D7-7894D9144A33}"/>
+    <hyperlink ref="B91" r:id="rId3" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP001A_Detail.svg" xr:uid="{761B47C6-804C-4528-8497-BBE932BB2C49}"/>
+    <hyperlink ref="B93" r:id="rId4" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP003A_Detail.svg" xr:uid="{EC8BC23F-0549-4B47-A475-38BE73BE9CEE}"/>
+    <hyperlink ref="B147" r:id="rId5" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV012A_Detail.svg" xr:uid="{5A391EDE-1D55-4CFD-9901-A29E0591193B}"/>
+    <hyperlink ref="B33" r:id="rId6" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE002A_Detail.svg" xr:uid="{BD7A7DCC-BFC7-48AF-B865-B8368E55F2E6}"/>
+    <hyperlink ref="B59" r:id="rId7" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE027A_Detail.svg" xr:uid="{4ECEB4FA-D039-495A-8F42-FFC9B443FDC3}"/>
+    <hyperlink ref="B84" r:id="rId8" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF009A_Detail.svg" xr:uid="{907022FE-3A1A-45BE-8FF2-AC230B1DD29B}"/>
+    <hyperlink ref="B133" r:id="rId9" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV001A_Detail.svg" xr:uid="{A8069CA7-B440-43C6-B571-35216079CADD}"/>
+    <hyperlink ref="B138" r:id="rId10" xr:uid="{7398F614-893C-4326-BA65-62E7CEF8B17B}"/>
+    <hyperlink ref="B152" r:id="rId11" xr:uid="{86D99A6B-DD65-4D76-9524-599D4EAB2E02}"/>
+    <hyperlink ref="B155" r:id="rId12" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV018A_Detail.svg" xr:uid="{3E8578A0-8239-405C-B417-86D7CEF2DB87}"/>
+    <hyperlink ref="B159" r:id="rId13" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV021A_Detail.svg" xr:uid="{27E00768-DA9C-4DAF-98AA-2381306E4A13}"/>
+    <hyperlink ref="B175" r:id="rId14" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ013A_Detail.svg" xr:uid="{9F7EE259-EBE5-4578-86F7-E5EF694FDA65}"/>
+    <hyperlink ref="B170" r:id="rId15" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ009A_Detail.svg" xr:uid="{30065FD0-FD2C-4BF8-A534-106ECA4A05E6}"/>
+    <hyperlink ref="B190" r:id="rId16" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/STPL008_Detail.svg" xr:uid="{F132DB26-A2BF-4161-B712-08766D64B599}"/>
+    <hyperlink ref="B193" r:id="rId17" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{21C87E9B-CBD0-4B81-A925-45F9B4FD8864}"/>
+    <hyperlink ref="B9" r:id="rId18" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA006A_Detail.svg" xr:uid="{C46298F6-C022-42A8-88EB-27031801D32E}"/>
+    <hyperlink ref="B6" r:id="rId19" display="PA002A" xr:uid="{6BAE8F82-BC2B-4427-9773-0A3AE429BDE1}"/>
+    <hyperlink ref="B34" r:id="rId20" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE003A_Detail.svg" xr:uid="{4004AC67-08BF-4573-A91C-196B852BE782}"/>
+    <hyperlink ref="B40" r:id="rId21" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE008A_Detail.svg" xr:uid="{907142FB-A61F-493E-ADCC-40C2E404D844}"/>
+    <hyperlink ref="B41" r:id="rId22" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE009A_Detail.svg" xr:uid="{42D7E312-902B-45B8-B2E6-478D821615A1}"/>
+    <hyperlink ref="B42" r:id="rId23" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE010A_Detail.svg" xr:uid="{12CE6EBF-4CA8-44DF-B6FC-040DFB92731D}"/>
+    <hyperlink ref="B29" r:id="rId24" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD018A_Detail.svg" xr:uid="{D9AD65D0-256C-4FDA-AB63-641CAEF296B8}"/>
+    <hyperlink ref="B32" r:id="rId25" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE001A_Detail.svg" xr:uid="{B5B862E7-DBAB-44C9-B7B4-21949ADAF9C9}"/>
+    <hyperlink ref="B37" r:id="rId26" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE006A_Detail.svg" xr:uid="{AA6401E6-CD51-4574-ABA6-C7BB3663F989}"/>
+    <hyperlink ref="B39" r:id="rId27" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE007A_Detail.svg" xr:uid="{B35184E7-56AF-48CA-8CC6-9A61FB055044}"/>
+    <hyperlink ref="B43" r:id="rId28" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE011A_Detail.svg" xr:uid="{52A5B7C0-AD9C-472F-899E-86CD63EFB3AA}"/>
+    <hyperlink ref="B44" r:id="rId29" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE012A_Detail.svg" xr:uid="{C3016BE0-26B5-41E3-A7DB-D7C53F62C108}"/>
+    <hyperlink ref="B45" r:id="rId30" display="PE012A" xr:uid="{FFB4E872-E736-41AC-8F80-41BB1E8C57A6}"/>
+    <hyperlink ref="B49" r:id="rId31" display="PE013A" xr:uid="{69F4C8E5-12AD-463A-8F4A-4719422312A8}"/>
+    <hyperlink ref="B23" r:id="rId32" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD012A_Detail.svg" xr:uid="{F25BE2C8-8813-4940-8329-63BBA6D15B89}"/>
+    <hyperlink ref="B134" r:id="rId33" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV002A_Detail.svg" xr:uid="{EB3DD888-4A6F-42F8-AD39-FAC973963B51}"/>
+    <hyperlink ref="B136" r:id="rId34" xr:uid="{C8A2ABD8-A0CE-4FB6-BD75-7694D40F91BE}"/>
+    <hyperlink ref="B140" r:id="rId35" xr:uid="{10BB9991-94D9-43E5-9038-0AD1029C8456}"/>
+    <hyperlink ref="B142" r:id="rId36" xr:uid="{E92459C1-EFAE-4D41-A9A2-B6CBF8031302}"/>
+    <hyperlink ref="B144" r:id="rId37" xr:uid="{FB94CBE5-59E0-4451-A8F5-AF4BCA7E6242}"/>
+    <hyperlink ref="B146" r:id="rId38" display="PV008A" xr:uid="{7C2F94E7-1DC8-40D5-9F4C-AA07CD1D7F60}"/>
+    <hyperlink ref="B148" r:id="rId39" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV013A_Detail.svg" xr:uid="{D981260A-8BAC-4F90-8B22-F4387848B90B}"/>
+    <hyperlink ref="B150" r:id="rId40" xr:uid="{7AB8E356-44B8-49E6-B29B-395AA92E87A4}"/>
+    <hyperlink ref="B154" r:id="rId41" xr:uid="{27C7E718-E4EC-4B45-A105-4219CB86145A}"/>
+    <hyperlink ref="B162" r:id="rId42" xr:uid="{22BEA91F-E09D-41B1-979E-65B6D728D85F}"/>
+    <hyperlink ref="B158" r:id="rId43" xr:uid="{64580D0C-1766-4DB3-AF77-41B1C3F4FBCB}"/>
+    <hyperlink ref="B163" r:id="rId44" display="PZ001A" xr:uid="{6198CEDF-7056-49B0-8C8C-0CE4F43ED518}"/>
+    <hyperlink ref="B5" r:id="rId45" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA002A_Detail.svg" xr:uid="{0302EB7E-2FF3-47CA-B5A8-8E3511F52559}"/>
+    <hyperlink ref="B18" r:id="rId46" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD007A_Detail.svg" xr:uid="{55939466-04EF-445D-B8C5-29A1F47BFBEC}"/>
+    <hyperlink ref="B12" r:id="rId47" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD001A_Detail.svg" xr:uid="{3C931296-EFA6-4A17-ABBE-BA3CEEBAE7CD}"/>
+    <hyperlink ref="B92" r:id="rId48" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP002A_Detail.svg" xr:uid="{7B04BB8C-B4F8-4443-9951-FF9779382F5E}"/>
+    <hyperlink ref="B98" r:id="rId49" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP008A_Detail.svg" xr:uid="{B8AA4B11-0A29-4052-8E9D-3BF8D275C0C3}"/>
+    <hyperlink ref="B94" r:id="rId50" display="PP003A" xr:uid="{A0025AF4-1428-4206-B942-D976CF2EABF6}"/>
+    <hyperlink ref="B95" r:id="rId51" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP005A_Detail.svg" xr:uid="{A6177C8F-61D8-4517-924D-AC098541874E}"/>
+    <hyperlink ref="B96" r:id="rId52" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP006A_Detail.svg" xr:uid="{CCC65F5C-1709-40F0-BC1E-5E22B9EE2E8B}"/>
+    <hyperlink ref="B97" r:id="rId53" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP007A_Detail.svg" xr:uid="{CF9DC830-F3E2-46F7-BB6E-F40EE3588C98}"/>
+    <hyperlink ref="B110" r:id="rId54" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS004A_Detail.svg" xr:uid="{9053D430-E6CE-479A-9C3A-E85BE51DDA2D}"/>
+    <hyperlink ref="B100" r:id="rId55" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP010A_Detail.svg" xr:uid="{0970F33B-0575-4123-83FA-27B45C94A4A2}"/>
+    <hyperlink ref="B101" r:id="rId56" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP011A_Detail.svg" xr:uid="{0EA32245-04D0-41E6-991A-61C23D6D04D5}"/>
+    <hyperlink ref="B102" r:id="rId57" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP012A_Detail.svg" xr:uid="{FBE8CA96-6772-460A-8C03-4C086593A5CE}"/>
+    <hyperlink ref="B104" r:id="rId58" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP014A_Detail.svg" xr:uid="{9377286C-CA88-49CA-8DB6-8B4673069711}"/>
+    <hyperlink ref="B105" r:id="rId59" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP015A_Detail.svg" xr:uid="{4CF07C91-9442-4F6E-8428-DC8B0ABD88EC}"/>
+    <hyperlink ref="B106" r:id="rId60" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP016A_Detail.svg" xr:uid="{95445AC5-539C-433D-929D-1B79509AB314}"/>
+    <hyperlink ref="B107" r:id="rId61" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP017A_Detail.svg" xr:uid="{F1EAA06B-6B10-469E-BFA8-DBE8DA0E67EC}"/>
+    <hyperlink ref="B108" r:id="rId62" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS001A_Detail.svg" xr:uid="{53C8229D-2E3F-405D-A9C8-3F6FE5E0EFCC}"/>
+    <hyperlink ref="B123" r:id="rId63" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT002A_Detail.svg" xr:uid="{8ED0FE06-63C6-4619-8AFA-C21DEA756B38}"/>
+    <hyperlink ref="B127" r:id="rId64" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT006A_Detail.svg" xr:uid="{DE7E75F2-6055-421D-A22C-888A6804396D}"/>
+    <hyperlink ref="B126" r:id="rId65" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT005A_Detail.svg" xr:uid="{95A726E8-8601-4CDB-BBED-77B49873F4C0}"/>
+    <hyperlink ref="B128" r:id="rId66" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT007A_Detail.svg" xr:uid="{B6131D2E-4752-4739-997C-D3CBF679F940}"/>
+    <hyperlink ref="B130" r:id="rId67" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT009A_Detail.svg" xr:uid="{D06AD6E5-7BA2-492F-8D44-8B09ADBF6122}"/>
+    <hyperlink ref="B131" r:id="rId68" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT010A_Detail.svg" xr:uid="{52343A83-46C2-4D49-BFE5-DA8717644CD2}"/>
+    <hyperlink ref="B164" r:id="rId69" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ003A_Detail.svg" xr:uid="{335D3D40-BE42-44FE-929A-0F3D3F26D262}"/>
+    <hyperlink ref="B165" r:id="rId70" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ004A_Detail.svg" xr:uid="{45517A4C-49CF-4A14-BE92-F3323139DBA8}"/>
+    <hyperlink ref="B167" r:id="rId71" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ006A_Detail.svg" xr:uid="{92F8D01F-B6E2-40C7-970D-7EAFB7872F29}"/>
+    <hyperlink ref="B174" r:id="rId72" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ012A_Detail.svg" xr:uid="{F5F1079A-1346-46A4-BF70-9025442AFB80}"/>
+    <hyperlink ref="B172" r:id="rId73" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ011A_Detail.svg" xr:uid="{BDA2ADBE-AC37-448F-9C41-243FB16B0996}"/>
+    <hyperlink ref="B8" r:id="rId74" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA005A_Detail.svg" xr:uid="{BA3A7E34-7D5B-4A78-BB78-1727C668EB8F}"/>
+    <hyperlink ref="B7" r:id="rId75" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA004A_Detail.svg" xr:uid="{39481051-1B60-44BF-8211-0D5C1980FD4B}"/>
+    <hyperlink ref="B13" r:id="rId76" display="PD001A" xr:uid="{3969656E-C88B-42A9-9C3B-B8275B159B5B}"/>
+    <hyperlink ref="B14" r:id="rId77" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD003A_Detail.svg" xr:uid="{86AB2467-10FE-4C5F-883D-EDA03495CD55}"/>
+    <hyperlink ref="B15" r:id="rId78" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD004A_Detail.svg" xr:uid="{A3F7C2AC-969E-4A1D-87C5-6BFE5671E4DC}"/>
+    <hyperlink ref="B16" r:id="rId79" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD005A_Detail.svg" xr:uid="{6DFFDA9D-5A28-4CC7-8DE9-876E2360BFEE}"/>
+    <hyperlink ref="B17" r:id="rId80" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD006A_Detail.svg" xr:uid="{3BB6ACEF-9AAF-4C4D-9A87-FCF6EA0F91BD}"/>
+    <hyperlink ref="B28" r:id="rId81" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD017A_Detail.svg" xr:uid="{28D1C6B0-DDE6-442D-9F10-91D27566478A}"/>
+    <hyperlink ref="B19" r:id="rId82" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD008A_Detail.svg" xr:uid="{AB7B0FCA-5804-4486-8380-FBA9F83DEE66}"/>
+    <hyperlink ref="B20" r:id="rId83" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD009A_Detail.svg" xr:uid="{9D870461-08B6-4714-8A00-09714564A8DF}"/>
+    <hyperlink ref="B21" r:id="rId84" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD010A_Detail.svg" xr:uid="{BB4A6A70-CBD2-4C62-B476-1DB99A7B8C9C}"/>
+    <hyperlink ref="B22" r:id="rId85" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD011A_Detail.svg" xr:uid="{5A9D789E-5B6D-46CC-883A-8FE28112F14B}"/>
+    <hyperlink ref="B24" r:id="rId86" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD013A_Detail.svg" xr:uid="{6394051E-0C5B-4871-B946-B73195930CB1}"/>
+    <hyperlink ref="B25" r:id="rId87" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD014A_Detail.svg" xr:uid="{89E87861-2175-4BEE-A5F9-33D47934E630}"/>
+    <hyperlink ref="B26" r:id="rId88" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD015A_Detail.svg" xr:uid="{C0901CAD-B396-4045-9DFB-94C087A6E9C7}"/>
+    <hyperlink ref="B27" r:id="rId89" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD016A_Detail.svg" xr:uid="{FE18571B-26F6-45A2-AE52-5E17B76EC7F3}"/>
+    <hyperlink ref="B50" r:id="rId90" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE018A_Detail.svg" xr:uid="{6D3B7973-3EAF-4809-A3A6-949465067CBC}"/>
+    <hyperlink ref="B52" r:id="rId91" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE020A_Detail.svg" xr:uid="{39CB98B6-29C9-4B55-BB4D-C050812B9145}"/>
+    <hyperlink ref="B53" r:id="rId92" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE021A_Detail.svg" xr:uid="{50AE8AE5-DEF4-4FC6-8682-258DF3904CD7}"/>
+    <hyperlink ref="B54" r:id="rId93" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE022A_Detail.svg" xr:uid="{93F60579-BA2A-4EDC-B883-017EBA23D13F}"/>
+    <hyperlink ref="B55" r:id="rId94" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE023A_Detail.svg" xr:uid="{2F7FC80D-3FA4-4BE4-A403-E017F265775F}"/>
+    <hyperlink ref="B56" r:id="rId95" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE024A_Detail.svg" xr:uid="{212E32CA-E31F-4B52-AC82-844C20339614}"/>
+    <hyperlink ref="B58" r:id="rId96" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE026A_Detail.svg" xr:uid="{9078864B-22E7-4236-BA73-76CA46B86A31}"/>
+    <hyperlink ref="B60" r:id="rId97" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE028A_Detail.svg" xr:uid="{F436B4D7-3AA5-4126-BBD2-BACE69A4A4E0}"/>
+    <hyperlink ref="B61" r:id="rId98" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE029A_Detail.svg" xr:uid="{C7A515AB-6C11-4EA4-85E4-5091485DAA17}"/>
+    <hyperlink ref="B65" r:id="rId99" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE033A_Detail.svg" xr:uid="{34E7B3BE-E531-4018-BB45-6CCB618C0FBB}"/>
+    <hyperlink ref="B62" r:id="rId100" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE030A_Detail.svg" xr:uid="{1F74D129-65A3-4B07-BF1F-5193476A8A04}"/>
+    <hyperlink ref="B64" r:id="rId101" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE032A_Detail.svg" xr:uid="{8A8FA28E-6634-4E0D-A29F-388C878E8DB9}"/>
+    <hyperlink ref="B66" r:id="rId102" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE034A_Detail.svg" xr:uid="{6C65D9E8-788A-4EFB-B896-E4E82EAA3CB0}"/>
+    <hyperlink ref="B68" r:id="rId103" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE036A_Detail.svg" xr:uid="{6A654C5A-571F-47D9-9387-6F62409DC1B7}"/>
+    <hyperlink ref="B67" r:id="rId104" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE035A_Detail.svg" xr:uid="{8BF957E4-037D-4E36-9BCA-83538FEE7EAF}"/>
+    <hyperlink ref="B69" r:id="rId105" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE037A_Detail.svg" xr:uid="{7931F92F-DB33-458A-84AB-EEE6E7217AAA}"/>
+    <hyperlink ref="B70" r:id="rId106" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE038A_Detail.svg" xr:uid="{F73D9E2D-2341-4000-BD06-BEF7EA513332}"/>
+    <hyperlink ref="B71" r:id="rId107" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE039A_Detail.svg" xr:uid="{FB0AAC16-DEA9-41D3-8765-ACE272916988}"/>
+    <hyperlink ref="B72" r:id="rId108" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE040A_Detail.svg" xr:uid="{9D15EFC4-F96D-4011-83A8-7E4FB0A02FD4}"/>
+    <hyperlink ref="B74" r:id="rId109" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE042A_Detail.svg" xr:uid="{4DC635F0-1E08-4047-98E2-D16EA3B8D3B6}"/>
+    <hyperlink ref="B75" r:id="rId110" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE043A_Detail.svg" xr:uid="{7A91C884-B181-4AC9-8872-A5B4FEC2FA44}"/>
+    <hyperlink ref="B76" r:id="rId111" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF001A_Detail.svg" xr:uid="{226AE98E-A3DA-4D82-91A1-7CFDF93A8DE9}"/>
+    <hyperlink ref="B77" r:id="rId112" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF002A_Detail.svg" xr:uid="{467E946A-F396-4E22-A95C-421F6CE0BC8B}"/>
+    <hyperlink ref="B78" r:id="rId113" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF003A_Detail.svg" xr:uid="{55C30B46-FD0C-4081-A7D2-D7A7DFE70B52}"/>
+    <hyperlink ref="B79" r:id="rId114" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF004A_Detail.svg" xr:uid="{1127E743-3E80-461C-9E2E-11276A527952}"/>
+    <hyperlink ref="B81" r:id="rId115" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF006A_Detail.svg" xr:uid="{C896FA40-2C0C-4F45-ABB7-4A0598EF464F}"/>
+    <hyperlink ref="B82" r:id="rId116" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF007A_Detail.svg" xr:uid="{B63E94F9-6FBE-473E-BB35-4B04D8BA205A}"/>
+    <hyperlink ref="B90" r:id="rId117" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF015A_Detail.svg" xr:uid="{D0C9703A-C515-442F-88BF-811B68EF3142}"/>
+    <hyperlink ref="B85" r:id="rId118" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF010A_Detail.svg" xr:uid="{8776960A-3D62-49BB-964C-0A029249E4ED}"/>
+    <hyperlink ref="B86" r:id="rId119" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF011A_Detail.svg" xr:uid="{52198015-5884-4164-AE13-C31DC940BF9F}"/>
+    <hyperlink ref="B88" r:id="rId120" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF013A_Detail.svg" xr:uid="{1676627D-C9A1-412D-A74B-FEC1DD6ADAFC}"/>
+    <hyperlink ref="B89" r:id="rId121" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF014A_Detail.svg" xr:uid="{0AE6782A-A294-4988-A1A8-09100E831215}"/>
+    <hyperlink ref="B3" r:id="rId122" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/LZ009A_Detail.svg" xr:uid="{964B3FA4-6BEE-49FA-A53D-C16D25DADF11}"/>
+    <hyperlink ref="B109" r:id="rId123" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS003A_Detail.svg" xr:uid="{D3E46F2B-78B9-41FF-AD13-E05C1AAC94AA}"/>
+    <hyperlink ref="B129" r:id="rId124" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT008A_Detail.svg" xr:uid="{A09F2ECE-A3F2-485F-89B3-392B6CCF3E0F}"/>
+    <hyperlink ref="B160" r:id="rId125" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV022A_Detail.svg" xr:uid="{7F2ADD73-6C39-4114-8228-83338A629639}"/>
+    <hyperlink ref="B186" r:id="rId126" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ024A_Detail.svg" xr:uid="{D7DC9173-D444-4E60-B47B-45295B162EA3}"/>
+    <hyperlink ref="B178" r:id="rId127" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ016A_Detail.svg" xr:uid="{223CCECC-C661-4D77-99FB-373C2C3EB9FD}"/>
+    <hyperlink ref="B184" r:id="rId128" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ022A_Detail.svg" xr:uid="{4E646DA6-844E-461F-A30F-E45D4A6BAEE0}"/>
+    <hyperlink ref="B179" r:id="rId129" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ017A_Detail.svg" xr:uid="{4AF15DA4-056F-4E39-B57F-D527D7C96314}"/>
+    <hyperlink ref="B180" r:id="rId130" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ018A_Detail.svg" xr:uid="{6A08BE2B-2F4A-40D0-87F1-2BF30F7E5204}"/>
+    <hyperlink ref="B181" r:id="rId131" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ019A_Detail.svg" xr:uid="{6C2DB1B2-D14C-41F7-85E9-0AD5CD60A40D}"/>
+    <hyperlink ref="B182" r:id="rId132" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ020A_Detail.svg" xr:uid="{3E5BB973-5805-404F-A772-22A577F5EA77}"/>
+    <hyperlink ref="B183" r:id="rId133" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ021A_Detail.svg" xr:uid="{96375F5D-1843-4B64-9FEB-59352041AF1C}"/>
+    <hyperlink ref="B185" r:id="rId134" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ023A_Detail.svg" xr:uid="{D811FB39-FE0C-4790-A865-54A17F50CA6D}"/>
+    <hyperlink ref="B187" r:id="rId135" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ025A_Detail.svg" xr:uid="{60163B1A-1792-49FF-9790-F2BF94ABFA4A}"/>
+    <hyperlink ref="B188" r:id="rId136" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ026A_Detail.svg" xr:uid="{0AAE0EB6-ECBB-4198-AA26-C684A0AECB97}"/>
+    <hyperlink ref="B189" r:id="rId137" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ027A_Detail.svg" xr:uid="{824407FA-7B30-4D5E-93CE-ED8122F65FFE}"/>
+    <hyperlink ref="B176" r:id="rId138" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ014A_Detail.svg" xr:uid="{F99B97AB-F1A6-4427-ABEB-25E3CC85B5DC}"/>
+    <hyperlink ref="B177" r:id="rId139" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ015A_Detail.svg" xr:uid="{12DA03AC-3D4B-49FC-B523-CC4091EF5CF4}"/>
+    <hyperlink ref="B30" r:id="rId140" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD019A_Detail.svg" xr:uid="{1FEADDE7-E396-46B6-9322-03EDCA28A99A}"/>
+    <hyperlink ref="B31" r:id="rId141" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PD020A_Detail.svg" xr:uid="{1987EC41-B7CC-4E23-B295-01B52113BE11}"/>
+    <hyperlink ref="B35" r:id="rId142" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE004A_Detail.svg" xr:uid="{22A02656-E11C-40BA-93D1-A3BA2FBE802C}"/>
+    <hyperlink ref="B36" r:id="rId143" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE005A_Detail.svg" xr:uid="{D679D4B8-1D0A-498C-B0C6-64751CDFD8A9}"/>
+    <hyperlink ref="B10" r:id="rId144" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PA007A_Detail.svg" xr:uid="{30DD321A-DB3E-4139-B7C6-5B72D5F41E50}"/>
+    <hyperlink ref="B46" r:id="rId145" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE014A_Detail.svg" xr:uid="{2B620BE4-F09B-478A-BDA6-76461B53049C}"/>
+    <hyperlink ref="B47" r:id="rId146" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE015A_Detail.svg" xr:uid="{57F06AB3-A2D4-42BD-8A97-785E7A9DEED3}"/>
+    <hyperlink ref="B48" r:id="rId147" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE016A_Detail.svg" xr:uid="{7714B096-A821-46A9-B38E-478AC0F60DFA}"/>
+    <hyperlink ref="B51" r:id="rId148" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE019A_Detail.svg" xr:uid="{77B288AB-A3B1-4E08-ABAC-36CEFD1274DD}"/>
+    <hyperlink ref="B63" r:id="rId149" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE031A_Detail.svg" xr:uid="{BD8A7598-0DFE-4ACB-ABFF-A23EE4147A0C}"/>
+    <hyperlink ref="B57" r:id="rId150" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE025A_Detail.svg" xr:uid="{111CB70F-38F3-4FA2-9171-155C1FE97029}"/>
+    <hyperlink ref="B111" r:id="rId151" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS005A_Detail.svg" xr:uid="{8BD8F9B2-845D-4212-B985-91349C8461AA}"/>
+    <hyperlink ref="B112" r:id="rId152" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS006A_Detail.svg" xr:uid="{616ABAAF-2406-46A1-9490-096325FB538C}"/>
+    <hyperlink ref="B113" r:id="rId153" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS007A_Detail.svg" xr:uid="{C158EBE4-9C88-4608-8165-95D1C5969FE5}"/>
+    <hyperlink ref="B114" r:id="rId154" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS008A_Detail.svg" xr:uid="{8B850863-4DBF-4261-A871-9900D82512A0}"/>
+    <hyperlink ref="B115" r:id="rId155" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS009A_Detail.svg" xr:uid="{EAA92938-1022-4B27-8A45-FC38DB3D12AB}"/>
+    <hyperlink ref="B116" r:id="rId156" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS010A_Detail.svg" xr:uid="{DE97D73F-147C-4EDC-A7D8-86145F37E03C}"/>
+    <hyperlink ref="B117" r:id="rId157" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS011A_Detail.svg" xr:uid="{006F66EF-728F-49E8-A5FE-751016748DAC}"/>
+    <hyperlink ref="B118" r:id="rId158" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS012A_Detail.svg" xr:uid="{8F448560-0B77-4837-B70F-0B9A88CD3C63}"/>
+    <hyperlink ref="B119" r:id="rId159" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS013A_Detail.svg" xr:uid="{0221699E-5F49-4DF1-B0AB-C4E5888F2A80}"/>
+    <hyperlink ref="B120" r:id="rId160" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS014A_Detail.svg" xr:uid="{C05394F3-DC5D-41A9-A414-4B0B18AAED5C}"/>
+    <hyperlink ref="B121" r:id="rId161" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS015A_Detail.svg" xr:uid="{C2CC68D8-9E61-4D94-BCC1-7A22522BAC81}"/>
+    <hyperlink ref="B122" r:id="rId162" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PS016A_Detail.svg" xr:uid="{47A88BDB-E04A-43F6-992D-C76510B510EF}"/>
+    <hyperlink ref="B124" r:id="rId163" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT003A_Detail.svg" xr:uid="{7CF97CF8-3E1A-4A9E-ABE2-3A579CF8676B}"/>
+    <hyperlink ref="B125" r:id="rId164" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT004A_Detail.svg" xr:uid="{75DC4A11-DAE8-4DC6-A6D0-7E3E61B719CC}"/>
+    <hyperlink ref="B73" r:id="rId165" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PE041A_Detail.svg" xr:uid="{EF9B4A93-EF2D-4E76-A4CC-16163CED7262}"/>
+    <hyperlink ref="B80" r:id="rId166" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF005A_Detail.svg" xr:uid="{3383514A-9E6D-45A7-AD65-0B18E1BAAD22}"/>
+    <hyperlink ref="B83" r:id="rId167" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF008A_Detail.svg" xr:uid="{73E8300F-62F2-4049-934B-015EDBEED287}"/>
+    <hyperlink ref="B87" r:id="rId168" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PF012A_Detail.svg" xr:uid="{E9B3CC0D-A34B-4C8A-B89B-B330DAD71021}"/>
+    <hyperlink ref="B99" r:id="rId169" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP009A_Detail.svg" xr:uid="{0A13328E-0285-44BD-B9CF-A05D28AD6EAD}"/>
+    <hyperlink ref="B132" r:id="rId170" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PT011A_Detail.svg" xr:uid="{E88B48B0-2B27-4600-8526-87B72CED5EC1}"/>
+    <hyperlink ref="B145" r:id="rId171" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV009A_Detail.svg" xr:uid="{25FF9022-3620-4A11-BF03-2A03200DD6CC}"/>
+    <hyperlink ref="B166" r:id="rId172" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ005A_Detail.svg" xr:uid="{92F69C2E-BC95-4B0C-9D0B-5D880C9FFE1C}"/>
+    <hyperlink ref="B168" r:id="rId173" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ007A_Detail.svg" xr:uid="{D96D22DE-45BD-4E25-A768-C8AAD05A8872}"/>
+    <hyperlink ref="B169" r:id="rId174" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ008A_Detail.svg" xr:uid="{14ADB638-7CCB-453F-BBA2-E88CDF197096}"/>
+    <hyperlink ref="B171" r:id="rId175" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PZ010A_Detail.svg" xr:uid="{7FE7B2D2-712E-48EB-BF5E-8AF8801ACB71}"/>
+    <hyperlink ref="B103" r:id="rId176" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PP013A_Detail.svg" xr:uid="{81BF01ED-214F-4F7B-B7B6-1F88A3E341A7}"/>
+    <hyperlink ref="B192" r:id="rId177" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM005B_Detail.svg" xr:uid="{C4A57621-4274-4BF3-A654-A53519FAE7AF}"/>
+    <hyperlink ref="B194" r:id="rId178" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017B_Detail.svg" xr:uid="{8BEF6540-739A-43C4-8507-74B88B0E3308}"/>
+    <hyperlink ref="B173" r:id="rId179" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PZ011B_Detail.svg" xr:uid="{0DC3D1D5-A861-49FB-8B82-28A6BF8D90FC}"/>
+    <hyperlink ref="B38" r:id="rId180" display="https://equinor.github.io/NOAKADEXPI/Symbols/Detail/PE006B_Detail.svg" xr:uid="{0C45D283-A845-475E-BF69-81FD14E9C822}"/>
+    <hyperlink ref="B191" r:id="rId181" xr:uid="{D8769202-39EC-477B-918F-91334ACD1BAB}"/>
+    <hyperlink ref="B195" r:id="rId182" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/IM017A_Detail.svg" xr:uid="{7F83B0A5-0EE0-43AE-AE92-E2BAA0FD9574}"/>
+    <hyperlink ref="B135" r:id="rId183" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV003A_Detail.svg" xr:uid="{0C8B99AD-4AA9-417E-B1B0-268F75966BCC}"/>
+    <hyperlink ref="B137" r:id="rId184" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV004A_Detail.svg" xr:uid="{BDAFB8FD-95C0-434B-AE16-15137BA37528}"/>
+    <hyperlink ref="B139" r:id="rId185" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV005A_Detail.svg" xr:uid="{0038139D-21F7-423E-87D5-9C5E62376BA1}"/>
+    <hyperlink ref="B141" r:id="rId186" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV007A_Detail.svg" xr:uid="{5EC742DE-13C4-4141-8F82-5BD0F4B990E0}"/>
+    <hyperlink ref="B143" r:id="rId187" display="PV007A" xr:uid="{830B1051-3967-43FC-B80A-74AF1570BEB9}"/>
+    <hyperlink ref="B149" r:id="rId188" display="PV013A" xr:uid="{30F95586-AB92-4653-B23F-7D3D3A962855}"/>
+    <hyperlink ref="B151" r:id="rId189" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV015A_Detail.svg" xr:uid="{F26CE65B-B76B-4D88-BDC6-01693C600359}"/>
+    <hyperlink ref="B153" r:id="rId190" display="PV007A" xr:uid="{02722343-94B7-48EC-B39E-9165025BCC28}"/>
+    <hyperlink ref="B156" r:id="rId191" xr:uid="{58E62EE8-432E-4351-BC8D-0F8B4B9357B7}"/>
+    <hyperlink ref="B157" r:id="rId192" display="https://toniapedersen.github.io/DEXPI/Symbols/Detail/PV019A_Detail.svg" xr:uid="{78DCB1A4-463F-4102-997B-4F6DE28990A5}"/>
+    <hyperlink ref="B161" r:id="rId193" display="PV008A" xr:uid="{6917B420-C7C7-497A-A516-FF58A19815DA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId242"/>
-  <legacyDrawing r:id="rId243"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId194"/>
+  <legacyDrawing r:id="rId195"/>
 </worksheet>
 </file>
 
